--- a/Bump_Sensor_Test/BumpDataArcCentred.xlsx
+++ b/Bump_Sensor_Test/BumpDataArcCentred.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uob-my.sharepoint.com/personal/hp21003_bristol_ac_uk/Documents/Year 4/Robotics/SEMTM0042_43_Group/Bump_Sensor_Test/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="8_{01EBAB60-033A-44EA-9F52-BC9677D5084A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6CEF73AA-2744-4DA3-9582-B9C69CD860C9}"/>
+  <xr:revisionPtr revIDLastSave="36" documentId="8_{01EBAB60-033A-44EA-9F52-BC9677D5084A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9F33BCF7-5BE3-4C49-8808-85D9792C7979}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="4" xr2:uid="{DC0997CF-A461-4C3D-B828-7A4D9066FEE4}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="8" xr2:uid="{DC0997CF-A461-4C3D-B828-7A4D9066FEE4}"/>
   </bookViews>
   <sheets>
     <sheet name="100mmY0" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,10 @@
     <sheet name="120mmY0" sheetId="3" r:id="rId3"/>
     <sheet name="130mmY0" sheetId="4" r:id="rId4"/>
     <sheet name="140mmY0" sheetId="5" r:id="rId5"/>
+    <sheet name="Addtional Tests" sheetId="6" r:id="rId6"/>
+    <sheet name="105mmY0" sheetId="7" r:id="rId7"/>
+    <sheet name="115mmY0" sheetId="8" r:id="rId8"/>
+    <sheet name="115 retest" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="6">
   <si>
     <t>i</t>
   </si>
@@ -13413,4 +13417,9083 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A6FFE5A-8BA2-4671-B7CF-947BFE7681B5}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0C50F00-B04B-41AD-97F3-D2B16142F239}">
+  <dimension ref="A1:I142"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2" t="s">
+        <v>1</v>
+      </c>
+      <c r="H2" t="s">
+        <v>2</v>
+      </c>
+      <c r="I2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>0</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>20661</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>1.95</v>
+      </c>
+      <c r="H3">
+        <v>0.32</v>
+      </c>
+      <c r="I3">
+        <v>14401</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>-0.28000000000000003</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>20711</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>1.95</v>
+      </c>
+      <c r="H4">
+        <v>0.32</v>
+      </c>
+      <c r="I4">
+        <v>14451</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5">
+        <v>-1.1299999999999999</v>
+      </c>
+      <c r="C5">
+        <v>-0.01</v>
+      </c>
+      <c r="D5">
+        <v>20761</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>1.95</v>
+      </c>
+      <c r="H5">
+        <v>0.32</v>
+      </c>
+      <c r="I5">
+        <v>14501</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6">
+        <v>-1.56</v>
+      </c>
+      <c r="C6">
+        <v>-0.02</v>
+      </c>
+      <c r="D6">
+        <v>20811</v>
+      </c>
+      <c r="F6">
+        <v>3</v>
+      </c>
+      <c r="G6">
+        <v>1.95</v>
+      </c>
+      <c r="H6">
+        <v>0.32</v>
+      </c>
+      <c r="I6">
+        <v>14552</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>4</v>
+      </c>
+      <c r="B7">
+        <v>-2.5499999999999998</v>
+      </c>
+      <c r="C7">
+        <v>-0.04</v>
+      </c>
+      <c r="D7">
+        <v>20861</v>
+      </c>
+      <c r="F7">
+        <v>4</v>
+      </c>
+      <c r="G7">
+        <v>1.95</v>
+      </c>
+      <c r="H7">
+        <v>0.32</v>
+      </c>
+      <c r="I7">
+        <v>14611</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>5</v>
+      </c>
+      <c r="B8">
+        <v>-5.81</v>
+      </c>
+      <c r="C8">
+        <v>-0.14000000000000001</v>
+      </c>
+      <c r="D8">
+        <v>20911</v>
+      </c>
+      <c r="F8">
+        <v>5</v>
+      </c>
+      <c r="G8">
+        <v>1.95</v>
+      </c>
+      <c r="H8">
+        <v>0.32</v>
+      </c>
+      <c r="I8">
+        <v>14661</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>6</v>
+      </c>
+      <c r="B9">
+        <v>-8.36</v>
+      </c>
+      <c r="C9">
+        <v>-0.21</v>
+      </c>
+      <c r="D9">
+        <v>20961</v>
+      </c>
+      <c r="F9">
+        <v>6</v>
+      </c>
+      <c r="G9">
+        <v>1.95</v>
+      </c>
+      <c r="H9">
+        <v>0.32</v>
+      </c>
+      <c r="I9">
+        <v>14711</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>7</v>
+      </c>
+      <c r="B10">
+        <v>-12.47</v>
+      </c>
+      <c r="C10">
+        <v>-0.36</v>
+      </c>
+      <c r="D10">
+        <v>21011</v>
+      </c>
+      <c r="F10">
+        <v>7</v>
+      </c>
+      <c r="G10">
+        <v>1.95</v>
+      </c>
+      <c r="H10">
+        <v>0.32</v>
+      </c>
+      <c r="I10">
+        <v>14761</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>8</v>
+      </c>
+      <c r="B11">
+        <v>-15.02</v>
+      </c>
+      <c r="C11">
+        <v>-0.47</v>
+      </c>
+      <c r="D11">
+        <v>21061</v>
+      </c>
+      <c r="F11">
+        <v>8</v>
+      </c>
+      <c r="G11">
+        <v>1.95</v>
+      </c>
+      <c r="H11">
+        <v>0.32</v>
+      </c>
+      <c r="I11">
+        <v>14811</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>9</v>
+      </c>
+      <c r="B12">
+        <v>-18.850000000000001</v>
+      </c>
+      <c r="C12">
+        <v>-0.65</v>
+      </c>
+      <c r="D12">
+        <v>21111</v>
+      </c>
+      <c r="F12">
+        <v>9</v>
+      </c>
+      <c r="G12">
+        <v>1.95</v>
+      </c>
+      <c r="H12">
+        <v>0.32</v>
+      </c>
+      <c r="I12">
+        <v>14861</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>10</v>
+      </c>
+      <c r="B13">
+        <v>-21.4</v>
+      </c>
+      <c r="C13">
+        <v>-0.78</v>
+      </c>
+      <c r="D13">
+        <v>21161</v>
+      </c>
+      <c r="F13">
+        <v>10</v>
+      </c>
+      <c r="G13">
+        <v>1.95</v>
+      </c>
+      <c r="H13">
+        <v>0.32</v>
+      </c>
+      <c r="I13">
+        <v>14911</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>11</v>
+      </c>
+      <c r="B14">
+        <v>-25.23</v>
+      </c>
+      <c r="C14">
+        <v>-1.01</v>
+      </c>
+      <c r="D14">
+        <v>21211</v>
+      </c>
+      <c r="F14">
+        <v>11</v>
+      </c>
+      <c r="G14">
+        <v>1.95</v>
+      </c>
+      <c r="H14">
+        <v>0.32</v>
+      </c>
+      <c r="I14">
+        <v>14961</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>12</v>
+      </c>
+      <c r="B15">
+        <v>-28.06</v>
+      </c>
+      <c r="C15">
+        <v>-1.19</v>
+      </c>
+      <c r="D15">
+        <v>21261</v>
+      </c>
+      <c r="F15">
+        <v>12</v>
+      </c>
+      <c r="G15">
+        <v>1.95</v>
+      </c>
+      <c r="H15">
+        <v>0.32</v>
+      </c>
+      <c r="I15">
+        <v>15011</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>13</v>
+      </c>
+      <c r="B16">
+        <v>-31.74</v>
+      </c>
+      <c r="C16">
+        <v>-1.44</v>
+      </c>
+      <c r="D16">
+        <v>21311</v>
+      </c>
+      <c r="F16">
+        <v>13</v>
+      </c>
+      <c r="G16">
+        <v>1.95</v>
+      </c>
+      <c r="H16">
+        <v>0.32</v>
+      </c>
+      <c r="I16">
+        <v>15062</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>14</v>
+      </c>
+      <c r="B17">
+        <v>-34.28</v>
+      </c>
+      <c r="C17">
+        <v>-1.63</v>
+      </c>
+      <c r="D17">
+        <v>21361</v>
+      </c>
+      <c r="F17">
+        <v>14</v>
+      </c>
+      <c r="G17">
+        <v>1.95</v>
+      </c>
+      <c r="H17">
+        <v>0.32</v>
+      </c>
+      <c r="I17">
+        <v>15121</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>15</v>
+      </c>
+      <c r="B18">
+        <v>-38.24</v>
+      </c>
+      <c r="C18">
+        <v>-1.94</v>
+      </c>
+      <c r="D18">
+        <v>21412</v>
+      </c>
+      <c r="F18">
+        <v>15</v>
+      </c>
+      <c r="G18">
+        <v>1.95</v>
+      </c>
+      <c r="H18">
+        <v>0.32</v>
+      </c>
+      <c r="I18">
+        <v>15171</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>16</v>
+      </c>
+      <c r="B19">
+        <v>-40.93</v>
+      </c>
+      <c r="C19">
+        <v>-2.19</v>
+      </c>
+      <c r="D19">
+        <v>21462</v>
+      </c>
+      <c r="F19">
+        <v>16</v>
+      </c>
+      <c r="G19">
+        <v>1.95</v>
+      </c>
+      <c r="H19">
+        <v>0.32</v>
+      </c>
+      <c r="I19">
+        <v>15221</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>17</v>
+      </c>
+      <c r="B20">
+        <v>-44.88</v>
+      </c>
+      <c r="C20">
+        <v>-2.56</v>
+      </c>
+      <c r="D20">
+        <v>21512</v>
+      </c>
+      <c r="F20">
+        <v>17</v>
+      </c>
+      <c r="G20">
+        <v>1.95</v>
+      </c>
+      <c r="H20">
+        <v>0.32</v>
+      </c>
+      <c r="I20">
+        <v>15271</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>18</v>
+      </c>
+      <c r="B21">
+        <v>-47.56</v>
+      </c>
+      <c r="C21">
+        <v>-2.82</v>
+      </c>
+      <c r="D21">
+        <v>21562</v>
+      </c>
+      <c r="F21">
+        <v>18</v>
+      </c>
+      <c r="G21">
+        <v>1.95</v>
+      </c>
+      <c r="H21">
+        <v>0.32</v>
+      </c>
+      <c r="I21">
+        <v>15321</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>19</v>
+      </c>
+      <c r="B22">
+        <v>-51.8</v>
+      </c>
+      <c r="C22">
+        <v>-3.26</v>
+      </c>
+      <c r="D22">
+        <v>21612</v>
+      </c>
+      <c r="F22">
+        <v>19</v>
+      </c>
+      <c r="G22">
+        <v>1.95</v>
+      </c>
+      <c r="H22">
+        <v>0.32</v>
+      </c>
+      <c r="I22">
+        <v>15371</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>20</v>
+      </c>
+      <c r="B23">
+        <v>-54.34</v>
+      </c>
+      <c r="C23">
+        <v>-3.55</v>
+      </c>
+      <c r="D23">
+        <v>21662</v>
+      </c>
+      <c r="F23">
+        <v>20</v>
+      </c>
+      <c r="G23">
+        <v>1.95</v>
+      </c>
+      <c r="H23">
+        <v>0.32</v>
+      </c>
+      <c r="I23">
+        <v>15421</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>21</v>
+      </c>
+      <c r="B24">
+        <v>-58.28</v>
+      </c>
+      <c r="C24">
+        <v>-4.0199999999999996</v>
+      </c>
+      <c r="D24">
+        <v>21712</v>
+      </c>
+      <c r="F24">
+        <v>21</v>
+      </c>
+      <c r="G24">
+        <v>1.95</v>
+      </c>
+      <c r="H24">
+        <v>0.32</v>
+      </c>
+      <c r="I24">
+        <v>15471</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>22</v>
+      </c>
+      <c r="B25">
+        <v>-61.1</v>
+      </c>
+      <c r="C25">
+        <v>-4.37</v>
+      </c>
+      <c r="D25">
+        <v>21762</v>
+      </c>
+      <c r="F25">
+        <v>22</v>
+      </c>
+      <c r="G25">
+        <v>1.95</v>
+      </c>
+      <c r="H25">
+        <v>0.32</v>
+      </c>
+      <c r="I25">
+        <v>15521</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>23</v>
+      </c>
+      <c r="B26">
+        <v>-65.17</v>
+      </c>
+      <c r="C26">
+        <v>-4.91</v>
+      </c>
+      <c r="D26">
+        <v>21812</v>
+      </c>
+      <c r="F26">
+        <v>23</v>
+      </c>
+      <c r="G26">
+        <v>1.95</v>
+      </c>
+      <c r="H26">
+        <v>0.32</v>
+      </c>
+      <c r="I26">
+        <v>15571</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>24</v>
+      </c>
+      <c r="B27">
+        <v>-68.12</v>
+      </c>
+      <c r="C27">
+        <v>-5.32</v>
+      </c>
+      <c r="D27">
+        <v>21862</v>
+      </c>
+      <c r="F27">
+        <v>24</v>
+      </c>
+      <c r="G27">
+        <v>1.95</v>
+      </c>
+      <c r="H27">
+        <v>0.32</v>
+      </c>
+      <c r="I27">
+        <v>15621</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>25</v>
+      </c>
+      <c r="B28">
+        <v>-72.34</v>
+      </c>
+      <c r="C28">
+        <v>-5.92</v>
+      </c>
+      <c r="D28">
+        <v>21912</v>
+      </c>
+      <c r="F28">
+        <v>25</v>
+      </c>
+      <c r="G28">
+        <v>1.95</v>
+      </c>
+      <c r="H28">
+        <v>0.32</v>
+      </c>
+      <c r="I28">
+        <v>15671</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>26</v>
+      </c>
+      <c r="B29">
+        <v>-75.14</v>
+      </c>
+      <c r="C29">
+        <v>-6.35</v>
+      </c>
+      <c r="D29">
+        <v>21963</v>
+      </c>
+      <c r="F29">
+        <v>26</v>
+      </c>
+      <c r="G29">
+        <v>1.95</v>
+      </c>
+      <c r="H29">
+        <v>0.32</v>
+      </c>
+      <c r="I29">
+        <v>15721</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>27</v>
+      </c>
+      <c r="B30">
+        <v>-79.63</v>
+      </c>
+      <c r="C30">
+        <v>-7.07</v>
+      </c>
+      <c r="D30">
+        <v>22013</v>
+      </c>
+      <c r="F30">
+        <v>27</v>
+      </c>
+      <c r="G30">
+        <v>1.95</v>
+      </c>
+      <c r="H30">
+        <v>0.32</v>
+      </c>
+      <c r="I30">
+        <v>15771</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>28</v>
+      </c>
+      <c r="B31">
+        <v>-82.28</v>
+      </c>
+      <c r="C31">
+        <v>-7.51</v>
+      </c>
+      <c r="D31">
+        <v>22063</v>
+      </c>
+      <c r="F31">
+        <v>28</v>
+      </c>
+      <c r="G31">
+        <v>1.95</v>
+      </c>
+      <c r="H31">
+        <v>0.32</v>
+      </c>
+      <c r="I31">
+        <v>15821</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>29</v>
+      </c>
+      <c r="B32">
+        <v>-86.62</v>
+      </c>
+      <c r="C32">
+        <v>-8.26</v>
+      </c>
+      <c r="D32">
+        <v>22113</v>
+      </c>
+      <c r="F32">
+        <v>29</v>
+      </c>
+      <c r="G32">
+        <v>1.95</v>
+      </c>
+      <c r="H32">
+        <v>0.32</v>
+      </c>
+      <c r="I32">
+        <v>15872</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>30</v>
+      </c>
+      <c r="B33">
+        <v>-89.55</v>
+      </c>
+      <c r="C33">
+        <v>-8.7799999999999994</v>
+      </c>
+      <c r="D33">
+        <v>22163</v>
+      </c>
+      <c r="F33">
+        <v>30</v>
+      </c>
+      <c r="G33">
+        <v>1.95</v>
+      </c>
+      <c r="H33">
+        <v>0.32</v>
+      </c>
+      <c r="I33">
+        <v>15931</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A34">
+        <v>31</v>
+      </c>
+      <c r="B34">
+        <v>-94.02</v>
+      </c>
+      <c r="C34">
+        <v>-9.59</v>
+      </c>
+      <c r="D34">
+        <v>22214</v>
+      </c>
+      <c r="F34">
+        <v>31</v>
+      </c>
+      <c r="G34">
+        <v>1.95</v>
+      </c>
+      <c r="H34">
+        <v>0.32</v>
+      </c>
+      <c r="I34">
+        <v>15981</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A35">
+        <v>32</v>
+      </c>
+      <c r="B35">
+        <v>-96.94</v>
+      </c>
+      <c r="C35">
+        <v>-10.15</v>
+      </c>
+      <c r="D35">
+        <v>22264</v>
+      </c>
+      <c r="F35">
+        <v>32</v>
+      </c>
+      <c r="G35">
+        <v>1.95</v>
+      </c>
+      <c r="H35">
+        <v>0.32</v>
+      </c>
+      <c r="I35">
+        <v>16031</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A36">
+        <v>33</v>
+      </c>
+      <c r="B36">
+        <v>-101.26</v>
+      </c>
+      <c r="C36">
+        <v>-11.02</v>
+      </c>
+      <c r="D36">
+        <v>22315</v>
+      </c>
+      <c r="F36">
+        <v>33</v>
+      </c>
+      <c r="G36">
+        <v>1.95</v>
+      </c>
+      <c r="H36">
+        <v>0.32</v>
+      </c>
+      <c r="I36">
+        <v>16081</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A37">
+        <v>34</v>
+      </c>
+      <c r="B37">
+        <v>-104.17</v>
+      </c>
+      <c r="C37">
+        <v>-11.62</v>
+      </c>
+      <c r="D37">
+        <v>22365</v>
+      </c>
+      <c r="F37">
+        <v>34</v>
+      </c>
+      <c r="G37">
+        <v>1.95</v>
+      </c>
+      <c r="H37">
+        <v>0.32</v>
+      </c>
+      <c r="I37">
+        <v>16131</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A38">
+        <v>35</v>
+      </c>
+      <c r="B38">
+        <v>-108.61</v>
+      </c>
+      <c r="C38">
+        <v>-12.57</v>
+      </c>
+      <c r="D38">
+        <v>22415</v>
+      </c>
+      <c r="F38">
+        <v>35</v>
+      </c>
+      <c r="G38">
+        <v>1.95</v>
+      </c>
+      <c r="H38">
+        <v>0.32</v>
+      </c>
+      <c r="I38">
+        <v>16181</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A39">
+        <v>36</v>
+      </c>
+      <c r="B39">
+        <v>-111.66</v>
+      </c>
+      <c r="C39">
+        <v>-13.25</v>
+      </c>
+      <c r="D39">
+        <v>22465</v>
+      </c>
+      <c r="F39">
+        <v>36</v>
+      </c>
+      <c r="G39">
+        <v>1.95</v>
+      </c>
+      <c r="H39">
+        <v>0.32</v>
+      </c>
+      <c r="I39">
+        <v>16231</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A40">
+        <v>37</v>
+      </c>
+      <c r="B40">
+        <v>-116.36</v>
+      </c>
+      <c r="C40">
+        <v>-14.33</v>
+      </c>
+      <c r="D40">
+        <v>22515</v>
+      </c>
+      <c r="F40">
+        <v>37</v>
+      </c>
+      <c r="G40">
+        <v>1.95</v>
+      </c>
+      <c r="H40">
+        <v>0.32</v>
+      </c>
+      <c r="I40">
+        <v>16281</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A41">
+        <v>38</v>
+      </c>
+      <c r="B41">
+        <v>-119.53</v>
+      </c>
+      <c r="C41">
+        <v>-15.1</v>
+      </c>
+      <c r="D41">
+        <v>22565</v>
+      </c>
+      <c r="F41">
+        <v>38</v>
+      </c>
+      <c r="G41">
+        <v>1.95</v>
+      </c>
+      <c r="H41">
+        <v>0.32</v>
+      </c>
+      <c r="I41">
+        <v>16331</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A42">
+        <v>39</v>
+      </c>
+      <c r="B42">
+        <v>-123.94</v>
+      </c>
+      <c r="C42">
+        <v>-16.18</v>
+      </c>
+      <c r="D42">
+        <v>22615</v>
+      </c>
+      <c r="F42">
+        <v>39</v>
+      </c>
+      <c r="G42">
+        <v>1.95</v>
+      </c>
+      <c r="H42">
+        <v>0.32</v>
+      </c>
+      <c r="I42">
+        <v>16381</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A43">
+        <v>40</v>
+      </c>
+      <c r="B43">
+        <v>-127.1</v>
+      </c>
+      <c r="C43">
+        <v>-16.98</v>
+      </c>
+      <c r="D43">
+        <v>22665</v>
+      </c>
+      <c r="F43">
+        <v>40</v>
+      </c>
+      <c r="G43">
+        <v>1.95</v>
+      </c>
+      <c r="H43">
+        <v>0.32</v>
+      </c>
+      <c r="I43">
+        <v>16431</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A44">
+        <v>41</v>
+      </c>
+      <c r="B44">
+        <v>-131.63999999999999</v>
+      </c>
+      <c r="C44">
+        <v>-18.149999999999999</v>
+      </c>
+      <c r="D44">
+        <v>22716</v>
+      </c>
+      <c r="F44">
+        <v>41</v>
+      </c>
+      <c r="G44">
+        <v>1.95</v>
+      </c>
+      <c r="H44">
+        <v>0.32</v>
+      </c>
+      <c r="I44">
+        <v>16481</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A45">
+        <v>42</v>
+      </c>
+      <c r="B45">
+        <v>-134.79</v>
+      </c>
+      <c r="C45">
+        <v>-19</v>
+      </c>
+      <c r="D45">
+        <v>22767</v>
+      </c>
+      <c r="F45">
+        <v>42</v>
+      </c>
+      <c r="G45">
+        <v>1.95</v>
+      </c>
+      <c r="H45">
+        <v>0.32</v>
+      </c>
+      <c r="I45">
+        <v>16531</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A46">
+        <v>43</v>
+      </c>
+      <c r="B46">
+        <v>-139.58000000000001</v>
+      </c>
+      <c r="C46">
+        <v>-20.309999999999999</v>
+      </c>
+      <c r="D46">
+        <v>22817</v>
+      </c>
+      <c r="F46">
+        <v>43</v>
+      </c>
+      <c r="G46">
+        <v>1.95</v>
+      </c>
+      <c r="H46">
+        <v>0.32</v>
+      </c>
+      <c r="I46">
+        <v>16581</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A47">
+        <v>44</v>
+      </c>
+      <c r="B47">
+        <v>-142.58000000000001</v>
+      </c>
+      <c r="C47">
+        <v>-21.16</v>
+      </c>
+      <c r="D47">
+        <v>22867</v>
+      </c>
+      <c r="F47">
+        <v>44</v>
+      </c>
+      <c r="G47">
+        <v>1.95</v>
+      </c>
+      <c r="H47">
+        <v>0.32</v>
+      </c>
+      <c r="I47">
+        <v>16632</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A48">
+        <v>45</v>
+      </c>
+      <c r="B48">
+        <v>-147.35</v>
+      </c>
+      <c r="C48">
+        <v>-22.54</v>
+      </c>
+      <c r="D48">
+        <v>22917</v>
+      </c>
+      <c r="F48">
+        <v>45</v>
+      </c>
+      <c r="G48">
+        <v>2.09</v>
+      </c>
+      <c r="H48">
+        <v>0.32</v>
+      </c>
+      <c r="I48">
+        <v>16683</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A49">
+        <v>46</v>
+      </c>
+      <c r="B49">
+        <v>-150.61000000000001</v>
+      </c>
+      <c r="C49">
+        <v>-23.52</v>
+      </c>
+      <c r="D49">
+        <v>22967</v>
+      </c>
+      <c r="F49">
+        <v>46</v>
+      </c>
+      <c r="G49">
+        <v>2.09</v>
+      </c>
+      <c r="H49">
+        <v>0.32</v>
+      </c>
+      <c r="I49">
+        <v>16742</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A50">
+        <v>47</v>
+      </c>
+      <c r="B50">
+        <v>-155.36000000000001</v>
+      </c>
+      <c r="C50">
+        <v>-24.97</v>
+      </c>
+      <c r="D50">
+        <v>23017</v>
+      </c>
+      <c r="F50">
+        <v>47</v>
+      </c>
+      <c r="G50">
+        <v>2.09</v>
+      </c>
+      <c r="H50">
+        <v>0.32</v>
+      </c>
+      <c r="I50">
+        <v>16792</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A51">
+        <v>48</v>
+      </c>
+      <c r="B51">
+        <v>-158.47</v>
+      </c>
+      <c r="C51">
+        <v>-25.94</v>
+      </c>
+      <c r="D51">
+        <v>23067</v>
+      </c>
+      <c r="F51">
+        <v>48</v>
+      </c>
+      <c r="G51">
+        <v>2.09</v>
+      </c>
+      <c r="H51">
+        <v>0.32</v>
+      </c>
+      <c r="I51">
+        <v>16842</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A52">
+        <v>49</v>
+      </c>
+      <c r="B52">
+        <v>-163.19999999999999</v>
+      </c>
+      <c r="C52">
+        <v>-27.46</v>
+      </c>
+      <c r="D52">
+        <v>23117</v>
+      </c>
+      <c r="F52">
+        <v>49</v>
+      </c>
+      <c r="G52">
+        <v>2.09</v>
+      </c>
+      <c r="H52">
+        <v>0.32</v>
+      </c>
+      <c r="I52">
+        <v>16892</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A53">
+        <v>50</v>
+      </c>
+      <c r="B53">
+        <v>-166.3</v>
+      </c>
+      <c r="C53">
+        <v>-28.49</v>
+      </c>
+      <c r="D53">
+        <v>23168</v>
+      </c>
+      <c r="F53">
+        <v>50</v>
+      </c>
+      <c r="G53">
+        <v>3.8</v>
+      </c>
+      <c r="H53">
+        <v>0.35</v>
+      </c>
+      <c r="I53">
+        <v>16942</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A54">
+        <v>51</v>
+      </c>
+      <c r="B54">
+        <v>-171.27</v>
+      </c>
+      <c r="C54">
+        <v>-30.18</v>
+      </c>
+      <c r="D54">
+        <v>23218</v>
+      </c>
+      <c r="F54">
+        <v>51</v>
+      </c>
+      <c r="G54">
+        <v>6.07</v>
+      </c>
+      <c r="H54">
+        <v>0.36</v>
+      </c>
+      <c r="I54">
+        <v>16992</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A55">
+        <v>52</v>
+      </c>
+      <c r="B55">
+        <v>-174.35</v>
+      </c>
+      <c r="C55">
+        <v>-31.25</v>
+      </c>
+      <c r="D55">
+        <v>23268</v>
+      </c>
+      <c r="F55">
+        <v>52</v>
+      </c>
+      <c r="G55">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="H55">
+        <v>0.36</v>
+      </c>
+      <c r="I55">
+        <v>17042</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A56">
+        <v>53</v>
+      </c>
+      <c r="B56">
+        <v>-179.3</v>
+      </c>
+      <c r="C56">
+        <v>-33</v>
+      </c>
+      <c r="D56">
+        <v>23318</v>
+      </c>
+      <c r="F56">
+        <v>53</v>
+      </c>
+      <c r="G56">
+        <v>12.61</v>
+      </c>
+      <c r="H56">
+        <v>0.35</v>
+      </c>
+      <c r="I56">
+        <v>17092</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A57">
+        <v>54</v>
+      </c>
+      <c r="B57">
+        <v>-182.63</v>
+      </c>
+      <c r="C57">
+        <v>-34.21</v>
+      </c>
+      <c r="D57">
+        <v>23369</v>
+      </c>
+      <c r="F57">
+        <v>54</v>
+      </c>
+      <c r="G57">
+        <v>16.16</v>
+      </c>
+      <c r="H57">
+        <v>0.34</v>
+      </c>
+      <c r="I57">
+        <v>17142</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A58">
+        <v>55</v>
+      </c>
+      <c r="B58">
+        <v>-187.42</v>
+      </c>
+      <c r="C58">
+        <v>-35.979999999999997</v>
+      </c>
+      <c r="D58">
+        <v>23419</v>
+      </c>
+      <c r="F58">
+        <v>55</v>
+      </c>
+      <c r="G58">
+        <v>19.850000000000001</v>
+      </c>
+      <c r="H58">
+        <v>0.33</v>
+      </c>
+      <c r="I58">
+        <v>17192</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A59">
+        <v>56</v>
+      </c>
+      <c r="B59">
+        <v>-190.6</v>
+      </c>
+      <c r="C59">
+        <v>-37.19</v>
+      </c>
+      <c r="D59">
+        <v>23469</v>
+      </c>
+      <c r="F59">
+        <v>56</v>
+      </c>
+      <c r="G59">
+        <v>23.83</v>
+      </c>
+      <c r="H59">
+        <v>0.34</v>
+      </c>
+      <c r="I59">
+        <v>17242</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A60">
+        <v>57</v>
+      </c>
+      <c r="B60">
+        <v>-195.37</v>
+      </c>
+      <c r="C60">
+        <v>-39.04</v>
+      </c>
+      <c r="D60">
+        <v>23519</v>
+      </c>
+      <c r="F60">
+        <v>57</v>
+      </c>
+      <c r="G60">
+        <v>27.81</v>
+      </c>
+      <c r="H60">
+        <v>0.34</v>
+      </c>
+      <c r="I60">
+        <v>17292</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A61">
+        <v>58</v>
+      </c>
+      <c r="B61">
+        <v>-198.53</v>
+      </c>
+      <c r="C61">
+        <v>-40.299999999999997</v>
+      </c>
+      <c r="D61">
+        <v>23569</v>
+      </c>
+      <c r="F61">
+        <v>58</v>
+      </c>
+      <c r="G61">
+        <v>31.93</v>
+      </c>
+      <c r="H61">
+        <v>0.35</v>
+      </c>
+      <c r="I61">
+        <v>17342</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A62">
+        <v>59</v>
+      </c>
+      <c r="B62">
+        <v>-203.39</v>
+      </c>
+      <c r="C62">
+        <v>-42.28</v>
+      </c>
+      <c r="D62">
+        <v>23620</v>
+      </c>
+      <c r="F62">
+        <v>59</v>
+      </c>
+      <c r="G62">
+        <v>35.770000000000003</v>
+      </c>
+      <c r="H62">
+        <v>0.37</v>
+      </c>
+      <c r="I62">
+        <v>17392</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A63">
+        <v>60</v>
+      </c>
+      <c r="B63">
+        <v>-206.79</v>
+      </c>
+      <c r="C63">
+        <v>-43.7</v>
+      </c>
+      <c r="D63">
+        <v>23670</v>
+      </c>
+      <c r="F63">
+        <v>60</v>
+      </c>
+      <c r="G63">
+        <v>39.75</v>
+      </c>
+      <c r="H63">
+        <v>0.4</v>
+      </c>
+      <c r="I63">
+        <v>17442</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A64">
+        <v>61</v>
+      </c>
+      <c r="B64">
+        <v>-211.49</v>
+      </c>
+      <c r="C64">
+        <v>-45.71</v>
+      </c>
+      <c r="D64">
+        <v>23720</v>
+      </c>
+      <c r="F64">
+        <v>61</v>
+      </c>
+      <c r="G64">
+        <v>44.01</v>
+      </c>
+      <c r="H64">
+        <v>0.43</v>
+      </c>
+      <c r="I64">
+        <v>17492</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A65">
+        <v>62</v>
+      </c>
+      <c r="B65">
+        <v>-214.74</v>
+      </c>
+      <c r="C65">
+        <v>-47.14</v>
+      </c>
+      <c r="D65">
+        <v>23770</v>
+      </c>
+      <c r="F65">
+        <v>62</v>
+      </c>
+      <c r="G65">
+        <v>48.13</v>
+      </c>
+      <c r="H65">
+        <v>0.46</v>
+      </c>
+      <c r="I65">
+        <v>17542</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A66">
+        <v>63</v>
+      </c>
+      <c r="B66">
+        <v>-219.4</v>
+      </c>
+      <c r="C66">
+        <v>-49.22</v>
+      </c>
+      <c r="D66">
+        <v>23820</v>
+      </c>
+      <c r="F66">
+        <v>63</v>
+      </c>
+      <c r="G66">
+        <v>52.39</v>
+      </c>
+      <c r="H66">
+        <v>0.51</v>
+      </c>
+      <c r="I66">
+        <v>17592</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A67">
+        <v>64</v>
+      </c>
+      <c r="B67">
+        <v>-222.63</v>
+      </c>
+      <c r="C67">
+        <v>-50.69</v>
+      </c>
+      <c r="D67">
+        <v>23870</v>
+      </c>
+      <c r="F67">
+        <v>64</v>
+      </c>
+      <c r="G67">
+        <v>56.66</v>
+      </c>
+      <c r="H67">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="I67">
+        <v>17642</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A68">
+        <v>65</v>
+      </c>
+      <c r="B68">
+        <v>-227.65</v>
+      </c>
+      <c r="C68">
+        <v>-53.01</v>
+      </c>
+      <c r="D68">
+        <v>23920</v>
+      </c>
+      <c r="F68">
+        <v>65</v>
+      </c>
+      <c r="G68">
+        <v>61.06</v>
+      </c>
+      <c r="H68">
+        <v>0.59</v>
+      </c>
+      <c r="I68">
+        <v>17692</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A69">
+        <v>66</v>
+      </c>
+      <c r="B69">
+        <v>-230.73</v>
+      </c>
+      <c r="C69">
+        <v>-54.46</v>
+      </c>
+      <c r="D69">
+        <v>23970</v>
+      </c>
+      <c r="F69">
+        <v>66</v>
+      </c>
+      <c r="G69">
+        <v>65.61</v>
+      </c>
+      <c r="H69">
+        <v>0.65</v>
+      </c>
+      <c r="I69">
+        <v>17742</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A70">
+        <v>67</v>
+      </c>
+      <c r="B70">
+        <v>-235.59</v>
+      </c>
+      <c r="C70">
+        <v>-56.78</v>
+      </c>
+      <c r="D70">
+        <v>24020</v>
+      </c>
+      <c r="F70">
+        <v>67</v>
+      </c>
+      <c r="G70">
+        <v>70.010000000000005</v>
+      </c>
+      <c r="H70">
+        <v>0.72</v>
+      </c>
+      <c r="I70">
+        <v>17793</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A71">
+        <v>68</v>
+      </c>
+      <c r="B71">
+        <v>-238.78</v>
+      </c>
+      <c r="C71">
+        <v>-58.34</v>
+      </c>
+      <c r="D71">
+        <v>24070</v>
+      </c>
+      <c r="F71">
+        <v>68</v>
+      </c>
+      <c r="G71">
+        <v>75.13</v>
+      </c>
+      <c r="H71">
+        <v>0.8</v>
+      </c>
+      <c r="I71">
+        <v>17852</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A72">
+        <v>69</v>
+      </c>
+      <c r="B72">
+        <v>-243.73</v>
+      </c>
+      <c r="C72">
+        <v>-60.82</v>
+      </c>
+      <c r="D72">
+        <v>24120</v>
+      </c>
+      <c r="F72">
+        <v>69</v>
+      </c>
+      <c r="G72">
+        <v>79.81</v>
+      </c>
+      <c r="H72">
+        <v>0.88</v>
+      </c>
+      <c r="I72">
+        <v>17902</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A73">
+        <v>70</v>
+      </c>
+      <c r="B73">
+        <v>-246.76</v>
+      </c>
+      <c r="C73">
+        <v>-62.36</v>
+      </c>
+      <c r="D73">
+        <v>24170</v>
+      </c>
+      <c r="F73">
+        <v>70</v>
+      </c>
+      <c r="G73">
+        <v>84.36</v>
+      </c>
+      <c r="H73">
+        <v>0.97</v>
+      </c>
+      <c r="I73">
+        <v>17952</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A74">
+        <v>71</v>
+      </c>
+      <c r="B74">
+        <v>-251.67</v>
+      </c>
+      <c r="C74">
+        <v>-64.92</v>
+      </c>
+      <c r="D74">
+        <v>24220</v>
+      </c>
+      <c r="F74">
+        <v>71</v>
+      </c>
+      <c r="G74">
+        <v>88.91</v>
+      </c>
+      <c r="H74">
+        <v>1.05</v>
+      </c>
+      <c r="I74">
+        <v>18002</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A75">
+        <v>72</v>
+      </c>
+      <c r="B75">
+        <v>-254.92</v>
+      </c>
+      <c r="C75">
+        <v>-66.650000000000006</v>
+      </c>
+      <c r="D75">
+        <v>24270</v>
+      </c>
+      <c r="F75">
+        <v>72</v>
+      </c>
+      <c r="G75">
+        <v>93.17</v>
+      </c>
+      <c r="H75">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="I75">
+        <v>18052</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A76">
+        <v>73</v>
+      </c>
+      <c r="B76">
+        <v>-259.79000000000002</v>
+      </c>
+      <c r="C76">
+        <v>-69.290000000000006</v>
+      </c>
+      <c r="D76">
+        <v>24320</v>
+      </c>
+      <c r="F76">
+        <v>73</v>
+      </c>
+      <c r="G76">
+        <v>97.71</v>
+      </c>
+      <c r="H76">
+        <v>1.25</v>
+      </c>
+      <c r="I76">
+        <v>18102</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A77">
+        <v>74</v>
+      </c>
+      <c r="B77">
+        <v>-262.77</v>
+      </c>
+      <c r="C77">
+        <v>-70.94</v>
+      </c>
+      <c r="D77">
+        <v>24371</v>
+      </c>
+      <c r="F77">
+        <v>74</v>
+      </c>
+      <c r="G77">
+        <v>102.26</v>
+      </c>
+      <c r="H77">
+        <v>1.34</v>
+      </c>
+      <c r="I77">
+        <v>18152</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A78">
+        <v>75</v>
+      </c>
+      <c r="B78">
+        <v>-266.10000000000002</v>
+      </c>
+      <c r="C78">
+        <v>-72.83</v>
+      </c>
+      <c r="D78">
+        <v>24421</v>
+      </c>
+      <c r="F78">
+        <v>75</v>
+      </c>
+      <c r="G78">
+        <v>106.81</v>
+      </c>
+      <c r="H78">
+        <v>1.43</v>
+      </c>
+      <c r="I78">
+        <v>18202</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A79">
+        <v>76</v>
+      </c>
+      <c r="B79">
+        <v>-268.56</v>
+      </c>
+      <c r="C79">
+        <v>-74.239999999999995</v>
+      </c>
+      <c r="D79">
+        <v>24471</v>
+      </c>
+      <c r="F79">
+        <v>76</v>
+      </c>
+      <c r="G79">
+        <v>111.21</v>
+      </c>
+      <c r="H79">
+        <v>1.53</v>
+      </c>
+      <c r="I79">
+        <v>18252</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A80">
+        <v>77</v>
+      </c>
+      <c r="B80">
+        <v>-271.99</v>
+      </c>
+      <c r="C80">
+        <v>-76.239999999999995</v>
+      </c>
+      <c r="D80">
+        <v>24521</v>
+      </c>
+      <c r="F80">
+        <v>77</v>
+      </c>
+      <c r="G80">
+        <v>115.19</v>
+      </c>
+      <c r="H80">
+        <v>1.62</v>
+      </c>
+      <c r="I80">
+        <v>18302</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A81">
+        <v>78</v>
+      </c>
+      <c r="B81">
+        <v>-274.43</v>
+      </c>
+      <c r="C81">
+        <v>-77.7</v>
+      </c>
+      <c r="D81">
+        <v>24571</v>
+      </c>
+      <c r="F81">
+        <v>78</v>
+      </c>
+      <c r="G81">
+        <v>119.02</v>
+      </c>
+      <c r="H81">
+        <v>1.7</v>
+      </c>
+      <c r="I81">
+        <v>18352</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A82">
+        <v>79</v>
+      </c>
+      <c r="B82">
+        <v>-277.95</v>
+      </c>
+      <c r="C82">
+        <v>-79.83</v>
+      </c>
+      <c r="D82">
+        <v>24621</v>
+      </c>
+      <c r="F82">
+        <v>79</v>
+      </c>
+      <c r="G82">
+        <v>122.15</v>
+      </c>
+      <c r="H82">
+        <v>1.79</v>
+      </c>
+      <c r="I82">
+        <v>18402</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A83">
+        <v>80</v>
+      </c>
+      <c r="B83">
+        <v>-280.36</v>
+      </c>
+      <c r="C83">
+        <v>-81.319999999999993</v>
+      </c>
+      <c r="D83">
+        <v>24671</v>
+      </c>
+      <c r="F83">
+        <v>80</v>
+      </c>
+      <c r="G83">
+        <v>126.27</v>
+      </c>
+      <c r="H83">
+        <v>1.9</v>
+      </c>
+      <c r="I83">
+        <v>18452</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A84">
+        <v>81</v>
+      </c>
+      <c r="B84">
+        <v>-283.95999999999998</v>
+      </c>
+      <c r="C84">
+        <v>-83.59</v>
+      </c>
+      <c r="D84">
+        <v>24721</v>
+      </c>
+      <c r="F84">
+        <v>81</v>
+      </c>
+      <c r="G84">
+        <v>130.24</v>
+      </c>
+      <c r="H84">
+        <v>2.02</v>
+      </c>
+      <c r="I84">
+        <v>18502</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A85">
+        <v>82</v>
+      </c>
+      <c r="B85">
+        <v>-286.35000000000002</v>
+      </c>
+      <c r="C85">
+        <v>-85.12</v>
+      </c>
+      <c r="D85">
+        <v>24771</v>
+      </c>
+      <c r="F85">
+        <v>82</v>
+      </c>
+      <c r="G85">
+        <v>134.22</v>
+      </c>
+      <c r="H85">
+        <v>2.15</v>
+      </c>
+      <c r="I85">
+        <v>18552</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A86">
+        <v>83</v>
+      </c>
+      <c r="B86">
+        <v>-289.79000000000002</v>
+      </c>
+      <c r="C86">
+        <v>-87.38</v>
+      </c>
+      <c r="D86">
+        <v>24821</v>
+      </c>
+      <c r="F86">
+        <v>83</v>
+      </c>
+      <c r="G86">
+        <v>137.91</v>
+      </c>
+      <c r="H86">
+        <v>2.29</v>
+      </c>
+      <c r="I86">
+        <v>18603</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A87">
+        <v>84</v>
+      </c>
+      <c r="B87">
+        <v>-292.14</v>
+      </c>
+      <c r="C87">
+        <v>-88.96</v>
+      </c>
+      <c r="D87">
+        <v>24871</v>
+      </c>
+      <c r="F87">
+        <v>84</v>
+      </c>
+      <c r="G87">
+        <v>142.6</v>
+      </c>
+      <c r="H87">
+        <v>2.5</v>
+      </c>
+      <c r="I87">
+        <v>18662</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A88">
+        <v>85</v>
+      </c>
+      <c r="B88">
+        <v>-295.54000000000002</v>
+      </c>
+      <c r="C88">
+        <v>-91.28</v>
+      </c>
+      <c r="D88">
+        <v>24922</v>
+      </c>
+      <c r="F88">
+        <v>85</v>
+      </c>
+      <c r="G88">
+        <v>146.43</v>
+      </c>
+      <c r="H88">
+        <v>2.69</v>
+      </c>
+      <c r="I88">
+        <v>18712</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A89">
+        <v>86</v>
+      </c>
+      <c r="B89">
+        <v>-297.87</v>
+      </c>
+      <c r="C89">
+        <v>-92.9</v>
+      </c>
+      <c r="D89">
+        <v>24972</v>
+      </c>
+      <c r="F89">
+        <v>86</v>
+      </c>
+      <c r="G89">
+        <v>150.54</v>
+      </c>
+      <c r="H89">
+        <v>2.9</v>
+      </c>
+      <c r="I89">
+        <v>18762</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="F90">
+        <v>87</v>
+      </c>
+      <c r="G90">
+        <v>154.80000000000001</v>
+      </c>
+      <c r="H90">
+        <v>3.15</v>
+      </c>
+      <c r="I90">
+        <v>18812</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="F91">
+        <v>88</v>
+      </c>
+      <c r="G91">
+        <v>158.91</v>
+      </c>
+      <c r="H91">
+        <v>3.41</v>
+      </c>
+      <c r="I91">
+        <v>18862</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="F92">
+        <v>89</v>
+      </c>
+      <c r="G92">
+        <v>163.16999999999999</v>
+      </c>
+      <c r="H92">
+        <v>3.7</v>
+      </c>
+      <c r="I92">
+        <v>18912</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="F93">
+        <v>90</v>
+      </c>
+      <c r="G93">
+        <v>167.56</v>
+      </c>
+      <c r="H93">
+        <v>4.01</v>
+      </c>
+      <c r="I93">
+        <v>18962</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="F94">
+        <v>91</v>
+      </c>
+      <c r="G94">
+        <v>171.53</v>
+      </c>
+      <c r="H94">
+        <v>4.32</v>
+      </c>
+      <c r="I94">
+        <v>19012</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="F95">
+        <v>92</v>
+      </c>
+      <c r="G95">
+        <v>175.77</v>
+      </c>
+      <c r="H95">
+        <v>4.67</v>
+      </c>
+      <c r="I95">
+        <v>19062</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="F96">
+        <v>93</v>
+      </c>
+      <c r="G96">
+        <v>180.16</v>
+      </c>
+      <c r="H96">
+        <v>5.05</v>
+      </c>
+      <c r="I96">
+        <v>19112</v>
+      </c>
+    </row>
+    <row r="97" spans="6:9" x14ac:dyDescent="0.35">
+      <c r="F97">
+        <v>94</v>
+      </c>
+      <c r="G97">
+        <v>184.55</v>
+      </c>
+      <c r="H97">
+        <v>5.47</v>
+      </c>
+      <c r="I97">
+        <v>19162</v>
+      </c>
+    </row>
+    <row r="98" spans="6:9" x14ac:dyDescent="0.35">
+      <c r="F98">
+        <v>95</v>
+      </c>
+      <c r="G98">
+        <v>188.93</v>
+      </c>
+      <c r="H98">
+        <v>5.92</v>
+      </c>
+      <c r="I98">
+        <v>19212</v>
+      </c>
+    </row>
+    <row r="99" spans="6:9" x14ac:dyDescent="0.35">
+      <c r="F99">
+        <v>96</v>
+      </c>
+      <c r="G99">
+        <v>193.03</v>
+      </c>
+      <c r="H99">
+        <v>6.35</v>
+      </c>
+      <c r="I99">
+        <v>19262</v>
+      </c>
+    </row>
+    <row r="100" spans="6:9" x14ac:dyDescent="0.35">
+      <c r="F100">
+        <v>97</v>
+      </c>
+      <c r="G100">
+        <v>197.27</v>
+      </c>
+      <c r="H100">
+        <v>6.81</v>
+      </c>
+      <c r="I100">
+        <v>19312</v>
+      </c>
+    </row>
+    <row r="101" spans="6:9" x14ac:dyDescent="0.35">
+      <c r="F101">
+        <v>98</v>
+      </c>
+      <c r="G101">
+        <v>201.36</v>
+      </c>
+      <c r="H101">
+        <v>7.27</v>
+      </c>
+      <c r="I101">
+        <v>19362</v>
+      </c>
+    </row>
+    <row r="102" spans="6:9" x14ac:dyDescent="0.35">
+      <c r="F102">
+        <v>99</v>
+      </c>
+      <c r="G102">
+        <v>205.73</v>
+      </c>
+      <c r="H102">
+        <v>7.81</v>
+      </c>
+      <c r="I102">
+        <v>19412</v>
+      </c>
+    </row>
+    <row r="103" spans="6:9" x14ac:dyDescent="0.35">
+      <c r="F103">
+        <v>100</v>
+      </c>
+      <c r="G103">
+        <v>209.82</v>
+      </c>
+      <c r="H103">
+        <v>8.34</v>
+      </c>
+      <c r="I103">
+        <v>19462</v>
+      </c>
+    </row>
+    <row r="104" spans="6:9" x14ac:dyDescent="0.35">
+      <c r="F104">
+        <v>101</v>
+      </c>
+      <c r="G104">
+        <v>214.18</v>
+      </c>
+      <c r="H104">
+        <v>8.9600000000000009</v>
+      </c>
+      <c r="I104">
+        <v>19512</v>
+      </c>
+    </row>
+    <row r="105" spans="6:9" x14ac:dyDescent="0.35">
+      <c r="F105">
+        <v>102</v>
+      </c>
+      <c r="G105">
+        <v>218.81</v>
+      </c>
+      <c r="H105">
+        <v>9.68</v>
+      </c>
+      <c r="I105">
+        <v>19562</v>
+      </c>
+    </row>
+    <row r="106" spans="6:9" x14ac:dyDescent="0.35">
+      <c r="F106">
+        <v>103</v>
+      </c>
+      <c r="G106">
+        <v>223.44</v>
+      </c>
+      <c r="H106">
+        <v>10.45</v>
+      </c>
+      <c r="I106">
+        <v>19612</v>
+      </c>
+    </row>
+    <row r="107" spans="6:9" x14ac:dyDescent="0.35">
+      <c r="F107">
+        <v>104</v>
+      </c>
+      <c r="G107">
+        <v>228.19</v>
+      </c>
+      <c r="H107">
+        <v>11.31</v>
+      </c>
+      <c r="I107">
+        <v>19662</v>
+      </c>
+    </row>
+    <row r="108" spans="6:9" x14ac:dyDescent="0.35">
+      <c r="F108">
+        <v>105</v>
+      </c>
+      <c r="G108">
+        <v>232.8</v>
+      </c>
+      <c r="H108">
+        <v>12.2</v>
+      </c>
+      <c r="I108">
+        <v>19713</v>
+      </c>
+    </row>
+    <row r="109" spans="6:9" x14ac:dyDescent="0.35">
+      <c r="F109">
+        <v>106</v>
+      </c>
+      <c r="G109">
+        <v>238.23</v>
+      </c>
+      <c r="H109">
+        <v>13.3</v>
+      </c>
+      <c r="I109">
+        <v>19772</v>
+      </c>
+    </row>
+    <row r="110" spans="6:9" x14ac:dyDescent="0.35">
+      <c r="F110">
+        <v>107</v>
+      </c>
+      <c r="G110">
+        <v>242.95</v>
+      </c>
+      <c r="H110">
+        <v>14.33</v>
+      </c>
+      <c r="I110">
+        <v>19822</v>
+      </c>
+    </row>
+    <row r="111" spans="6:9" x14ac:dyDescent="0.35">
+      <c r="F111">
+        <v>108</v>
+      </c>
+      <c r="G111">
+        <v>247.52</v>
+      </c>
+      <c r="H111">
+        <v>15.39</v>
+      </c>
+      <c r="I111">
+        <v>19872</v>
+      </c>
+    </row>
+    <row r="112" spans="6:9" x14ac:dyDescent="0.35">
+      <c r="F112">
+        <v>109</v>
+      </c>
+      <c r="G112">
+        <v>252.21</v>
+      </c>
+      <c r="H112">
+        <v>16.55</v>
+      </c>
+      <c r="I112">
+        <v>19922</v>
+      </c>
+    </row>
+    <row r="113" spans="6:9" x14ac:dyDescent="0.35">
+      <c r="F113">
+        <v>110</v>
+      </c>
+      <c r="G113">
+        <v>256.74</v>
+      </c>
+      <c r="H113">
+        <v>17.739999999999998</v>
+      </c>
+      <c r="I113">
+        <v>19972</v>
+      </c>
+    </row>
+    <row r="114" spans="6:9" x14ac:dyDescent="0.35">
+      <c r="F114">
+        <v>111</v>
+      </c>
+      <c r="G114">
+        <v>261.27</v>
+      </c>
+      <c r="H114">
+        <v>18.96</v>
+      </c>
+      <c r="I114">
+        <v>20022</v>
+      </c>
+    </row>
+    <row r="115" spans="6:9" x14ac:dyDescent="0.35">
+      <c r="F115">
+        <v>112</v>
+      </c>
+      <c r="G115">
+        <v>265.77999999999997</v>
+      </c>
+      <c r="H115">
+        <v>20.239999999999998</v>
+      </c>
+      <c r="I115">
+        <v>20072</v>
+      </c>
+    </row>
+    <row r="116" spans="6:9" x14ac:dyDescent="0.35">
+      <c r="F116">
+        <v>113</v>
+      </c>
+      <c r="G116">
+        <v>270.27</v>
+      </c>
+      <c r="H116">
+        <v>21.58</v>
+      </c>
+      <c r="I116">
+        <v>20122</v>
+      </c>
+    </row>
+    <row r="117" spans="6:9" x14ac:dyDescent="0.35">
+      <c r="F117">
+        <v>114</v>
+      </c>
+      <c r="G117">
+        <v>274.75</v>
+      </c>
+      <c r="H117">
+        <v>22.97</v>
+      </c>
+      <c r="I117">
+        <v>20172</v>
+      </c>
+    </row>
+    <row r="118" spans="6:9" x14ac:dyDescent="0.35">
+      <c r="F118">
+        <v>115</v>
+      </c>
+      <c r="G118">
+        <v>279.20999999999998</v>
+      </c>
+      <c r="H118">
+        <v>24.41</v>
+      </c>
+      <c r="I118">
+        <v>20222</v>
+      </c>
+    </row>
+    <row r="119" spans="6:9" x14ac:dyDescent="0.35">
+      <c r="F119">
+        <v>116</v>
+      </c>
+      <c r="G119">
+        <v>283.12</v>
+      </c>
+      <c r="H119">
+        <v>25.72</v>
+      </c>
+      <c r="I119">
+        <v>20272</v>
+      </c>
+    </row>
+    <row r="120" spans="6:9" x14ac:dyDescent="0.35">
+      <c r="F120">
+        <v>117</v>
+      </c>
+      <c r="G120">
+        <v>286.35000000000002</v>
+      </c>
+      <c r="H120">
+        <v>26.82</v>
+      </c>
+      <c r="I120">
+        <v>20322</v>
+      </c>
+    </row>
+    <row r="121" spans="6:9" x14ac:dyDescent="0.35">
+      <c r="F121">
+        <v>118</v>
+      </c>
+      <c r="G121">
+        <v>290.64</v>
+      </c>
+      <c r="H121">
+        <v>-627.02</v>
+      </c>
+      <c r="I121">
+        <v>20381</v>
+      </c>
+    </row>
+    <row r="122" spans="6:9" x14ac:dyDescent="0.35">
+      <c r="F122">
+        <v>119</v>
+      </c>
+      <c r="G122">
+        <v>291.17</v>
+      </c>
+      <c r="H122">
+        <v>-626.83000000000004</v>
+      </c>
+      <c r="I122">
+        <v>20432</v>
+      </c>
+    </row>
+    <row r="123" spans="6:9" x14ac:dyDescent="0.35">
+      <c r="F123">
+        <v>120</v>
+      </c>
+      <c r="G123">
+        <v>292.37</v>
+      </c>
+      <c r="H123">
+        <v>-626.39</v>
+      </c>
+      <c r="I123">
+        <v>20482</v>
+      </c>
+    </row>
+    <row r="124" spans="6:9" x14ac:dyDescent="0.35">
+      <c r="F124">
+        <v>121</v>
+      </c>
+      <c r="G124">
+        <v>295.44</v>
+      </c>
+      <c r="H124">
+        <v>-625.26</v>
+      </c>
+      <c r="I124">
+        <v>20532</v>
+      </c>
+    </row>
+    <row r="125" spans="6:9" x14ac:dyDescent="0.35">
+      <c r="F125">
+        <v>122</v>
+      </c>
+      <c r="G125">
+        <v>299.02</v>
+      </c>
+      <c r="H125">
+        <v>-623.89</v>
+      </c>
+      <c r="I125">
+        <v>20582</v>
+      </c>
+    </row>
+    <row r="126" spans="6:9" x14ac:dyDescent="0.35">
+      <c r="F126">
+        <v>123</v>
+      </c>
+      <c r="G126">
+        <v>302.99</v>
+      </c>
+      <c r="H126">
+        <v>-622.34</v>
+      </c>
+      <c r="I126">
+        <v>20632</v>
+      </c>
+    </row>
+    <row r="127" spans="6:9" x14ac:dyDescent="0.35">
+      <c r="F127">
+        <v>124</v>
+      </c>
+      <c r="G127">
+        <v>307.47000000000003</v>
+      </c>
+      <c r="H127">
+        <v>-620.53</v>
+      </c>
+      <c r="I127">
+        <v>20682</v>
+      </c>
+    </row>
+    <row r="128" spans="6:9" x14ac:dyDescent="0.35">
+      <c r="F128">
+        <v>125</v>
+      </c>
+      <c r="G128">
+        <v>311.8</v>
+      </c>
+      <c r="H128">
+        <v>-618.73</v>
+      </c>
+      <c r="I128">
+        <v>20732</v>
+      </c>
+    </row>
+    <row r="129" spans="6:9" x14ac:dyDescent="0.35">
+      <c r="F129">
+        <v>126</v>
+      </c>
+      <c r="G129">
+        <v>315.85000000000002</v>
+      </c>
+      <c r="H129">
+        <v>-617</v>
+      </c>
+      <c r="I129">
+        <v>20782</v>
+      </c>
+    </row>
+    <row r="130" spans="6:9" x14ac:dyDescent="0.35">
+      <c r="F130">
+        <v>127</v>
+      </c>
+      <c r="G130">
+        <v>319.5</v>
+      </c>
+      <c r="H130">
+        <v>-615.4</v>
+      </c>
+      <c r="I130">
+        <v>20832</v>
+      </c>
+    </row>
+    <row r="131" spans="6:9" x14ac:dyDescent="0.35">
+      <c r="F131">
+        <v>128</v>
+      </c>
+      <c r="G131">
+        <v>321.57</v>
+      </c>
+      <c r="H131">
+        <v>-614.48</v>
+      </c>
+      <c r="I131">
+        <v>20891</v>
+      </c>
+    </row>
+    <row r="132" spans="6:9" x14ac:dyDescent="0.35">
+      <c r="F132">
+        <v>129</v>
+      </c>
+      <c r="G132">
+        <v>321.83</v>
+      </c>
+      <c r="H132">
+        <v>-614.36</v>
+      </c>
+      <c r="I132">
+        <v>20942</v>
+      </c>
+    </row>
+    <row r="133" spans="6:9" x14ac:dyDescent="0.35">
+      <c r="F133">
+        <v>130</v>
+      </c>
+      <c r="G133">
+        <v>324.52999999999997</v>
+      </c>
+      <c r="H133">
+        <v>-613.08000000000004</v>
+      </c>
+      <c r="I133">
+        <v>20992</v>
+      </c>
+    </row>
+    <row r="134" spans="6:9" x14ac:dyDescent="0.35">
+      <c r="F134">
+        <v>131</v>
+      </c>
+      <c r="G134">
+        <v>325.42</v>
+      </c>
+      <c r="H134">
+        <v>-612.65</v>
+      </c>
+      <c r="I134">
+        <v>21051</v>
+      </c>
+    </row>
+    <row r="135" spans="6:9" x14ac:dyDescent="0.35">
+      <c r="F135">
+        <v>132</v>
+      </c>
+      <c r="G135">
+        <v>325.42</v>
+      </c>
+      <c r="H135">
+        <v>-612.65</v>
+      </c>
+      <c r="I135">
+        <v>21101</v>
+      </c>
+    </row>
+    <row r="136" spans="6:9" x14ac:dyDescent="0.35">
+      <c r="F136">
+        <v>133</v>
+      </c>
+      <c r="G136">
+        <v>325.42</v>
+      </c>
+      <c r="H136">
+        <v>-612.65</v>
+      </c>
+      <c r="I136">
+        <v>21151</v>
+      </c>
+    </row>
+    <row r="137" spans="6:9" x14ac:dyDescent="0.35">
+      <c r="F137">
+        <v>134</v>
+      </c>
+      <c r="G137">
+        <v>325.42</v>
+      </c>
+      <c r="H137">
+        <v>-612.65</v>
+      </c>
+      <c r="I137">
+        <v>21201</v>
+      </c>
+    </row>
+    <row r="138" spans="6:9" x14ac:dyDescent="0.35">
+      <c r="F138">
+        <v>135</v>
+      </c>
+      <c r="G138">
+        <v>325.42</v>
+      </c>
+      <c r="H138">
+        <v>-612.65</v>
+      </c>
+      <c r="I138">
+        <v>21251</v>
+      </c>
+    </row>
+    <row r="139" spans="6:9" x14ac:dyDescent="0.35">
+      <c r="F139">
+        <v>136</v>
+      </c>
+      <c r="G139">
+        <v>325.42</v>
+      </c>
+      <c r="H139">
+        <v>-612.65</v>
+      </c>
+      <c r="I139">
+        <v>21301</v>
+      </c>
+    </row>
+    <row r="140" spans="6:9" x14ac:dyDescent="0.35">
+      <c r="F140">
+        <v>137</v>
+      </c>
+      <c r="G140">
+        <v>325.42</v>
+      </c>
+      <c r="H140">
+        <v>-612.65</v>
+      </c>
+      <c r="I140">
+        <v>21351</v>
+      </c>
+    </row>
+    <row r="141" spans="6:9" x14ac:dyDescent="0.35">
+      <c r="F141">
+        <v>138</v>
+      </c>
+      <c r="G141">
+        <v>325.42</v>
+      </c>
+      <c r="H141">
+        <v>-612.65</v>
+      </c>
+      <c r="I141">
+        <v>21401</v>
+      </c>
+    </row>
+    <row r="142" spans="6:9" x14ac:dyDescent="0.35">
+      <c r="F142">
+        <v>139</v>
+      </c>
+      <c r="G142">
+        <v>325.42</v>
+      </c>
+      <c r="H142">
+        <v>-612.65</v>
+      </c>
+      <c r="I142">
+        <v>21451</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{547486A0-688D-4234-B917-99AF31B0D7E7}">
+  <dimension ref="A1:S104"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2" t="s">
+        <v>1</v>
+      </c>
+      <c r="H2" t="s">
+        <v>2</v>
+      </c>
+      <c r="I2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>0</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>17296</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>2.37</v>
+      </c>
+      <c r="H3">
+        <v>1.06</v>
+      </c>
+      <c r="I3">
+        <v>14406</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>17346</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>2.65</v>
+      </c>
+      <c r="H4">
+        <v>1.07</v>
+      </c>
+      <c r="I4">
+        <v>14456</v>
+      </c>
+      <c r="P4" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>1</v>
+      </c>
+      <c r="R4" t="s">
+        <v>2</v>
+      </c>
+      <c r="S4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>17397</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>2.65</v>
+      </c>
+      <c r="H5">
+        <v>1.07</v>
+      </c>
+      <c r="I5">
+        <v>14507</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>1.66</v>
+      </c>
+      <c r="R5">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="S5">
+        <v>14412</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>17447</v>
+      </c>
+      <c r="F6">
+        <v>3</v>
+      </c>
+      <c r="G6">
+        <v>2.65</v>
+      </c>
+      <c r="H6">
+        <v>1.07</v>
+      </c>
+      <c r="I6">
+        <v>14566</v>
+      </c>
+      <c r="P6">
+        <v>1</v>
+      </c>
+      <c r="Q6">
+        <v>1.66</v>
+      </c>
+      <c r="R6">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="S6">
+        <v>14462</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>4</v>
+      </c>
+      <c r="B7">
+        <v>-2.69</v>
+      </c>
+      <c r="C7">
+        <v>-0.03</v>
+      </c>
+      <c r="D7">
+        <v>17497</v>
+      </c>
+      <c r="F7">
+        <v>4</v>
+      </c>
+      <c r="G7">
+        <v>2.65</v>
+      </c>
+      <c r="H7">
+        <v>1.07</v>
+      </c>
+      <c r="I7">
+        <v>14616</v>
+      </c>
+      <c r="P7">
+        <v>2</v>
+      </c>
+      <c r="Q7">
+        <v>1.66</v>
+      </c>
+      <c r="R7">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="S7">
+        <v>14512</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>5</v>
+      </c>
+      <c r="B8">
+        <v>-5.38</v>
+      </c>
+      <c r="C8">
+        <v>-0.1</v>
+      </c>
+      <c r="D8">
+        <v>17547</v>
+      </c>
+      <c r="F8">
+        <v>5</v>
+      </c>
+      <c r="G8">
+        <v>2.65</v>
+      </c>
+      <c r="H8">
+        <v>1.07</v>
+      </c>
+      <c r="I8">
+        <v>14666</v>
+      </c>
+      <c r="P8">
+        <v>3</v>
+      </c>
+      <c r="Q8">
+        <v>1.66</v>
+      </c>
+      <c r="R8">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="S8">
+        <v>14562</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>6</v>
+      </c>
+      <c r="B9">
+        <v>-9.64</v>
+      </c>
+      <c r="C9">
+        <v>-0.23</v>
+      </c>
+      <c r="D9">
+        <v>17597</v>
+      </c>
+      <c r="F9">
+        <v>6</v>
+      </c>
+      <c r="G9">
+        <v>2.65</v>
+      </c>
+      <c r="H9">
+        <v>1.07</v>
+      </c>
+      <c r="I9">
+        <v>14716</v>
+      </c>
+      <c r="P9">
+        <v>4</v>
+      </c>
+      <c r="Q9">
+        <v>1.66</v>
+      </c>
+      <c r="R9">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="S9">
+        <v>14612</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>7</v>
+      </c>
+      <c r="B10">
+        <v>-12.19</v>
+      </c>
+      <c r="C10">
+        <v>-0.32</v>
+      </c>
+      <c r="D10">
+        <v>17647</v>
+      </c>
+      <c r="F10">
+        <v>7</v>
+      </c>
+      <c r="G10">
+        <v>2.65</v>
+      </c>
+      <c r="H10">
+        <v>1.07</v>
+      </c>
+      <c r="I10">
+        <v>14767</v>
+      </c>
+      <c r="P10">
+        <v>5</v>
+      </c>
+      <c r="Q10">
+        <v>1.66</v>
+      </c>
+      <c r="R10">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="S10">
+        <v>14662</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>8</v>
+      </c>
+      <c r="B11">
+        <v>-15.59</v>
+      </c>
+      <c r="C11">
+        <v>-0.46</v>
+      </c>
+      <c r="D11">
+        <v>17698</v>
+      </c>
+      <c r="F11">
+        <v>8</v>
+      </c>
+      <c r="G11">
+        <v>2.65</v>
+      </c>
+      <c r="H11">
+        <v>1.07</v>
+      </c>
+      <c r="I11">
+        <v>14826</v>
+      </c>
+      <c r="P11">
+        <v>6</v>
+      </c>
+      <c r="Q11">
+        <v>1.66</v>
+      </c>
+      <c r="R11">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="S11">
+        <v>14712</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>9</v>
+      </c>
+      <c r="B12">
+        <v>-18.14</v>
+      </c>
+      <c r="C12">
+        <v>-0.56999999999999995</v>
+      </c>
+      <c r="D12">
+        <v>17748</v>
+      </c>
+      <c r="F12">
+        <v>9</v>
+      </c>
+      <c r="G12">
+        <v>2.65</v>
+      </c>
+      <c r="H12">
+        <v>1.07</v>
+      </c>
+      <c r="I12">
+        <v>14876</v>
+      </c>
+      <c r="P12">
+        <v>7</v>
+      </c>
+      <c r="Q12">
+        <v>1.95</v>
+      </c>
+      <c r="R12">
+        <v>0.16</v>
+      </c>
+      <c r="S12">
+        <v>14764</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>10</v>
+      </c>
+      <c r="B13">
+        <v>-21.97</v>
+      </c>
+      <c r="C13">
+        <v>-0.77</v>
+      </c>
+      <c r="D13">
+        <v>17799</v>
+      </c>
+      <c r="F13">
+        <v>10</v>
+      </c>
+      <c r="G13">
+        <v>2.65</v>
+      </c>
+      <c r="H13">
+        <v>1.07</v>
+      </c>
+      <c r="I13">
+        <v>14926</v>
+      </c>
+      <c r="P13">
+        <v>8</v>
+      </c>
+      <c r="Q13">
+        <v>1.95</v>
+      </c>
+      <c r="R13">
+        <v>0.16</v>
+      </c>
+      <c r="S13">
+        <v>14823</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>11</v>
+      </c>
+      <c r="B14">
+        <v>-24.52</v>
+      </c>
+      <c r="C14">
+        <v>-0.93</v>
+      </c>
+      <c r="D14">
+        <v>17849</v>
+      </c>
+      <c r="F14">
+        <v>11</v>
+      </c>
+      <c r="G14">
+        <v>2.65</v>
+      </c>
+      <c r="H14">
+        <v>1.07</v>
+      </c>
+      <c r="I14">
+        <v>14977</v>
+      </c>
+      <c r="P14">
+        <v>9</v>
+      </c>
+      <c r="Q14">
+        <v>1.95</v>
+      </c>
+      <c r="R14">
+        <v>0.16</v>
+      </c>
+      <c r="S14">
+        <v>14873</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>12</v>
+      </c>
+      <c r="B15">
+        <v>-28.34</v>
+      </c>
+      <c r="C15">
+        <v>-1.17</v>
+      </c>
+      <c r="D15">
+        <v>17899</v>
+      </c>
+      <c r="F15">
+        <v>12</v>
+      </c>
+      <c r="G15">
+        <v>2.79</v>
+      </c>
+      <c r="H15">
+        <v>1.07</v>
+      </c>
+      <c r="I15">
+        <v>15036</v>
+      </c>
+      <c r="P15">
+        <v>10</v>
+      </c>
+      <c r="Q15">
+        <v>1.95</v>
+      </c>
+      <c r="R15">
+        <v>0.16</v>
+      </c>
+      <c r="S15">
+        <v>14923</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>13</v>
+      </c>
+      <c r="B16">
+        <v>-31.17</v>
+      </c>
+      <c r="C16">
+        <v>-1.37</v>
+      </c>
+      <c r="D16">
+        <v>17949</v>
+      </c>
+      <c r="F16">
+        <v>13</v>
+      </c>
+      <c r="G16">
+        <v>3.5</v>
+      </c>
+      <c r="H16">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="I16">
+        <v>15086</v>
+      </c>
+      <c r="P16">
+        <v>11</v>
+      </c>
+      <c r="Q16">
+        <v>1.95</v>
+      </c>
+      <c r="R16">
+        <v>0.16</v>
+      </c>
+      <c r="S16">
+        <v>14973</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>14</v>
+      </c>
+      <c r="B17">
+        <v>-35.130000000000003</v>
+      </c>
+      <c r="C17">
+        <v>-1.67</v>
+      </c>
+      <c r="D17">
+        <v>17999</v>
+      </c>
+      <c r="F17">
+        <v>14</v>
+      </c>
+      <c r="G17">
+        <v>4.92</v>
+      </c>
+      <c r="H17">
+        <v>1.22</v>
+      </c>
+      <c r="I17">
+        <v>15136</v>
+      </c>
+      <c r="P17">
+        <v>12</v>
+      </c>
+      <c r="Q17">
+        <v>1.95</v>
+      </c>
+      <c r="R17">
+        <v>0.16</v>
+      </c>
+      <c r="S17">
+        <v>15024</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>15</v>
+      </c>
+      <c r="B18">
+        <v>-37.82</v>
+      </c>
+      <c r="C18">
+        <v>-1.89</v>
+      </c>
+      <c r="D18">
+        <v>18049</v>
+      </c>
+      <c r="F18">
+        <v>15</v>
+      </c>
+      <c r="G18">
+        <v>7.18</v>
+      </c>
+      <c r="H18">
+        <v>1.46</v>
+      </c>
+      <c r="I18">
+        <v>15186</v>
+      </c>
+      <c r="P18">
+        <v>13</v>
+      </c>
+      <c r="Q18">
+        <v>1.95</v>
+      </c>
+      <c r="R18">
+        <v>0.16</v>
+      </c>
+      <c r="S18">
+        <v>15074</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>16</v>
+      </c>
+      <c r="B19">
+        <v>-41.63</v>
+      </c>
+      <c r="C19">
+        <v>-2.23</v>
+      </c>
+      <c r="D19">
+        <v>18099</v>
+      </c>
+      <c r="F19">
+        <v>16</v>
+      </c>
+      <c r="G19">
+        <v>10.29</v>
+      </c>
+      <c r="H19">
+        <v>1.82</v>
+      </c>
+      <c r="I19">
+        <v>15237</v>
+      </c>
+      <c r="P19">
+        <v>14</v>
+      </c>
+      <c r="Q19">
+        <v>1.95</v>
+      </c>
+      <c r="R19">
+        <v>0.16</v>
+      </c>
+      <c r="S19">
+        <v>15124</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>17</v>
+      </c>
+      <c r="B20">
+        <v>-44.18</v>
+      </c>
+      <c r="C20">
+        <v>-2.4700000000000002</v>
+      </c>
+      <c r="D20">
+        <v>18149</v>
+      </c>
+      <c r="F20">
+        <v>17</v>
+      </c>
+      <c r="G20">
+        <v>13.67</v>
+      </c>
+      <c r="H20">
+        <v>2.21</v>
+      </c>
+      <c r="I20">
+        <v>15296</v>
+      </c>
+      <c r="P20">
+        <v>15</v>
+      </c>
+      <c r="Q20">
+        <v>1.95</v>
+      </c>
+      <c r="R20">
+        <v>0.16</v>
+      </c>
+      <c r="S20">
+        <v>15174</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>18</v>
+      </c>
+      <c r="B21">
+        <v>-48.13</v>
+      </c>
+      <c r="C21">
+        <v>-2.86</v>
+      </c>
+      <c r="D21">
+        <v>18199</v>
+      </c>
+      <c r="F21">
+        <v>18</v>
+      </c>
+      <c r="G21">
+        <v>17.91</v>
+      </c>
+      <c r="H21">
+        <v>2.68</v>
+      </c>
+      <c r="I21">
+        <v>15346</v>
+      </c>
+      <c r="P21">
+        <v>16</v>
+      </c>
+      <c r="Q21">
+        <v>1.95</v>
+      </c>
+      <c r="R21">
+        <v>0.16</v>
+      </c>
+      <c r="S21">
+        <v>15224</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>19</v>
+      </c>
+      <c r="B22">
+        <v>-50.95</v>
+      </c>
+      <c r="C22">
+        <v>-3.16</v>
+      </c>
+      <c r="D22">
+        <v>18249</v>
+      </c>
+      <c r="F22">
+        <v>19</v>
+      </c>
+      <c r="G22">
+        <v>22.01</v>
+      </c>
+      <c r="H22">
+        <v>3.11</v>
+      </c>
+      <c r="I22">
+        <v>15396</v>
+      </c>
+      <c r="P22">
+        <v>17</v>
+      </c>
+      <c r="Q22">
+        <v>1.95</v>
+      </c>
+      <c r="R22">
+        <v>0.16</v>
+      </c>
+      <c r="S22">
+        <v>15275</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>20</v>
+      </c>
+      <c r="B23">
+        <v>-54.76</v>
+      </c>
+      <c r="C23">
+        <v>-3.59</v>
+      </c>
+      <c r="D23">
+        <v>18299</v>
+      </c>
+      <c r="F23">
+        <v>20</v>
+      </c>
+      <c r="G23">
+        <v>25.97</v>
+      </c>
+      <c r="H23">
+        <v>3.51</v>
+      </c>
+      <c r="I23">
+        <v>15447</v>
+      </c>
+      <c r="P23">
+        <v>18</v>
+      </c>
+      <c r="Q23">
+        <v>2.8</v>
+      </c>
+      <c r="R23">
+        <v>0.2</v>
+      </c>
+      <c r="S23">
+        <v>15334</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>21</v>
+      </c>
+      <c r="B24">
+        <v>-57.43</v>
+      </c>
+      <c r="C24">
+        <v>-3.91</v>
+      </c>
+      <c r="D24">
+        <v>18349</v>
+      </c>
+      <c r="F24">
+        <v>21</v>
+      </c>
+      <c r="G24">
+        <v>30.92</v>
+      </c>
+      <c r="H24">
+        <v>3.98</v>
+      </c>
+      <c r="I24">
+        <v>15506</v>
+      </c>
+      <c r="P24">
+        <v>19</v>
+      </c>
+      <c r="Q24">
+        <v>4.21</v>
+      </c>
+      <c r="R24">
+        <v>0.32</v>
+      </c>
+      <c r="S24">
+        <v>15384</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>22</v>
+      </c>
+      <c r="B25">
+        <v>-61.66</v>
+      </c>
+      <c r="C25">
+        <v>-4.43</v>
+      </c>
+      <c r="D25">
+        <v>18399</v>
+      </c>
+      <c r="F25">
+        <v>22</v>
+      </c>
+      <c r="G25">
+        <v>34.880000000000003</v>
+      </c>
+      <c r="H25">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="I25">
+        <v>15556</v>
+      </c>
+      <c r="P25">
+        <v>20</v>
+      </c>
+      <c r="Q25">
+        <v>6.47</v>
+      </c>
+      <c r="R25">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="S25">
+        <v>15435</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>23</v>
+      </c>
+      <c r="B26">
+        <v>-64.47</v>
+      </c>
+      <c r="C26">
+        <v>-4.8</v>
+      </c>
+      <c r="D26">
+        <v>18449</v>
+      </c>
+      <c r="F26">
+        <v>23</v>
+      </c>
+      <c r="G26">
+        <v>38.979999999999997</v>
+      </c>
+      <c r="H26">
+        <v>4.74</v>
+      </c>
+      <c r="I26">
+        <v>15606</v>
+      </c>
+      <c r="P26">
+        <v>21</v>
+      </c>
+      <c r="Q26">
+        <v>9.43</v>
+      </c>
+      <c r="R26">
+        <v>0.95</v>
+      </c>
+      <c r="S26">
+        <v>15485</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>24</v>
+      </c>
+      <c r="B27">
+        <v>-68.69</v>
+      </c>
+      <c r="C27">
+        <v>-5.38</v>
+      </c>
+      <c r="D27">
+        <v>18500</v>
+      </c>
+      <c r="F27">
+        <v>24</v>
+      </c>
+      <c r="G27">
+        <v>43.23</v>
+      </c>
+      <c r="H27">
+        <v>5.13</v>
+      </c>
+      <c r="I27">
+        <v>15656</v>
+      </c>
+      <c r="P27">
+        <v>22</v>
+      </c>
+      <c r="Q27">
+        <v>12.82</v>
+      </c>
+      <c r="R27">
+        <v>1.36</v>
+      </c>
+      <c r="S27">
+        <v>15536</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>25</v>
+      </c>
+      <c r="B28">
+        <v>-71.63</v>
+      </c>
+      <c r="C28">
+        <v>-5.81</v>
+      </c>
+      <c r="D28">
+        <v>18550</v>
+      </c>
+      <c r="F28">
+        <v>25</v>
+      </c>
+      <c r="G28">
+        <v>47.62</v>
+      </c>
+      <c r="H28">
+        <v>5.52</v>
+      </c>
+      <c r="I28">
+        <v>15707</v>
+      </c>
+      <c r="P28">
+        <v>23</v>
+      </c>
+      <c r="Q28">
+        <v>17.34</v>
+      </c>
+      <c r="R28">
+        <v>1.88</v>
+      </c>
+      <c r="S28">
+        <v>15595</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>26</v>
+      </c>
+      <c r="B29">
+        <v>-74.44</v>
+      </c>
+      <c r="C29">
+        <v>-6.24</v>
+      </c>
+      <c r="D29">
+        <v>18600</v>
+      </c>
+      <c r="F29">
+        <v>26</v>
+      </c>
+      <c r="G29">
+        <v>52.71</v>
+      </c>
+      <c r="H29">
+        <v>5.97</v>
+      </c>
+      <c r="I29">
+        <v>15766</v>
+      </c>
+      <c r="P29">
+        <v>24</v>
+      </c>
+      <c r="Q29">
+        <v>21.86</v>
+      </c>
+      <c r="R29">
+        <v>2.36</v>
+      </c>
+      <c r="S29">
+        <v>15654</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>27</v>
+      </c>
+      <c r="B30">
+        <v>-78.930000000000007</v>
+      </c>
+      <c r="C30">
+        <v>-6.94</v>
+      </c>
+      <c r="D30">
+        <v>18650</v>
+      </c>
+      <c r="F30">
+        <v>27</v>
+      </c>
+      <c r="G30">
+        <v>56.96</v>
+      </c>
+      <c r="H30">
+        <v>6.32</v>
+      </c>
+      <c r="I30">
+        <v>15816</v>
+      </c>
+      <c r="P30">
+        <v>25</v>
+      </c>
+      <c r="Q30">
+        <v>25.68</v>
+      </c>
+      <c r="R30">
+        <v>2.72</v>
+      </c>
+      <c r="S30">
+        <v>15705</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>28</v>
+      </c>
+      <c r="B31">
+        <v>-81.73</v>
+      </c>
+      <c r="C31">
+        <v>-7.39</v>
+      </c>
+      <c r="D31">
+        <v>18700</v>
+      </c>
+      <c r="F31">
+        <v>28</v>
+      </c>
+      <c r="G31">
+        <v>60.93</v>
+      </c>
+      <c r="H31">
+        <v>6.63</v>
+      </c>
+      <c r="I31">
+        <v>15866</v>
+      </c>
+      <c r="P31">
+        <v>26</v>
+      </c>
+      <c r="Q31">
+        <v>30.35</v>
+      </c>
+      <c r="R31">
+        <v>3.13</v>
+      </c>
+      <c r="S31">
+        <v>15764</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>29</v>
+      </c>
+      <c r="B32">
+        <v>-86.2</v>
+      </c>
+      <c r="C32">
+        <v>-8.15</v>
+      </c>
+      <c r="D32">
+        <v>18750</v>
+      </c>
+      <c r="F32">
+        <v>29</v>
+      </c>
+      <c r="G32">
+        <v>65.319999999999993</v>
+      </c>
+      <c r="H32">
+        <v>6.94</v>
+      </c>
+      <c r="I32">
+        <v>15917</v>
+      </c>
+      <c r="P32">
+        <v>27</v>
+      </c>
+      <c r="Q32">
+        <v>34.6</v>
+      </c>
+      <c r="R32">
+        <v>3.48</v>
+      </c>
+      <c r="S32">
+        <v>15814</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>30</v>
+      </c>
+      <c r="B33">
+        <v>-89</v>
+      </c>
+      <c r="C33">
+        <v>-8.64</v>
+      </c>
+      <c r="D33">
+        <v>18800</v>
+      </c>
+      <c r="F33">
+        <v>30</v>
+      </c>
+      <c r="G33">
+        <v>70.849999999999994</v>
+      </c>
+      <c r="H33">
+        <v>7.34</v>
+      </c>
+      <c r="I33">
+        <v>15976</v>
+      </c>
+      <c r="P33">
+        <v>28</v>
+      </c>
+      <c r="Q33">
+        <v>38.56</v>
+      </c>
+      <c r="R33">
+        <v>3.79</v>
+      </c>
+      <c r="S33">
+        <v>15864</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A34">
+        <v>31</v>
+      </c>
+      <c r="B34">
+        <v>-93.46</v>
+      </c>
+      <c r="C34">
+        <v>-9.4600000000000009</v>
+      </c>
+      <c r="D34">
+        <v>18851</v>
+      </c>
+      <c r="F34">
+        <v>31</v>
+      </c>
+      <c r="G34">
+        <v>75.239999999999995</v>
+      </c>
+      <c r="H34">
+        <v>7.65</v>
+      </c>
+      <c r="I34">
+        <v>16026</v>
+      </c>
+      <c r="P34">
+        <v>29</v>
+      </c>
+      <c r="Q34">
+        <v>42.53</v>
+      </c>
+      <c r="R34">
+        <v>4.08</v>
+      </c>
+      <c r="S34">
+        <v>15915</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A35">
+        <v>32</v>
+      </c>
+      <c r="B35">
+        <v>-97.78</v>
+      </c>
+      <c r="C35">
+        <v>-10.29</v>
+      </c>
+      <c r="D35">
+        <v>18902</v>
+      </c>
+      <c r="F35">
+        <v>32</v>
+      </c>
+      <c r="G35">
+        <v>79.64</v>
+      </c>
+      <c r="H35">
+        <v>7.95</v>
+      </c>
+      <c r="I35">
+        <v>16076</v>
+      </c>
+      <c r="P35">
+        <v>30</v>
+      </c>
+      <c r="Q35">
+        <v>47.49</v>
+      </c>
+      <c r="R35">
+        <v>4.42</v>
+      </c>
+      <c r="S35">
+        <v>15974</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A36">
+        <v>33</v>
+      </c>
+      <c r="B36">
+        <v>-100.84</v>
+      </c>
+      <c r="C36">
+        <v>-10.9</v>
+      </c>
+      <c r="D36">
+        <v>18952</v>
+      </c>
+      <c r="F36">
+        <v>33</v>
+      </c>
+      <c r="G36">
+        <v>84.31</v>
+      </c>
+      <c r="H36">
+        <v>8.27</v>
+      </c>
+      <c r="I36">
+        <v>16126</v>
+      </c>
+      <c r="P36">
+        <v>31</v>
+      </c>
+      <c r="Q36">
+        <v>51.89</v>
+      </c>
+      <c r="R36">
+        <v>4.7</v>
+      </c>
+      <c r="S36">
+        <v>16024</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A37">
+        <v>34</v>
+      </c>
+      <c r="B37">
+        <v>-105.29</v>
+      </c>
+      <c r="C37">
+        <v>-11.82</v>
+      </c>
+      <c r="D37">
+        <v>19002</v>
+      </c>
+      <c r="F37">
+        <v>34</v>
+      </c>
+      <c r="G37">
+        <v>88.57</v>
+      </c>
+      <c r="H37">
+        <v>8.57</v>
+      </c>
+      <c r="I37">
+        <v>16177</v>
+      </c>
+      <c r="P37">
+        <v>32</v>
+      </c>
+      <c r="Q37">
+        <v>56.29</v>
+      </c>
+      <c r="R37">
+        <v>4.96</v>
+      </c>
+      <c r="S37">
+        <v>16074</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A38">
+        <v>35</v>
+      </c>
+      <c r="B38">
+        <v>-108.2</v>
+      </c>
+      <c r="C38">
+        <v>-12.44</v>
+      </c>
+      <c r="D38">
+        <v>19052</v>
+      </c>
+      <c r="F38">
+        <v>35</v>
+      </c>
+      <c r="G38">
+        <v>93.95</v>
+      </c>
+      <c r="H38">
+        <v>8.94</v>
+      </c>
+      <c r="I38">
+        <v>16236</v>
+      </c>
+      <c r="P38">
+        <v>33</v>
+      </c>
+      <c r="Q38">
+        <v>60.54</v>
+      </c>
+      <c r="R38">
+        <v>5.22</v>
+      </c>
+      <c r="S38">
+        <v>16124</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A39">
+        <v>36</v>
+      </c>
+      <c r="B39">
+        <v>-112.77</v>
+      </c>
+      <c r="C39">
+        <v>-13.44</v>
+      </c>
+      <c r="D39">
+        <v>19102</v>
+      </c>
+      <c r="F39">
+        <v>36</v>
+      </c>
+      <c r="G39">
+        <v>98.63</v>
+      </c>
+      <c r="H39">
+        <v>9.26</v>
+      </c>
+      <c r="I39">
+        <v>16286</v>
+      </c>
+      <c r="P39">
+        <v>34</v>
+      </c>
+      <c r="Q39">
+        <v>64.94</v>
+      </c>
+      <c r="R39">
+        <v>5.48</v>
+      </c>
+      <c r="S39">
+        <v>16175</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A40">
+        <v>37</v>
+      </c>
+      <c r="B40">
+        <v>-115.82</v>
+      </c>
+      <c r="C40">
+        <v>-14.13</v>
+      </c>
+      <c r="D40">
+        <v>19152</v>
+      </c>
+      <c r="F40">
+        <v>37</v>
+      </c>
+      <c r="G40">
+        <v>103.17</v>
+      </c>
+      <c r="H40">
+        <v>9.59</v>
+      </c>
+      <c r="I40">
+        <v>16336</v>
+      </c>
+      <c r="P40">
+        <v>35</v>
+      </c>
+      <c r="Q40">
+        <v>70.05</v>
+      </c>
+      <c r="R40">
+        <v>5.74</v>
+      </c>
+      <c r="S40">
+        <v>16234</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A41">
+        <v>38</v>
+      </c>
+      <c r="B41">
+        <v>-120.24</v>
+      </c>
+      <c r="C41">
+        <v>-15.18</v>
+      </c>
+      <c r="D41">
+        <v>19202</v>
+      </c>
+      <c r="F41">
+        <v>38</v>
+      </c>
+      <c r="G41">
+        <v>107.84</v>
+      </c>
+      <c r="H41">
+        <v>9.94</v>
+      </c>
+      <c r="I41">
+        <v>16387</v>
+      </c>
+      <c r="P41">
+        <v>36</v>
+      </c>
+      <c r="Q41">
+        <v>74.59</v>
+      </c>
+      <c r="R41">
+        <v>5.97</v>
+      </c>
+      <c r="S41">
+        <v>16284</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A42">
+        <v>39</v>
+      </c>
+      <c r="B42">
+        <v>-123.54</v>
+      </c>
+      <c r="C42">
+        <v>-15.98</v>
+      </c>
+      <c r="D42">
+        <v>19252</v>
+      </c>
+      <c r="F42">
+        <v>39</v>
+      </c>
+      <c r="G42">
+        <v>113.51</v>
+      </c>
+      <c r="H42">
+        <v>10.38</v>
+      </c>
+      <c r="I42">
+        <v>16446</v>
+      </c>
+      <c r="P42">
+        <v>37</v>
+      </c>
+      <c r="Q42">
+        <v>79.27</v>
+      </c>
+      <c r="R42">
+        <v>6.2</v>
+      </c>
+      <c r="S42">
+        <v>16334</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A43">
+        <v>40</v>
+      </c>
+      <c r="B43">
+        <v>-128.08000000000001</v>
+      </c>
+      <c r="C43">
+        <v>-17.13</v>
+      </c>
+      <c r="D43">
+        <v>19302</v>
+      </c>
+      <c r="F43">
+        <v>40</v>
+      </c>
+      <c r="G43">
+        <v>117.9</v>
+      </c>
+      <c r="H43">
+        <v>10.72</v>
+      </c>
+      <c r="I43">
+        <v>16496</v>
+      </c>
+      <c r="P43">
+        <v>38</v>
+      </c>
+      <c r="Q43">
+        <v>83.82</v>
+      </c>
+      <c r="R43">
+        <v>6.41</v>
+      </c>
+      <c r="S43">
+        <v>16385</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A44">
+        <v>41</v>
+      </c>
+      <c r="B44">
+        <v>-131.38</v>
+      </c>
+      <c r="C44">
+        <v>-17.989999999999998</v>
+      </c>
+      <c r="D44">
+        <v>19352</v>
+      </c>
+      <c r="F44">
+        <v>41</v>
+      </c>
+      <c r="G44">
+        <v>122.58</v>
+      </c>
+      <c r="H44">
+        <v>11.1</v>
+      </c>
+      <c r="I44">
+        <v>16546</v>
+      </c>
+      <c r="P44">
+        <v>39</v>
+      </c>
+      <c r="Q44">
+        <v>89.07</v>
+      </c>
+      <c r="R44">
+        <v>6.64</v>
+      </c>
+      <c r="S44">
+        <v>16444</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A45">
+        <v>42</v>
+      </c>
+      <c r="B45">
+        <v>-136.04</v>
+      </c>
+      <c r="C45">
+        <v>-19.23</v>
+      </c>
+      <c r="D45">
+        <v>19402</v>
+      </c>
+      <c r="F45">
+        <v>42</v>
+      </c>
+      <c r="G45">
+        <v>127.39</v>
+      </c>
+      <c r="H45">
+        <v>11.49</v>
+      </c>
+      <c r="I45">
+        <v>16596</v>
+      </c>
+      <c r="P45">
+        <v>40</v>
+      </c>
+      <c r="Q45">
+        <v>93.18</v>
+      </c>
+      <c r="R45">
+        <v>6.83</v>
+      </c>
+      <c r="S45">
+        <v>16494</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A46">
+        <v>43</v>
+      </c>
+      <c r="B46">
+        <v>-139.05000000000001</v>
+      </c>
+      <c r="C46">
+        <v>-20.059999999999999</v>
+      </c>
+      <c r="D46">
+        <v>19452</v>
+      </c>
+      <c r="F46">
+        <v>43</v>
+      </c>
+      <c r="G46">
+        <v>132.21</v>
+      </c>
+      <c r="H46">
+        <v>11.88</v>
+      </c>
+      <c r="I46">
+        <v>16646</v>
+      </c>
+      <c r="P46">
+        <v>41</v>
+      </c>
+      <c r="Q46">
+        <v>97.87</v>
+      </c>
+      <c r="R46">
+        <v>7.05</v>
+      </c>
+      <c r="S46">
+        <v>16544</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A47">
+        <v>44</v>
+      </c>
+      <c r="B47">
+        <v>-143.69</v>
+      </c>
+      <c r="C47">
+        <v>-21.37</v>
+      </c>
+      <c r="D47">
+        <v>19502</v>
+      </c>
+      <c r="F47">
+        <v>44</v>
+      </c>
+      <c r="G47">
+        <v>136.74</v>
+      </c>
+      <c r="H47">
+        <v>12.26</v>
+      </c>
+      <c r="I47">
+        <v>16696</v>
+      </c>
+      <c r="P47">
+        <v>42</v>
+      </c>
+      <c r="Q47">
+        <v>102.41</v>
+      </c>
+      <c r="R47">
+        <v>7.25</v>
+      </c>
+      <c r="S47">
+        <v>16594</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A48">
+        <v>45</v>
+      </c>
+      <c r="B48">
+        <v>-146.83000000000001</v>
+      </c>
+      <c r="C48">
+        <v>-22.27</v>
+      </c>
+      <c r="D48">
+        <v>19552</v>
+      </c>
+      <c r="F48">
+        <v>45</v>
+      </c>
+      <c r="G48">
+        <v>141.41</v>
+      </c>
+      <c r="H48">
+        <v>12.67</v>
+      </c>
+      <c r="I48">
+        <v>16746</v>
+      </c>
+      <c r="P48">
+        <v>43</v>
+      </c>
+      <c r="Q48">
+        <v>106.95</v>
+      </c>
+      <c r="R48">
+        <v>7.45</v>
+      </c>
+      <c r="S48">
+        <v>16644</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A49">
+        <v>46</v>
+      </c>
+      <c r="B49">
+        <v>-150.09</v>
+      </c>
+      <c r="C49">
+        <v>-23.22</v>
+      </c>
+      <c r="D49">
+        <v>19602</v>
+      </c>
+      <c r="F49">
+        <v>46</v>
+      </c>
+      <c r="G49">
+        <v>146.22</v>
+      </c>
+      <c r="H49">
+        <v>13.09</v>
+      </c>
+      <c r="I49">
+        <v>16796</v>
+      </c>
+      <c r="P49">
+        <v>44</v>
+      </c>
+      <c r="Q49">
+        <v>111.64</v>
+      </c>
+      <c r="R49">
+        <v>7.66</v>
+      </c>
+      <c r="S49">
+        <v>16694</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A50">
+        <v>47</v>
+      </c>
+      <c r="B50">
+        <v>-154.71</v>
+      </c>
+      <c r="C50">
+        <v>-24.61</v>
+      </c>
+      <c r="D50">
+        <v>19652</v>
+      </c>
+      <c r="F50">
+        <v>47</v>
+      </c>
+      <c r="G50">
+        <v>151.03</v>
+      </c>
+      <c r="H50">
+        <v>13.51</v>
+      </c>
+      <c r="I50">
+        <v>16846</v>
+      </c>
+      <c r="P50">
+        <v>45</v>
+      </c>
+      <c r="Q50">
+        <v>116.46</v>
+      </c>
+      <c r="R50">
+        <v>7.89</v>
+      </c>
+      <c r="S50">
+        <v>16744</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A51">
+        <v>48</v>
+      </c>
+      <c r="B51">
+        <v>-157.83000000000001</v>
+      </c>
+      <c r="C51">
+        <v>-25.56</v>
+      </c>
+      <c r="D51">
+        <v>19702</v>
+      </c>
+      <c r="F51">
+        <v>48</v>
+      </c>
+      <c r="G51">
+        <v>155.85</v>
+      </c>
+      <c r="H51">
+        <v>13.95</v>
+      </c>
+      <c r="I51">
+        <v>16897</v>
+      </c>
+      <c r="P51">
+        <v>46</v>
+      </c>
+      <c r="Q51">
+        <v>121.15</v>
+      </c>
+      <c r="R51">
+        <v>8.1199999999999992</v>
+      </c>
+      <c r="S51">
+        <v>16794</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A52">
+        <v>49</v>
+      </c>
+      <c r="B52">
+        <v>-162.69999999999999</v>
+      </c>
+      <c r="C52">
+        <v>-27.1</v>
+      </c>
+      <c r="D52">
+        <v>19752</v>
+      </c>
+      <c r="F52">
+        <v>49</v>
+      </c>
+      <c r="G52">
+        <v>161.5</v>
+      </c>
+      <c r="H52">
+        <v>14.48</v>
+      </c>
+      <c r="I52">
+        <v>16956</v>
+      </c>
+      <c r="P52">
+        <v>47</v>
+      </c>
+      <c r="Q52">
+        <v>125.83</v>
+      </c>
+      <c r="R52">
+        <v>8.35</v>
+      </c>
+      <c r="S52">
+        <v>16844</v>
+      </c>
+    </row>
+    <row r="53" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A53">
+        <v>50</v>
+      </c>
+      <c r="B53">
+        <v>-165.67</v>
+      </c>
+      <c r="C53">
+        <v>-28.07</v>
+      </c>
+      <c r="D53">
+        <v>19802</v>
+      </c>
+      <c r="F53">
+        <v>50</v>
+      </c>
+      <c r="G53">
+        <v>166.46</v>
+      </c>
+      <c r="H53">
+        <v>14.94</v>
+      </c>
+      <c r="I53">
+        <v>17006</v>
+      </c>
+      <c r="P53">
+        <v>48</v>
+      </c>
+      <c r="Q53">
+        <v>130.37</v>
+      </c>
+      <c r="R53">
+        <v>8.56</v>
+      </c>
+      <c r="S53">
+        <v>16894</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A54">
+        <v>51</v>
+      </c>
+      <c r="B54">
+        <v>-170.38</v>
+      </c>
+      <c r="C54">
+        <v>-29.64</v>
+      </c>
+      <c r="D54">
+        <v>19852</v>
+      </c>
+      <c r="F54">
+        <v>51</v>
+      </c>
+      <c r="G54">
+        <v>171.41</v>
+      </c>
+      <c r="H54">
+        <v>15.39</v>
+      </c>
+      <c r="I54">
+        <v>17056</v>
+      </c>
+      <c r="P54">
+        <v>49</v>
+      </c>
+      <c r="Q54">
+        <v>135.19999999999999</v>
+      </c>
+      <c r="R54">
+        <v>8.7799999999999994</v>
+      </c>
+      <c r="S54">
+        <v>16944</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A55">
+        <v>52</v>
+      </c>
+      <c r="B55">
+        <v>-173.74</v>
+      </c>
+      <c r="C55">
+        <v>-30.78</v>
+      </c>
+      <c r="D55">
+        <v>19902</v>
+      </c>
+      <c r="F55">
+        <v>52</v>
+      </c>
+      <c r="G55">
+        <v>175.94</v>
+      </c>
+      <c r="H55">
+        <v>15.81</v>
+      </c>
+      <c r="I55">
+        <v>17106</v>
+      </c>
+      <c r="P55">
+        <v>50</v>
+      </c>
+      <c r="Q55">
+        <v>139.88</v>
+      </c>
+      <c r="R55">
+        <v>9</v>
+      </c>
+      <c r="S55">
+        <v>16994</v>
+      </c>
+    </row>
+    <row r="56" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A56">
+        <v>53</v>
+      </c>
+      <c r="B56">
+        <v>-178.56</v>
+      </c>
+      <c r="C56">
+        <v>-32.479999999999997</v>
+      </c>
+      <c r="D56">
+        <v>19952</v>
+      </c>
+      <c r="F56">
+        <v>53</v>
+      </c>
+      <c r="G56">
+        <v>180.46</v>
+      </c>
+      <c r="H56">
+        <v>16.239999999999998</v>
+      </c>
+      <c r="I56">
+        <v>17157</v>
+      </c>
+      <c r="P56">
+        <v>51</v>
+      </c>
+      <c r="Q56">
+        <v>144.41999999999999</v>
+      </c>
+      <c r="R56">
+        <v>9.23</v>
+      </c>
+      <c r="S56">
+        <v>17044</v>
+      </c>
+    </row>
+    <row r="57" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A57">
+        <v>54</v>
+      </c>
+      <c r="B57">
+        <v>-181.62</v>
+      </c>
+      <c r="C57">
+        <v>-33.590000000000003</v>
+      </c>
+      <c r="D57">
+        <v>20002</v>
+      </c>
+      <c r="F57">
+        <v>54</v>
+      </c>
+      <c r="G57">
+        <v>186.26</v>
+      </c>
+      <c r="H57">
+        <v>16.79</v>
+      </c>
+      <c r="I57">
+        <v>17216</v>
+      </c>
+      <c r="P57">
+        <v>52</v>
+      </c>
+      <c r="Q57">
+        <v>149.11000000000001</v>
+      </c>
+      <c r="R57">
+        <v>9.4700000000000006</v>
+      </c>
+      <c r="S57">
+        <v>17094</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A58">
+        <v>55</v>
+      </c>
+      <c r="B58">
+        <v>-186.55</v>
+      </c>
+      <c r="C58">
+        <v>-35.409999999999997</v>
+      </c>
+      <c r="D58">
+        <v>20052</v>
+      </c>
+      <c r="F58">
+        <v>55</v>
+      </c>
+      <c r="G58">
+        <v>191.07</v>
+      </c>
+      <c r="H58">
+        <v>17.260000000000002</v>
+      </c>
+      <c r="I58">
+        <v>17266</v>
+      </c>
+      <c r="P58">
+        <v>53</v>
+      </c>
+      <c r="Q58">
+        <v>153.93</v>
+      </c>
+      <c r="R58">
+        <v>9.73</v>
+      </c>
+      <c r="S58">
+        <v>17144</v>
+      </c>
+    </row>
+    <row r="59" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A59">
+        <v>56</v>
+      </c>
+      <c r="B59">
+        <v>-189.73</v>
+      </c>
+      <c r="C59">
+        <v>-36.61</v>
+      </c>
+      <c r="D59">
+        <v>20102</v>
+      </c>
+      <c r="F59">
+        <v>56</v>
+      </c>
+      <c r="G59">
+        <v>195.88</v>
+      </c>
+      <c r="H59">
+        <v>17.75</v>
+      </c>
+      <c r="I59">
+        <v>17316</v>
+      </c>
+      <c r="P59">
+        <v>54</v>
+      </c>
+      <c r="Q59">
+        <v>158.61000000000001</v>
+      </c>
+      <c r="R59">
+        <v>10.01</v>
+      </c>
+      <c r="S59">
+        <v>17195</v>
+      </c>
+    </row>
+    <row r="60" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A60">
+        <v>57</v>
+      </c>
+      <c r="B60">
+        <v>-194.63</v>
+      </c>
+      <c r="C60">
+        <v>-38.51</v>
+      </c>
+      <c r="D60">
+        <v>20152</v>
+      </c>
+      <c r="F60">
+        <v>57</v>
+      </c>
+      <c r="G60">
+        <v>200.4</v>
+      </c>
+      <c r="H60">
+        <v>18.190000000000001</v>
+      </c>
+      <c r="I60">
+        <v>17367</v>
+      </c>
+      <c r="P60">
+        <v>55</v>
+      </c>
+      <c r="Q60">
+        <v>164.42</v>
+      </c>
+      <c r="R60">
+        <v>10.41</v>
+      </c>
+      <c r="S60">
+        <v>17254</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A61">
+        <v>58</v>
+      </c>
+      <c r="B61">
+        <v>-197.8</v>
+      </c>
+      <c r="C61">
+        <v>-39.76</v>
+      </c>
+      <c r="D61">
+        <v>20202</v>
+      </c>
+      <c r="F61">
+        <v>58</v>
+      </c>
+      <c r="G61">
+        <v>205.63</v>
+      </c>
+      <c r="H61">
+        <v>18.72</v>
+      </c>
+      <c r="I61">
+        <v>17426</v>
+      </c>
+      <c r="P61">
+        <v>56</v>
+      </c>
+      <c r="Q61">
+        <v>169.24</v>
+      </c>
+      <c r="R61">
+        <v>10.76</v>
+      </c>
+      <c r="S61">
+        <v>17304</v>
+      </c>
+    </row>
+    <row r="62" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A62">
+        <v>59</v>
+      </c>
+      <c r="B62">
+        <v>-202.67</v>
+      </c>
+      <c r="C62">
+        <v>-41.71</v>
+      </c>
+      <c r="D62">
+        <v>20252</v>
+      </c>
+      <c r="F62">
+        <v>59</v>
+      </c>
+      <c r="G62">
+        <v>210.29</v>
+      </c>
+      <c r="H62">
+        <v>19.239999999999998</v>
+      </c>
+      <c r="I62">
+        <v>17476</v>
+      </c>
+      <c r="P62">
+        <v>57</v>
+      </c>
+      <c r="Q62">
+        <v>174.06</v>
+      </c>
+      <c r="R62">
+        <v>11.14</v>
+      </c>
+      <c r="S62">
+        <v>17354</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A63">
+        <v>60</v>
+      </c>
+      <c r="B63">
+        <v>-205.95</v>
+      </c>
+      <c r="C63">
+        <v>-43.05</v>
+      </c>
+      <c r="D63">
+        <v>20302</v>
+      </c>
+      <c r="F63">
+        <v>60</v>
+      </c>
+      <c r="G63">
+        <v>215.09</v>
+      </c>
+      <c r="H63">
+        <v>19.809999999999999</v>
+      </c>
+      <c r="I63">
+        <v>17526</v>
+      </c>
+      <c r="P63">
+        <v>58</v>
+      </c>
+      <c r="Q63">
+        <v>178.87</v>
+      </c>
+      <c r="R63">
+        <v>11.55</v>
+      </c>
+      <c r="S63">
+        <v>17404</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A64">
+        <v>61</v>
+      </c>
+      <c r="B64">
+        <v>-210.79</v>
+      </c>
+      <c r="C64">
+        <v>-45.09</v>
+      </c>
+      <c r="D64">
+        <v>20352</v>
+      </c>
+      <c r="F64">
+        <v>61</v>
+      </c>
+      <c r="G64">
+        <v>219.89</v>
+      </c>
+      <c r="H64">
+        <v>20.39</v>
+      </c>
+      <c r="I64">
+        <v>17576</v>
+      </c>
+      <c r="P64">
+        <v>59</v>
+      </c>
+      <c r="Q64">
+        <v>183.68</v>
+      </c>
+      <c r="R64">
+        <v>11.99</v>
+      </c>
+      <c r="S64">
+        <v>17455</v>
+      </c>
+    </row>
+    <row r="65" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A65">
+        <v>62</v>
+      </c>
+      <c r="B65">
+        <v>-214.05</v>
+      </c>
+      <c r="C65">
+        <v>-46.49</v>
+      </c>
+      <c r="D65">
+        <v>20403</v>
+      </c>
+      <c r="F65">
+        <v>62</v>
+      </c>
+      <c r="G65">
+        <v>224.68</v>
+      </c>
+      <c r="H65">
+        <v>20.99</v>
+      </c>
+      <c r="I65">
+        <v>17627</v>
+      </c>
+      <c r="P65">
+        <v>60</v>
+      </c>
+      <c r="Q65">
+        <v>189.62</v>
+      </c>
+      <c r="R65">
+        <v>12.57</v>
+      </c>
+      <c r="S65">
+        <v>17514</v>
+      </c>
+    </row>
+    <row r="66" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A66">
+        <v>63</v>
+      </c>
+      <c r="B66">
+        <v>-218.85</v>
+      </c>
+      <c r="C66">
+        <v>-48.61</v>
+      </c>
+      <c r="D66">
+        <v>20453</v>
+      </c>
+      <c r="F66">
+        <v>63</v>
+      </c>
+      <c r="G66">
+        <v>230.6</v>
+      </c>
+      <c r="H66">
+        <v>21.77</v>
+      </c>
+      <c r="I66">
+        <v>17686</v>
+      </c>
+      <c r="P66">
+        <v>61</v>
+      </c>
+      <c r="Q66">
+        <v>194.15</v>
+      </c>
+      <c r="R66">
+        <v>13.04</v>
+      </c>
+      <c r="S66">
+        <v>17564</v>
+      </c>
+    </row>
+    <row r="67" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A67">
+        <v>64</v>
+      </c>
+      <c r="B67">
+        <v>-222.09</v>
+      </c>
+      <c r="C67">
+        <v>-50.06</v>
+      </c>
+      <c r="D67">
+        <v>20503</v>
+      </c>
+      <c r="F67">
+        <v>64</v>
+      </c>
+      <c r="G67">
+        <v>235.67</v>
+      </c>
+      <c r="H67">
+        <v>22.45</v>
+      </c>
+      <c r="I67">
+        <v>17736</v>
+      </c>
+      <c r="P67">
+        <v>62</v>
+      </c>
+      <c r="Q67">
+        <v>198.81</v>
+      </c>
+      <c r="R67">
+        <v>13.55</v>
+      </c>
+      <c r="S67">
+        <v>17614</v>
+      </c>
+    </row>
+    <row r="68" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A68">
+        <v>65</v>
+      </c>
+      <c r="B68">
+        <v>-226.86</v>
+      </c>
+      <c r="C68">
+        <v>-52.24</v>
+      </c>
+      <c r="D68">
+        <v>20553</v>
+      </c>
+      <c r="F68">
+        <v>65</v>
+      </c>
+      <c r="G68">
+        <v>240.59</v>
+      </c>
+      <c r="H68">
+        <v>23.14</v>
+      </c>
+      <c r="I68">
+        <v>17786</v>
+      </c>
+      <c r="P68">
+        <v>63</v>
+      </c>
+      <c r="Q68">
+        <v>203.47</v>
+      </c>
+      <c r="R68">
+        <v>14.08</v>
+      </c>
+      <c r="S68">
+        <v>17665</v>
+      </c>
+    </row>
+    <row r="69" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A69">
+        <v>66</v>
+      </c>
+      <c r="B69">
+        <v>-230.07</v>
+      </c>
+      <c r="C69">
+        <v>-53.74</v>
+      </c>
+      <c r="D69">
+        <v>20603</v>
+      </c>
+      <c r="F69">
+        <v>66</v>
+      </c>
+      <c r="G69">
+        <v>245.52</v>
+      </c>
+      <c r="H69">
+        <v>23.84</v>
+      </c>
+      <c r="I69">
+        <v>17837</v>
+      </c>
+      <c r="P69">
+        <v>64</v>
+      </c>
+      <c r="Q69">
+        <v>208.96</v>
+      </c>
+      <c r="R69">
+        <v>14.79</v>
+      </c>
+      <c r="S69">
+        <v>17724</v>
+      </c>
+    </row>
+    <row r="70" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A70">
+        <v>67</v>
+      </c>
+      <c r="B70">
+        <v>-235.06</v>
+      </c>
+      <c r="C70">
+        <v>-56.13</v>
+      </c>
+      <c r="D70">
+        <v>20654</v>
+      </c>
+      <c r="F70">
+        <v>67</v>
+      </c>
+      <c r="G70">
+        <v>251.28</v>
+      </c>
+      <c r="H70">
+        <v>24.68</v>
+      </c>
+      <c r="I70">
+        <v>17896</v>
+      </c>
+      <c r="P70">
+        <v>65</v>
+      </c>
+      <c r="Q70">
+        <v>213.75</v>
+      </c>
+      <c r="R70">
+        <v>15.47</v>
+      </c>
+      <c r="S70">
+        <v>17774</v>
+      </c>
+    </row>
+    <row r="71" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A71">
+        <v>68</v>
+      </c>
+      <c r="B71">
+        <v>-238.25</v>
+      </c>
+      <c r="C71">
+        <v>-57.68</v>
+      </c>
+      <c r="D71">
+        <v>20704</v>
+      </c>
+      <c r="F71">
+        <v>68</v>
+      </c>
+      <c r="G71">
+        <v>256.33999999999997</v>
+      </c>
+      <c r="H71">
+        <v>25.44</v>
+      </c>
+      <c r="I71">
+        <v>17946</v>
+      </c>
+      <c r="P71">
+        <v>66</v>
+      </c>
+      <c r="Q71">
+        <v>218.24</v>
+      </c>
+      <c r="R71">
+        <v>16.14</v>
+      </c>
+      <c r="S71">
+        <v>17824</v>
+      </c>
+    </row>
+    <row r="72" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A72">
+        <v>69</v>
+      </c>
+      <c r="B72">
+        <v>-243.08</v>
+      </c>
+      <c r="C72">
+        <v>-60.07</v>
+      </c>
+      <c r="D72">
+        <v>20754</v>
+      </c>
+      <c r="F72">
+        <v>69</v>
+      </c>
+      <c r="G72">
+        <v>261.12</v>
+      </c>
+      <c r="H72">
+        <v>26.15</v>
+      </c>
+      <c r="I72">
+        <v>17996</v>
+      </c>
+      <c r="P72">
+        <v>67</v>
+      </c>
+      <c r="Q72">
+        <v>223.86</v>
+      </c>
+      <c r="R72">
+        <v>17.02</v>
+      </c>
+      <c r="S72">
+        <v>17883</v>
+      </c>
+    </row>
+    <row r="73" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A73">
+        <v>70</v>
+      </c>
+      <c r="B73">
+        <v>-246.38</v>
+      </c>
+      <c r="C73">
+        <v>-61.73</v>
+      </c>
+      <c r="D73">
+        <v>20804</v>
+      </c>
+      <c r="F73">
+        <v>70</v>
+      </c>
+      <c r="G73">
+        <v>265.62</v>
+      </c>
+      <c r="H73">
+        <v>26.82</v>
+      </c>
+      <c r="I73">
+        <v>18046</v>
+      </c>
+      <c r="P73">
+        <v>68</v>
+      </c>
+      <c r="Q73">
+        <v>228.63</v>
+      </c>
+      <c r="R73">
+        <v>17.79</v>
+      </c>
+      <c r="S73">
+        <v>17933</v>
+      </c>
+    </row>
+    <row r="74" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A74">
+        <v>71</v>
+      </c>
+      <c r="B74">
+        <v>-251.3</v>
+      </c>
+      <c r="C74">
+        <v>-64.260000000000005</v>
+      </c>
+      <c r="D74">
+        <v>20854</v>
+      </c>
+      <c r="F74">
+        <v>71</v>
+      </c>
+      <c r="G74">
+        <v>270.39999999999998</v>
+      </c>
+      <c r="H74">
+        <v>27.54</v>
+      </c>
+      <c r="I74">
+        <v>18097</v>
+      </c>
+      <c r="P74">
+        <v>69</v>
+      </c>
+      <c r="Q74">
+        <v>233.81</v>
+      </c>
+      <c r="R74">
+        <v>18.670000000000002</v>
+      </c>
+      <c r="S74">
+        <v>17983</v>
+      </c>
+    </row>
+    <row r="75" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A75">
+        <v>72</v>
+      </c>
+      <c r="B75">
+        <v>-254.57</v>
+      </c>
+      <c r="C75">
+        <v>-65.97</v>
+      </c>
+      <c r="D75">
+        <v>20904</v>
+      </c>
+      <c r="F75">
+        <v>72</v>
+      </c>
+      <c r="G75">
+        <v>276.14999999999998</v>
+      </c>
+      <c r="H75">
+        <v>-626.92999999999995</v>
+      </c>
+      <c r="I75">
+        <v>18155</v>
+      </c>
+      <c r="P75">
+        <v>70</v>
+      </c>
+      <c r="Q75">
+        <v>238.85</v>
+      </c>
+      <c r="R75">
+        <v>19.57</v>
+      </c>
+      <c r="S75">
+        <v>18033</v>
+      </c>
+    </row>
+    <row r="76" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A76">
+        <v>73</v>
+      </c>
+      <c r="B76">
+        <v>-259.45</v>
+      </c>
+      <c r="C76">
+        <v>-68.569999999999993</v>
+      </c>
+      <c r="D76">
+        <v>20954</v>
+      </c>
+      <c r="F76">
+        <v>73</v>
+      </c>
+      <c r="G76">
+        <v>281.33999999999997</v>
+      </c>
+      <c r="H76">
+        <v>-626.08000000000004</v>
+      </c>
+      <c r="I76">
+        <v>18205</v>
+      </c>
+      <c r="P76">
+        <v>71</v>
+      </c>
+      <c r="Q76">
+        <v>243.6</v>
+      </c>
+      <c r="R76">
+        <v>20.45</v>
+      </c>
+      <c r="S76">
+        <v>18083</v>
+      </c>
+    </row>
+    <row r="77" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A77">
+        <v>74</v>
+      </c>
+      <c r="B77">
+        <v>-262.44</v>
+      </c>
+      <c r="C77">
+        <v>-70.2</v>
+      </c>
+      <c r="D77">
+        <v>21004</v>
+      </c>
+      <c r="F77">
+        <v>74</v>
+      </c>
+      <c r="G77">
+        <v>286.94</v>
+      </c>
+      <c r="H77">
+        <v>-625.1</v>
+      </c>
+      <c r="I77">
+        <v>18255</v>
+      </c>
+      <c r="P77">
+        <v>72</v>
+      </c>
+      <c r="Q77">
+        <v>248.34</v>
+      </c>
+      <c r="R77">
+        <v>21.37</v>
+      </c>
+      <c r="S77">
+        <v>18134</v>
+      </c>
+    </row>
+    <row r="78" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A78">
+        <v>75</v>
+      </c>
+      <c r="B78">
+        <v>-265.79000000000002</v>
+      </c>
+      <c r="C78">
+        <v>-72.069999999999993</v>
+      </c>
+      <c r="D78">
+        <v>21054</v>
+      </c>
+      <c r="F78">
+        <v>75</v>
+      </c>
+      <c r="G78">
+        <v>291.95999999999998</v>
+      </c>
+      <c r="H78">
+        <v>-624.14</v>
+      </c>
+      <c r="I78">
+        <v>18306</v>
+      </c>
+      <c r="P78">
+        <v>73</v>
+      </c>
+      <c r="Q78">
+        <v>254.18</v>
+      </c>
+      <c r="R78">
+        <v>22.61</v>
+      </c>
+      <c r="S78">
+        <v>18193</v>
+      </c>
+    </row>
+    <row r="79" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A79">
+        <v>76</v>
+      </c>
+      <c r="B79">
+        <v>-268.13</v>
+      </c>
+      <c r="C79">
+        <v>-73.400000000000006</v>
+      </c>
+      <c r="D79">
+        <v>21104</v>
+      </c>
+      <c r="F79">
+        <v>76</v>
+      </c>
+      <c r="G79">
+        <v>297.52999999999997</v>
+      </c>
+      <c r="H79">
+        <v>-623.01</v>
+      </c>
+      <c r="I79">
+        <v>18364</v>
+      </c>
+      <c r="P79">
+        <v>74</v>
+      </c>
+      <c r="Q79">
+        <v>259.17</v>
+      </c>
+      <c r="R79">
+        <v>23.72</v>
+      </c>
+      <c r="S79">
+        <v>18243</v>
+      </c>
+    </row>
+    <row r="80" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A80">
+        <v>77</v>
+      </c>
+      <c r="B80">
+        <v>-271.68</v>
+      </c>
+      <c r="C80">
+        <v>-75.47</v>
+      </c>
+      <c r="D80">
+        <v>21154</v>
+      </c>
+      <c r="F80">
+        <v>77</v>
+      </c>
+      <c r="G80">
+        <v>301.98</v>
+      </c>
+      <c r="H80">
+        <v>-622.04</v>
+      </c>
+      <c r="I80">
+        <v>18414</v>
+      </c>
+      <c r="P80">
+        <v>75</v>
+      </c>
+      <c r="Q80">
+        <v>264.01</v>
+      </c>
+      <c r="R80">
+        <v>24.86</v>
+      </c>
+      <c r="S80">
+        <v>18293</v>
+      </c>
+    </row>
+    <row r="81" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A81">
+        <v>78</v>
+      </c>
+      <c r="B81">
+        <v>-274</v>
+      </c>
+      <c r="C81">
+        <v>-76.849999999999994</v>
+      </c>
+      <c r="D81">
+        <v>21204</v>
+      </c>
+      <c r="F81">
+        <v>78</v>
+      </c>
+      <c r="G81">
+        <v>306.95999999999998</v>
+      </c>
+      <c r="H81">
+        <v>-620.88</v>
+      </c>
+      <c r="I81">
+        <v>18464</v>
+      </c>
+      <c r="P81">
+        <v>76</v>
+      </c>
+      <c r="Q81">
+        <v>268.83999999999997</v>
+      </c>
+      <c r="R81">
+        <v>26.05</v>
+      </c>
+      <c r="S81">
+        <v>18343</v>
+      </c>
+    </row>
+    <row r="82" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A82">
+        <v>79</v>
+      </c>
+      <c r="B82">
+        <v>-277.39999999999998</v>
+      </c>
+      <c r="C82">
+        <v>-78.900000000000006</v>
+      </c>
+      <c r="D82">
+        <v>21254</v>
+      </c>
+      <c r="F82">
+        <v>79</v>
+      </c>
+      <c r="G82">
+        <v>311.77999999999997</v>
+      </c>
+      <c r="H82">
+        <v>-619.66</v>
+      </c>
+      <c r="I82">
+        <v>18514</v>
+      </c>
+      <c r="P82">
+        <v>77</v>
+      </c>
+      <c r="Q82">
+        <v>273.79000000000002</v>
+      </c>
+      <c r="R82">
+        <v>27.33</v>
+      </c>
+      <c r="S82">
+        <v>18393</v>
+      </c>
+    </row>
+    <row r="83" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A83">
+        <v>80</v>
+      </c>
+      <c r="B83">
+        <v>-279.82</v>
+      </c>
+      <c r="C83">
+        <v>-80.39</v>
+      </c>
+      <c r="D83">
+        <v>21304</v>
+      </c>
+      <c r="F83">
+        <v>80</v>
+      </c>
+      <c r="G83">
+        <v>317.39</v>
+      </c>
+      <c r="H83">
+        <v>-618.11</v>
+      </c>
+      <c r="I83">
+        <v>18573</v>
+      </c>
+      <c r="P83">
+        <v>78</v>
+      </c>
+      <c r="Q83">
+        <v>278.45</v>
+      </c>
+      <c r="R83">
+        <v>-626.76</v>
+      </c>
+      <c r="S83">
+        <v>18443</v>
+      </c>
+    </row>
+    <row r="84" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A84">
+        <v>81</v>
+      </c>
+      <c r="B84">
+        <v>-283.3</v>
+      </c>
+      <c r="C84">
+        <v>-82.58</v>
+      </c>
+      <c r="D84">
+        <v>21354</v>
+      </c>
+      <c r="F84">
+        <v>81</v>
+      </c>
+      <c r="G84">
+        <v>320.8</v>
+      </c>
+      <c r="H84">
+        <v>-617.1</v>
+      </c>
+      <c r="I84">
+        <v>18623</v>
+      </c>
+      <c r="P84">
+        <v>79</v>
+      </c>
+      <c r="Q84">
+        <v>283.24</v>
+      </c>
+      <c r="R84">
+        <v>-625.4</v>
+      </c>
+      <c r="S84">
+        <v>18493</v>
+      </c>
+    </row>
+    <row r="85" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A85">
+        <v>82</v>
+      </c>
+      <c r="B85">
+        <v>-285.69</v>
+      </c>
+      <c r="C85">
+        <v>-84.11</v>
+      </c>
+      <c r="D85">
+        <v>21404</v>
+      </c>
+      <c r="F85">
+        <v>82</v>
+      </c>
+      <c r="G85">
+        <v>321.07</v>
+      </c>
+      <c r="H85">
+        <v>-617.02</v>
+      </c>
+      <c r="I85">
+        <v>18673</v>
+      </c>
+      <c r="P85">
+        <v>80</v>
+      </c>
+      <c r="Q85">
+        <v>288.27999999999997</v>
+      </c>
+      <c r="R85">
+        <v>-623.91</v>
+      </c>
+      <c r="S85">
+        <v>18543</v>
+      </c>
+    </row>
+    <row r="86" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A86">
+        <v>83</v>
+      </c>
+      <c r="B86">
+        <v>-289.26</v>
+      </c>
+      <c r="C86">
+        <v>-86.43</v>
+      </c>
+      <c r="D86">
+        <v>21454</v>
+      </c>
+      <c r="F86">
+        <v>83</v>
+      </c>
+      <c r="G86">
+        <v>321.07</v>
+      </c>
+      <c r="H86">
+        <v>-617.02</v>
+      </c>
+      <c r="I86">
+        <v>18723</v>
+      </c>
+      <c r="P86">
+        <v>81</v>
+      </c>
+      <c r="Q86">
+        <v>292.89</v>
+      </c>
+      <c r="R86">
+        <v>-622.48</v>
+      </c>
+      <c r="S86">
+        <v>18593</v>
+      </c>
+    </row>
+    <row r="87" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A87">
+        <v>84</v>
+      </c>
+      <c r="B87">
+        <v>-291.61</v>
+      </c>
+      <c r="C87">
+        <v>-88.01</v>
+      </c>
+      <c r="D87">
+        <v>21504</v>
+      </c>
+      <c r="F87">
+        <v>84</v>
+      </c>
+      <c r="G87">
+        <v>321.07</v>
+      </c>
+      <c r="H87">
+        <v>-617.02</v>
+      </c>
+      <c r="I87">
+        <v>18774</v>
+      </c>
+      <c r="P87">
+        <v>82</v>
+      </c>
+      <c r="Q87">
+        <v>297.63</v>
+      </c>
+      <c r="R87">
+        <v>-620.96</v>
+      </c>
+      <c r="S87">
+        <v>18643</v>
+      </c>
+    </row>
+    <row r="88" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A88">
+        <v>85</v>
+      </c>
+      <c r="B88">
+        <v>-295.14</v>
+      </c>
+      <c r="C88">
+        <v>-90.4</v>
+      </c>
+      <c r="D88">
+        <v>21555</v>
+      </c>
+      <c r="F88">
+        <v>85</v>
+      </c>
+      <c r="G88">
+        <v>321.07</v>
+      </c>
+      <c r="H88">
+        <v>-617.02</v>
+      </c>
+      <c r="I88">
+        <v>18833</v>
+      </c>
+      <c r="P88">
+        <v>83</v>
+      </c>
+      <c r="Q88">
+        <v>303.14999999999998</v>
+      </c>
+      <c r="R88">
+        <v>-619.09</v>
+      </c>
+      <c r="S88">
+        <v>18702</v>
+      </c>
+    </row>
+    <row r="89" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A89">
+        <v>86</v>
+      </c>
+      <c r="B89">
+        <v>-297.47000000000003</v>
+      </c>
+      <c r="C89">
+        <v>-92.01</v>
+      </c>
+      <c r="D89">
+        <v>21605</v>
+      </c>
+      <c r="F89">
+        <v>86</v>
+      </c>
+      <c r="G89">
+        <v>321.07</v>
+      </c>
+      <c r="H89">
+        <v>-617.02</v>
+      </c>
+      <c r="I89">
+        <v>18883</v>
+      </c>
+      <c r="P89">
+        <v>84</v>
+      </c>
+      <c r="Q89">
+        <v>307.7</v>
+      </c>
+      <c r="R89">
+        <v>-617.48</v>
+      </c>
+      <c r="S89">
+        <v>18752</v>
+      </c>
+    </row>
+    <row r="90" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A90">
+        <v>87</v>
+      </c>
+      <c r="B90">
+        <v>-300.95</v>
+      </c>
+      <c r="C90">
+        <v>-94.46</v>
+      </c>
+      <c r="D90">
+        <v>21655</v>
+      </c>
+      <c r="F90">
+        <v>87</v>
+      </c>
+      <c r="G90">
+        <v>321.07</v>
+      </c>
+      <c r="H90">
+        <v>-617.02</v>
+      </c>
+      <c r="I90">
+        <v>18933</v>
+      </c>
+      <c r="P90">
+        <v>85</v>
+      </c>
+      <c r="Q90">
+        <v>311.17</v>
+      </c>
+      <c r="R90">
+        <v>-616.21</v>
+      </c>
+      <c r="S90">
+        <v>18802</v>
+      </c>
+    </row>
+    <row r="91" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A91">
+        <v>88</v>
+      </c>
+      <c r="B91">
+        <v>-303.14</v>
+      </c>
+      <c r="C91">
+        <v>-96.03</v>
+      </c>
+      <c r="D91">
+        <v>21705</v>
+      </c>
+      <c r="F91">
+        <v>88</v>
+      </c>
+      <c r="G91">
+        <v>321.07</v>
+      </c>
+      <c r="H91">
+        <v>-617.02</v>
+      </c>
+      <c r="I91">
+        <v>18983</v>
+      </c>
+      <c r="P91">
+        <v>86</v>
+      </c>
+      <c r="Q91">
+        <v>311.57</v>
+      </c>
+      <c r="R91">
+        <v>-616.05999999999995</v>
+      </c>
+      <c r="S91">
+        <v>18853</v>
+      </c>
+    </row>
+    <row r="92" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="F92">
+        <v>89</v>
+      </c>
+      <c r="G92">
+        <v>321.07</v>
+      </c>
+      <c r="H92">
+        <v>-617.02</v>
+      </c>
+      <c r="I92">
+        <v>19033</v>
+      </c>
+      <c r="P92">
+        <v>87</v>
+      </c>
+      <c r="Q92">
+        <v>313.95999999999998</v>
+      </c>
+      <c r="R92">
+        <v>-615.14</v>
+      </c>
+      <c r="S92">
+        <v>18904</v>
+      </c>
+    </row>
+    <row r="93" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="F93">
+        <v>90</v>
+      </c>
+      <c r="G93">
+        <v>321.07</v>
+      </c>
+      <c r="H93">
+        <v>-617.02</v>
+      </c>
+      <c r="I93">
+        <v>19083</v>
+      </c>
+      <c r="P93">
+        <v>88</v>
+      </c>
+      <c r="Q93">
+        <v>317.64</v>
+      </c>
+      <c r="R93">
+        <v>-613.63</v>
+      </c>
+      <c r="S93">
+        <v>18963</v>
+      </c>
+    </row>
+    <row r="94" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="P94">
+        <v>89</v>
+      </c>
+      <c r="Q94">
+        <v>321.82</v>
+      </c>
+      <c r="R94">
+        <v>-611.84</v>
+      </c>
+      <c r="S94">
+        <v>19013</v>
+      </c>
+    </row>
+    <row r="95" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="P95">
+        <v>90</v>
+      </c>
+      <c r="Q95">
+        <v>326.5</v>
+      </c>
+      <c r="R95">
+        <v>-609.78</v>
+      </c>
+      <c r="S95">
+        <v>19073</v>
+      </c>
+    </row>
+    <row r="96" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="P96">
+        <v>91</v>
+      </c>
+      <c r="Q96">
+        <v>-326.52</v>
+      </c>
+      <c r="R96">
+        <v>-608.74</v>
+      </c>
+      <c r="S96">
+        <v>19132</v>
+      </c>
+    </row>
+    <row r="97" spans="16:19" x14ac:dyDescent="0.35">
+      <c r="P97">
+        <v>92</v>
+      </c>
+      <c r="Q97">
+        <v>-326.52</v>
+      </c>
+      <c r="R97">
+        <v>-608.74</v>
+      </c>
+      <c r="S97">
+        <v>19182</v>
+      </c>
+    </row>
+    <row r="98" spans="16:19" x14ac:dyDescent="0.35">
+      <c r="P98">
+        <v>93</v>
+      </c>
+      <c r="Q98">
+        <v>-326.52</v>
+      </c>
+      <c r="R98">
+        <v>-608.74</v>
+      </c>
+      <c r="S98">
+        <v>19232</v>
+      </c>
+    </row>
+    <row r="99" spans="16:19" x14ac:dyDescent="0.35">
+      <c r="P99">
+        <v>94</v>
+      </c>
+      <c r="Q99">
+        <v>-326.52</v>
+      </c>
+      <c r="R99">
+        <v>-608.74</v>
+      </c>
+      <c r="S99">
+        <v>19282</v>
+      </c>
+    </row>
+    <row r="100" spans="16:19" x14ac:dyDescent="0.35">
+      <c r="P100">
+        <v>95</v>
+      </c>
+      <c r="Q100">
+        <v>-326.52</v>
+      </c>
+      <c r="R100">
+        <v>-608.74</v>
+      </c>
+      <c r="S100">
+        <v>19332</v>
+      </c>
+    </row>
+    <row r="101" spans="16:19" x14ac:dyDescent="0.35">
+      <c r="P101">
+        <v>96</v>
+      </c>
+      <c r="Q101">
+        <v>-326.52</v>
+      </c>
+      <c r="R101">
+        <v>-608.74</v>
+      </c>
+      <c r="S101">
+        <v>19382</v>
+      </c>
+    </row>
+    <row r="102" spans="16:19" x14ac:dyDescent="0.35">
+      <c r="P102">
+        <v>97</v>
+      </c>
+      <c r="Q102">
+        <v>-326.52</v>
+      </c>
+      <c r="R102">
+        <v>-608.74</v>
+      </c>
+      <c r="S102">
+        <v>19432</v>
+      </c>
+    </row>
+    <row r="103" spans="16:19" x14ac:dyDescent="0.35">
+      <c r="P103">
+        <v>98</v>
+      </c>
+      <c r="Q103">
+        <v>-326.52</v>
+      </c>
+      <c r="R103">
+        <v>-608.74</v>
+      </c>
+      <c r="S103">
+        <v>19482</v>
+      </c>
+    </row>
+    <row r="104" spans="16:19" x14ac:dyDescent="0.35">
+      <c r="P104">
+        <v>99</v>
+      </c>
+      <c r="Q104">
+        <v>-326.52</v>
+      </c>
+      <c r="R104">
+        <v>-608.74</v>
+      </c>
+      <c r="S104">
+        <v>19532</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{631A7A13-8FED-4C8B-B127-A981A183D85E}">
+  <dimension ref="A1:I95"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2" t="s">
+        <v>1</v>
+      </c>
+      <c r="H2" t="s">
+        <v>2</v>
+      </c>
+      <c r="I2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>0</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>14592</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>3.94</v>
+      </c>
+      <c r="H3">
+        <v>0.36</v>
+      </c>
+      <c r="I3">
+        <v>14433</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>-0.28000000000000003</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>14642</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>4.5</v>
+      </c>
+      <c r="H4">
+        <v>0.33</v>
+      </c>
+      <c r="I4">
+        <v>14483</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5">
+        <v>-1.84</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>14693</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>4.79</v>
+      </c>
+      <c r="H5">
+        <v>0.32</v>
+      </c>
+      <c r="I5">
+        <v>14533</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6">
+        <v>-2.5499999999999998</v>
+      </c>
+      <c r="C6">
+        <v>-0.01</v>
+      </c>
+      <c r="D6">
+        <v>14743</v>
+      </c>
+      <c r="F6">
+        <v>3</v>
+      </c>
+      <c r="G6">
+        <v>5.36</v>
+      </c>
+      <c r="H6">
+        <v>0.3</v>
+      </c>
+      <c r="I6">
+        <v>14584</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>4</v>
+      </c>
+      <c r="B7">
+        <v>-4.82</v>
+      </c>
+      <c r="C7">
+        <v>-0.04</v>
+      </c>
+      <c r="D7">
+        <v>14793</v>
+      </c>
+      <c r="F7">
+        <v>4</v>
+      </c>
+      <c r="G7">
+        <v>5.64</v>
+      </c>
+      <c r="H7">
+        <v>0.3</v>
+      </c>
+      <c r="I7">
+        <v>14635</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>5</v>
+      </c>
+      <c r="B8">
+        <v>-7.51</v>
+      </c>
+      <c r="C8">
+        <v>-0.09</v>
+      </c>
+      <c r="D8">
+        <v>14843</v>
+      </c>
+      <c r="F8">
+        <v>5</v>
+      </c>
+      <c r="G8">
+        <v>6.21</v>
+      </c>
+      <c r="H8">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="I8">
+        <v>14694</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>6</v>
+      </c>
+      <c r="B9">
+        <v>-11.63</v>
+      </c>
+      <c r="C9">
+        <v>-0.18</v>
+      </c>
+      <c r="D9">
+        <v>14893</v>
+      </c>
+      <c r="F9">
+        <v>6</v>
+      </c>
+      <c r="G9">
+        <v>6.92</v>
+      </c>
+      <c r="H9">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="I9">
+        <v>14744</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>7</v>
+      </c>
+      <c r="B10">
+        <v>-14.04</v>
+      </c>
+      <c r="C10">
+        <v>-0.25</v>
+      </c>
+      <c r="D10">
+        <v>14943</v>
+      </c>
+      <c r="F10">
+        <v>7</v>
+      </c>
+      <c r="G10">
+        <v>7.91</v>
+      </c>
+      <c r="H10">
+        <v>0.32</v>
+      </c>
+      <c r="I10">
+        <v>14794</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>8</v>
+      </c>
+      <c r="B11">
+        <v>-17.579999999999998</v>
+      </c>
+      <c r="C11">
+        <v>-0.38</v>
+      </c>
+      <c r="D11">
+        <v>14994</v>
+      </c>
+      <c r="F11">
+        <v>8</v>
+      </c>
+      <c r="G11">
+        <v>8.6199999999999992</v>
+      </c>
+      <c r="H11">
+        <v>0.35</v>
+      </c>
+      <c r="I11">
+        <v>14844</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>9</v>
+      </c>
+      <c r="B12">
+        <v>-19.989999999999998</v>
+      </c>
+      <c r="C12">
+        <v>-0.48</v>
+      </c>
+      <c r="D12">
+        <v>15044</v>
+      </c>
+      <c r="F12">
+        <v>9</v>
+      </c>
+      <c r="G12">
+        <v>9.6199999999999992</v>
+      </c>
+      <c r="H12">
+        <v>0.42</v>
+      </c>
+      <c r="I12">
+        <v>14895</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>10</v>
+      </c>
+      <c r="B13">
+        <v>-23.96</v>
+      </c>
+      <c r="C13">
+        <v>-0.67</v>
+      </c>
+      <c r="D13">
+        <v>15094</v>
+      </c>
+      <c r="F13">
+        <v>10</v>
+      </c>
+      <c r="G13">
+        <v>10.46</v>
+      </c>
+      <c r="H13">
+        <v>0.49</v>
+      </c>
+      <c r="I13">
+        <v>14955</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>11</v>
+      </c>
+      <c r="B14">
+        <v>-26.37</v>
+      </c>
+      <c r="C14">
+        <v>-0.79</v>
+      </c>
+      <c r="D14">
+        <v>15145</v>
+      </c>
+      <c r="F14">
+        <v>11</v>
+      </c>
+      <c r="G14">
+        <v>11.17</v>
+      </c>
+      <c r="H14">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="I14">
+        <v>15005</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>12</v>
+      </c>
+      <c r="B15">
+        <v>-30.19</v>
+      </c>
+      <c r="C15">
+        <v>-1.02</v>
+      </c>
+      <c r="D15">
+        <v>15195</v>
+      </c>
+      <c r="F15">
+        <v>12</v>
+      </c>
+      <c r="G15">
+        <v>11.31</v>
+      </c>
+      <c r="H15">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="I15">
+        <v>15055</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>13</v>
+      </c>
+      <c r="B16">
+        <v>-32.880000000000003</v>
+      </c>
+      <c r="C16">
+        <v>-1.2</v>
+      </c>
+      <c r="D16">
+        <v>15246</v>
+      </c>
+      <c r="F16">
+        <v>13</v>
+      </c>
+      <c r="G16">
+        <v>13.15</v>
+      </c>
+      <c r="H16">
+        <v>0.79</v>
+      </c>
+      <c r="I16">
+        <v>15106</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>14</v>
+      </c>
+      <c r="B17">
+        <v>-36.840000000000003</v>
+      </c>
+      <c r="C17">
+        <v>-1.49</v>
+      </c>
+      <c r="D17">
+        <v>15296</v>
+      </c>
+      <c r="F17">
+        <v>14</v>
+      </c>
+      <c r="G17">
+        <v>15.83</v>
+      </c>
+      <c r="H17">
+        <v>1.08</v>
+      </c>
+      <c r="I17">
+        <v>15165</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>15</v>
+      </c>
+      <c r="B18">
+        <v>-39.53</v>
+      </c>
+      <c r="C18">
+        <v>-1.71</v>
+      </c>
+      <c r="D18">
+        <v>15346</v>
+      </c>
+      <c r="F18">
+        <v>15</v>
+      </c>
+      <c r="G18">
+        <v>18.52</v>
+      </c>
+      <c r="H18">
+        <v>1.35</v>
+      </c>
+      <c r="I18">
+        <v>15215</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>16</v>
+      </c>
+      <c r="B19">
+        <v>-43.63</v>
+      </c>
+      <c r="C19">
+        <v>-2.0699999999999998</v>
+      </c>
+      <c r="D19">
+        <v>15396</v>
+      </c>
+      <c r="F19">
+        <v>16</v>
+      </c>
+      <c r="G19">
+        <v>21.63</v>
+      </c>
+      <c r="H19">
+        <v>1.63</v>
+      </c>
+      <c r="I19">
+        <v>15265</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>17</v>
+      </c>
+      <c r="B20">
+        <v>-46.31</v>
+      </c>
+      <c r="C20">
+        <v>-2.3199999999999998</v>
+      </c>
+      <c r="D20">
+        <v>15447</v>
+      </c>
+      <c r="F20">
+        <v>17</v>
+      </c>
+      <c r="G20">
+        <v>24.75</v>
+      </c>
+      <c r="H20">
+        <v>1.89</v>
+      </c>
+      <c r="I20">
+        <v>15315</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>18</v>
+      </c>
+      <c r="B21">
+        <v>-50.26</v>
+      </c>
+      <c r="C21">
+        <v>-2.72</v>
+      </c>
+      <c r="D21">
+        <v>15497</v>
+      </c>
+      <c r="F21">
+        <v>18</v>
+      </c>
+      <c r="G21">
+        <v>28.15</v>
+      </c>
+      <c r="H21">
+        <v>2.14</v>
+      </c>
+      <c r="I21">
+        <v>15365</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>19</v>
+      </c>
+      <c r="B22">
+        <v>-52.94</v>
+      </c>
+      <c r="C22">
+        <v>-3.01</v>
+      </c>
+      <c r="D22">
+        <v>15547</v>
+      </c>
+      <c r="F22">
+        <v>19</v>
+      </c>
+      <c r="G22">
+        <v>31.55</v>
+      </c>
+      <c r="H22">
+        <v>2.36</v>
+      </c>
+      <c r="I22">
+        <v>15415</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>20</v>
+      </c>
+      <c r="B23">
+        <v>-57.17</v>
+      </c>
+      <c r="C23">
+        <v>-3.48</v>
+      </c>
+      <c r="D23">
+        <v>15597</v>
+      </c>
+      <c r="F23">
+        <v>20</v>
+      </c>
+      <c r="G23">
+        <v>34.96</v>
+      </c>
+      <c r="H23">
+        <v>2.5499999999999998</v>
+      </c>
+      <c r="I23">
+        <v>15465</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>21</v>
+      </c>
+      <c r="B24">
+        <v>-60.13</v>
+      </c>
+      <c r="C24">
+        <v>-3.84</v>
+      </c>
+      <c r="D24">
+        <v>15647</v>
+      </c>
+      <c r="F24">
+        <v>21</v>
+      </c>
+      <c r="G24">
+        <v>38.5</v>
+      </c>
+      <c r="H24">
+        <v>2.72</v>
+      </c>
+      <c r="I24">
+        <v>15515</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>22</v>
+      </c>
+      <c r="B25">
+        <v>-64.209999999999994</v>
+      </c>
+      <c r="C25">
+        <v>-4.3499999999999996</v>
+      </c>
+      <c r="D25">
+        <v>15698</v>
+      </c>
+      <c r="F25">
+        <v>22</v>
+      </c>
+      <c r="G25">
+        <v>42.05</v>
+      </c>
+      <c r="H25">
+        <v>2.85</v>
+      </c>
+      <c r="I25">
+        <v>15565</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>23</v>
+      </c>
+      <c r="B26">
+        <v>-67.17</v>
+      </c>
+      <c r="C26">
+        <v>-4.7300000000000004</v>
+      </c>
+      <c r="D26">
+        <v>15748</v>
+      </c>
+      <c r="F26">
+        <v>23</v>
+      </c>
+      <c r="G26">
+        <v>45.75</v>
+      </c>
+      <c r="H26">
+        <v>2.97</v>
+      </c>
+      <c r="I26">
+        <v>15616</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>24</v>
+      </c>
+      <c r="B27">
+        <v>-71.099999999999994</v>
+      </c>
+      <c r="C27">
+        <v>-5.26</v>
+      </c>
+      <c r="D27">
+        <v>15798</v>
+      </c>
+      <c r="F27">
+        <v>24</v>
+      </c>
+      <c r="G27">
+        <v>50.29</v>
+      </c>
+      <c r="H27">
+        <v>3.06</v>
+      </c>
+      <c r="I27">
+        <v>15675</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>25</v>
+      </c>
+      <c r="B28">
+        <v>-73.91</v>
+      </c>
+      <c r="C28">
+        <v>-5.66</v>
+      </c>
+      <c r="D28">
+        <v>15848</v>
+      </c>
+      <c r="F28">
+        <v>25</v>
+      </c>
+      <c r="G28">
+        <v>54.27</v>
+      </c>
+      <c r="H28">
+        <v>3.1</v>
+      </c>
+      <c r="I28">
+        <v>15725</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>26</v>
+      </c>
+      <c r="B29">
+        <v>-78.12</v>
+      </c>
+      <c r="C29">
+        <v>-6.28</v>
+      </c>
+      <c r="D29">
+        <v>15898</v>
+      </c>
+      <c r="F29">
+        <v>26</v>
+      </c>
+      <c r="G29">
+        <v>58.11</v>
+      </c>
+      <c r="H29">
+        <v>3.1</v>
+      </c>
+      <c r="I29">
+        <v>15775</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>27</v>
+      </c>
+      <c r="B30">
+        <v>-81.069999999999993</v>
+      </c>
+      <c r="C30">
+        <v>-6.73</v>
+      </c>
+      <c r="D30">
+        <v>15948</v>
+      </c>
+      <c r="F30">
+        <v>27</v>
+      </c>
+      <c r="G30">
+        <v>62.09</v>
+      </c>
+      <c r="H30">
+        <v>3.09</v>
+      </c>
+      <c r="I30">
+        <v>15825</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>28</v>
+      </c>
+      <c r="B31">
+        <v>-83.87</v>
+      </c>
+      <c r="C31">
+        <v>-7.18</v>
+      </c>
+      <c r="D31">
+        <v>15998</v>
+      </c>
+      <c r="F31">
+        <v>28</v>
+      </c>
+      <c r="G31">
+        <v>65.78</v>
+      </c>
+      <c r="H31">
+        <v>3.06</v>
+      </c>
+      <c r="I31">
+        <v>15876</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>29</v>
+      </c>
+      <c r="B32">
+        <v>-88.35</v>
+      </c>
+      <c r="C32">
+        <v>-7.93</v>
+      </c>
+      <c r="D32">
+        <v>16048</v>
+      </c>
+      <c r="F32">
+        <v>29</v>
+      </c>
+      <c r="G32">
+        <v>70.75</v>
+      </c>
+      <c r="H32">
+        <v>2.99</v>
+      </c>
+      <c r="I32">
+        <v>15935</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>30</v>
+      </c>
+      <c r="B33">
+        <v>-91</v>
+      </c>
+      <c r="C33">
+        <v>-8.39</v>
+      </c>
+      <c r="D33">
+        <v>16098</v>
+      </c>
+      <c r="F33">
+        <v>30</v>
+      </c>
+      <c r="G33">
+        <v>75.02</v>
+      </c>
+      <c r="H33">
+        <v>2.89</v>
+      </c>
+      <c r="I33">
+        <v>15985</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A34">
+        <v>31</v>
+      </c>
+      <c r="B34">
+        <v>-95.33</v>
+      </c>
+      <c r="C34">
+        <v>-9.19</v>
+      </c>
+      <c r="D34">
+        <v>16148</v>
+      </c>
+      <c r="F34">
+        <v>31</v>
+      </c>
+      <c r="G34">
+        <v>78.989999999999995</v>
+      </c>
+      <c r="H34">
+        <v>2.76</v>
+      </c>
+      <c r="I34">
+        <v>16035</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A35">
+        <v>32</v>
+      </c>
+      <c r="B35">
+        <v>-98.39</v>
+      </c>
+      <c r="C35">
+        <v>-9.7899999999999991</v>
+      </c>
+      <c r="D35">
+        <v>16198</v>
+      </c>
+      <c r="F35">
+        <v>32</v>
+      </c>
+      <c r="G35">
+        <v>82.97</v>
+      </c>
+      <c r="H35">
+        <v>2.61</v>
+      </c>
+      <c r="I35">
+        <v>16086</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A36">
+        <v>33</v>
+      </c>
+      <c r="B36">
+        <v>-102.98</v>
+      </c>
+      <c r="C36">
+        <v>-10.71</v>
+      </c>
+      <c r="D36">
+        <v>16248</v>
+      </c>
+      <c r="F36">
+        <v>33</v>
+      </c>
+      <c r="G36">
+        <v>88.08</v>
+      </c>
+      <c r="H36">
+        <v>2.35</v>
+      </c>
+      <c r="I36">
+        <v>16145</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A37">
+        <v>34</v>
+      </c>
+      <c r="B37">
+        <v>-105.9</v>
+      </c>
+      <c r="C37">
+        <v>-11.32</v>
+      </c>
+      <c r="D37">
+        <v>16299</v>
+      </c>
+      <c r="F37">
+        <v>34</v>
+      </c>
+      <c r="G37">
+        <v>92.47</v>
+      </c>
+      <c r="H37">
+        <v>2.11</v>
+      </c>
+      <c r="I37">
+        <v>16195</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A38">
+        <v>35</v>
+      </c>
+      <c r="B38">
+        <v>-110.48</v>
+      </c>
+      <c r="C38">
+        <v>-12.29</v>
+      </c>
+      <c r="D38">
+        <v>16349</v>
+      </c>
+      <c r="F38">
+        <v>35</v>
+      </c>
+      <c r="G38">
+        <v>96.87</v>
+      </c>
+      <c r="H38">
+        <v>1.86</v>
+      </c>
+      <c r="I38">
+        <v>16245</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A39">
+        <v>36</v>
+      </c>
+      <c r="B39">
+        <v>-113.53</v>
+      </c>
+      <c r="C39">
+        <v>-12.96</v>
+      </c>
+      <c r="D39">
+        <v>16399</v>
+      </c>
+      <c r="F39">
+        <v>36</v>
+      </c>
+      <c r="G39">
+        <v>101.13</v>
+      </c>
+      <c r="H39">
+        <v>1.59</v>
+      </c>
+      <c r="I39">
+        <v>16295</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A40">
+        <v>37</v>
+      </c>
+      <c r="B40">
+        <v>-117.95</v>
+      </c>
+      <c r="C40">
+        <v>-13.96</v>
+      </c>
+      <c r="D40">
+        <v>16449</v>
+      </c>
+      <c r="F40">
+        <v>37</v>
+      </c>
+      <c r="G40">
+        <v>105.66</v>
+      </c>
+      <c r="H40">
+        <v>1.29</v>
+      </c>
+      <c r="I40">
+        <v>16346</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A41">
+        <v>38</v>
+      </c>
+      <c r="B41">
+        <v>-120.99</v>
+      </c>
+      <c r="C41">
+        <v>-14.66</v>
+      </c>
+      <c r="D41">
+        <v>16499</v>
+      </c>
+      <c r="F41">
+        <v>38</v>
+      </c>
+      <c r="G41">
+        <v>111.05</v>
+      </c>
+      <c r="H41">
+        <v>0.93</v>
+      </c>
+      <c r="I41">
+        <v>16405</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A42">
+        <v>39</v>
+      </c>
+      <c r="B42">
+        <v>-125.55</v>
+      </c>
+      <c r="C42">
+        <v>-15.76</v>
+      </c>
+      <c r="D42">
+        <v>16550</v>
+      </c>
+      <c r="F42">
+        <v>39</v>
+      </c>
+      <c r="G42">
+        <v>115.73</v>
+      </c>
+      <c r="H42">
+        <v>0.62</v>
+      </c>
+      <c r="I42">
+        <v>16455</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A43">
+        <v>40</v>
+      </c>
+      <c r="B43">
+        <v>-130.22</v>
+      </c>
+      <c r="C43">
+        <v>-16.93</v>
+      </c>
+      <c r="D43">
+        <v>16601</v>
+      </c>
+      <c r="F43">
+        <v>40</v>
+      </c>
+      <c r="G43">
+        <v>120.27</v>
+      </c>
+      <c r="H43">
+        <v>0.32</v>
+      </c>
+      <c r="I43">
+        <v>16505</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A44">
+        <v>41</v>
+      </c>
+      <c r="B44">
+        <v>-133.52000000000001</v>
+      </c>
+      <c r="C44">
+        <v>-17.78</v>
+      </c>
+      <c r="D44">
+        <v>16651</v>
+      </c>
+      <c r="F44">
+        <v>41</v>
+      </c>
+      <c r="G44">
+        <v>124.95</v>
+      </c>
+      <c r="H44">
+        <v>0.02</v>
+      </c>
+      <c r="I44">
+        <v>16556</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A45">
+        <v>42</v>
+      </c>
+      <c r="B45">
+        <v>-136.54</v>
+      </c>
+      <c r="C45">
+        <v>-18.57</v>
+      </c>
+      <c r="D45">
+        <v>16701</v>
+      </c>
+      <c r="F45">
+        <v>42</v>
+      </c>
+      <c r="G45">
+        <v>130.62</v>
+      </c>
+      <c r="H45">
+        <v>-0.35</v>
+      </c>
+      <c r="I45">
+        <v>16615</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A46">
+        <v>43</v>
+      </c>
+      <c r="B46">
+        <v>-141.33000000000001</v>
+      </c>
+      <c r="C46">
+        <v>-19.89</v>
+      </c>
+      <c r="D46">
+        <v>16751</v>
+      </c>
+      <c r="F46">
+        <v>43</v>
+      </c>
+      <c r="G46">
+        <v>135.30000000000001</v>
+      </c>
+      <c r="H46">
+        <v>-0.63</v>
+      </c>
+      <c r="I46">
+        <v>16665</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A47">
+        <v>44</v>
+      </c>
+      <c r="B47">
+        <v>-144.33000000000001</v>
+      </c>
+      <c r="C47">
+        <v>-20.73</v>
+      </c>
+      <c r="D47">
+        <v>16801</v>
+      </c>
+      <c r="F47">
+        <v>44</v>
+      </c>
+      <c r="G47">
+        <v>139.97999999999999</v>
+      </c>
+      <c r="H47">
+        <v>-0.89</v>
+      </c>
+      <c r="I47">
+        <v>16715</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A48">
+        <v>45</v>
+      </c>
+      <c r="B48">
+        <v>-148.97</v>
+      </c>
+      <c r="C48">
+        <v>-22.07</v>
+      </c>
+      <c r="D48">
+        <v>16851</v>
+      </c>
+      <c r="F48">
+        <v>45</v>
+      </c>
+      <c r="G48">
+        <v>144.52000000000001</v>
+      </c>
+      <c r="H48">
+        <v>-1.1200000000000001</v>
+      </c>
+      <c r="I48">
+        <v>16765</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A49">
+        <v>46</v>
+      </c>
+      <c r="B49">
+        <v>-152.22999999999999</v>
+      </c>
+      <c r="C49">
+        <v>-23.03</v>
+      </c>
+      <c r="D49">
+        <v>16901</v>
+      </c>
+      <c r="F49">
+        <v>46</v>
+      </c>
+      <c r="G49">
+        <v>149.07</v>
+      </c>
+      <c r="H49">
+        <v>-1.32</v>
+      </c>
+      <c r="I49">
+        <v>16816</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A50">
+        <v>47</v>
+      </c>
+      <c r="B50">
+        <v>-156.85</v>
+      </c>
+      <c r="C50">
+        <v>-24.44</v>
+      </c>
+      <c r="D50">
+        <v>16951</v>
+      </c>
+      <c r="F50">
+        <v>47</v>
+      </c>
+      <c r="G50">
+        <v>154.75</v>
+      </c>
+      <c r="H50">
+        <v>-1.53</v>
+      </c>
+      <c r="I50">
+        <v>16875</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A51">
+        <v>48</v>
+      </c>
+      <c r="B51">
+        <v>-159.96</v>
+      </c>
+      <c r="C51">
+        <v>-25.4</v>
+      </c>
+      <c r="D51">
+        <v>17001</v>
+      </c>
+      <c r="F51">
+        <v>48</v>
+      </c>
+      <c r="G51">
+        <v>159.57</v>
+      </c>
+      <c r="H51">
+        <v>-1.68</v>
+      </c>
+      <c r="I51">
+        <v>16925</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A52">
+        <v>49</v>
+      </c>
+      <c r="B52">
+        <v>-164.84</v>
+      </c>
+      <c r="C52">
+        <v>-26.93</v>
+      </c>
+      <c r="D52">
+        <v>17051</v>
+      </c>
+      <c r="F52">
+        <v>49</v>
+      </c>
+      <c r="G52">
+        <v>164.4</v>
+      </c>
+      <c r="H52">
+        <v>-1.78</v>
+      </c>
+      <c r="I52">
+        <v>16975</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A53">
+        <v>50</v>
+      </c>
+      <c r="B53">
+        <v>-167.81</v>
+      </c>
+      <c r="C53">
+        <v>-27.89</v>
+      </c>
+      <c r="D53">
+        <v>17101</v>
+      </c>
+      <c r="F53">
+        <v>50</v>
+      </c>
+      <c r="G53">
+        <v>169.09</v>
+      </c>
+      <c r="H53">
+        <v>-1.81</v>
+      </c>
+      <c r="I53">
+        <v>17026</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A54">
+        <v>51</v>
+      </c>
+      <c r="B54">
+        <v>-172.66</v>
+      </c>
+      <c r="C54">
+        <v>-29.49</v>
+      </c>
+      <c r="D54">
+        <v>17153</v>
+      </c>
+      <c r="F54">
+        <v>51</v>
+      </c>
+      <c r="G54">
+        <v>174.64</v>
+      </c>
+      <c r="H54">
+        <v>-1.8</v>
+      </c>
+      <c r="I54">
+        <v>17085</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A55">
+        <v>52</v>
+      </c>
+      <c r="B55">
+        <v>-175.88</v>
+      </c>
+      <c r="C55">
+        <v>-30.59</v>
+      </c>
+      <c r="D55">
+        <v>17203</v>
+      </c>
+      <c r="F55">
+        <v>52</v>
+      </c>
+      <c r="G55">
+        <v>179.47</v>
+      </c>
+      <c r="H55">
+        <v>-1.76</v>
+      </c>
+      <c r="I55">
+        <v>17135</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A56">
+        <v>53</v>
+      </c>
+      <c r="B56">
+        <v>-180.57</v>
+      </c>
+      <c r="C56">
+        <v>-32.22</v>
+      </c>
+      <c r="D56">
+        <v>17254</v>
+      </c>
+      <c r="F56">
+        <v>53</v>
+      </c>
+      <c r="G56">
+        <v>183.44</v>
+      </c>
+      <c r="H56">
+        <v>-1.7</v>
+      </c>
+      <c r="I56">
+        <v>17185</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A57">
+        <v>54</v>
+      </c>
+      <c r="B57">
+        <v>-183.78</v>
+      </c>
+      <c r="C57">
+        <v>-33.36</v>
+      </c>
+      <c r="D57">
+        <v>17304</v>
+      </c>
+      <c r="F57">
+        <v>54</v>
+      </c>
+      <c r="G57">
+        <v>188.42</v>
+      </c>
+      <c r="H57">
+        <v>-1.57</v>
+      </c>
+      <c r="I57">
+        <v>17235</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A58">
+        <v>55</v>
+      </c>
+      <c r="B58">
+        <v>-188.71</v>
+      </c>
+      <c r="C58">
+        <v>-35.17</v>
+      </c>
+      <c r="D58">
+        <v>17354</v>
+      </c>
+      <c r="F58">
+        <v>55</v>
+      </c>
+      <c r="G58">
+        <v>193.39</v>
+      </c>
+      <c r="H58">
+        <v>-1.38</v>
+      </c>
+      <c r="I58">
+        <v>17285</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A59">
+        <v>56</v>
+      </c>
+      <c r="B59">
+        <v>-191.9</v>
+      </c>
+      <c r="C59">
+        <v>-36.36</v>
+      </c>
+      <c r="D59">
+        <v>17404</v>
+      </c>
+      <c r="F59">
+        <v>56</v>
+      </c>
+      <c r="G59">
+        <v>197.79</v>
+      </c>
+      <c r="H59">
+        <v>-1.18</v>
+      </c>
+      <c r="I59">
+        <v>17335</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A60">
+        <v>57</v>
+      </c>
+      <c r="B60">
+        <v>-196.67</v>
+      </c>
+      <c r="C60">
+        <v>-38.18</v>
+      </c>
+      <c r="D60">
+        <v>17454</v>
+      </c>
+      <c r="F60">
+        <v>57</v>
+      </c>
+      <c r="G60">
+        <v>202.61</v>
+      </c>
+      <c r="H60">
+        <v>-0.91</v>
+      </c>
+      <c r="I60">
+        <v>17385</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A61">
+        <v>58</v>
+      </c>
+      <c r="B61">
+        <v>-199.97</v>
+      </c>
+      <c r="C61">
+        <v>-39.479999999999997</v>
+      </c>
+      <c r="D61">
+        <v>17504</v>
+      </c>
+      <c r="F61">
+        <v>58</v>
+      </c>
+      <c r="G61">
+        <v>207.29</v>
+      </c>
+      <c r="H61">
+        <v>-0.57999999999999996</v>
+      </c>
+      <c r="I61">
+        <v>17435</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A62">
+        <v>59</v>
+      </c>
+      <c r="B62">
+        <v>-204.71</v>
+      </c>
+      <c r="C62">
+        <v>-41.39</v>
+      </c>
+      <c r="D62">
+        <v>17554</v>
+      </c>
+      <c r="F62">
+        <v>59</v>
+      </c>
+      <c r="G62">
+        <v>211.96</v>
+      </c>
+      <c r="H62">
+        <v>-0.2</v>
+      </c>
+      <c r="I62">
+        <v>17485</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A63">
+        <v>60</v>
+      </c>
+      <c r="B63">
+        <v>-208.12</v>
+      </c>
+      <c r="C63">
+        <v>-42.78</v>
+      </c>
+      <c r="D63">
+        <v>17605</v>
+      </c>
+      <c r="F63">
+        <v>60</v>
+      </c>
+      <c r="G63">
+        <v>216.77</v>
+      </c>
+      <c r="H63">
+        <v>0.25</v>
+      </c>
+      <c r="I63">
+        <v>17536</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A64">
+        <v>61</v>
+      </c>
+      <c r="B64">
+        <v>-212.84</v>
+      </c>
+      <c r="C64">
+        <v>-44.74</v>
+      </c>
+      <c r="D64">
+        <v>17655</v>
+      </c>
+      <c r="F64">
+        <v>61</v>
+      </c>
+      <c r="G64">
+        <v>222.56</v>
+      </c>
+      <c r="H64">
+        <v>0.87</v>
+      </c>
+      <c r="I64">
+        <v>17595</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A65">
+        <v>62</v>
+      </c>
+      <c r="B65">
+        <v>-216.1</v>
+      </c>
+      <c r="C65">
+        <v>-46.14</v>
+      </c>
+      <c r="D65">
+        <v>17705</v>
+      </c>
+      <c r="F65">
+        <v>62</v>
+      </c>
+      <c r="G65">
+        <v>228.49</v>
+      </c>
+      <c r="H65">
+        <v>1.6</v>
+      </c>
+      <c r="I65">
+        <v>17654</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A66">
+        <v>63</v>
+      </c>
+      <c r="B66">
+        <v>-221.04</v>
+      </c>
+      <c r="C66">
+        <v>-48.29</v>
+      </c>
+      <c r="D66">
+        <v>17755</v>
+      </c>
+      <c r="F66">
+        <v>63</v>
+      </c>
+      <c r="G66">
+        <v>233.42</v>
+      </c>
+      <c r="H66">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="I66">
+        <v>17704</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A67">
+        <v>64</v>
+      </c>
+      <c r="B67">
+        <v>-224.41</v>
+      </c>
+      <c r="C67">
+        <v>-49.79</v>
+      </c>
+      <c r="D67">
+        <v>17805</v>
+      </c>
+      <c r="F67">
+        <v>64</v>
+      </c>
+      <c r="G67">
+        <v>238.48</v>
+      </c>
+      <c r="H67">
+        <v>2.99</v>
+      </c>
+      <c r="I67">
+        <v>17754</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A68">
+        <v>65</v>
+      </c>
+      <c r="B68">
+        <v>-229.18</v>
+      </c>
+      <c r="C68">
+        <v>-51.97</v>
+      </c>
+      <c r="D68">
+        <v>17855</v>
+      </c>
+      <c r="F68">
+        <v>65</v>
+      </c>
+      <c r="G68">
+        <v>243.39</v>
+      </c>
+      <c r="H68">
+        <v>3.78</v>
+      </c>
+      <c r="I68">
+        <v>17804</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A69">
+        <v>66</v>
+      </c>
+      <c r="B69">
+        <v>-232.4</v>
+      </c>
+      <c r="C69">
+        <v>-53.47</v>
+      </c>
+      <c r="D69">
+        <v>17905</v>
+      </c>
+      <c r="F69">
+        <v>66</v>
+      </c>
+      <c r="G69">
+        <v>248.29</v>
+      </c>
+      <c r="H69">
+        <v>4.62</v>
+      </c>
+      <c r="I69">
+        <v>17854</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A70">
+        <v>67</v>
+      </c>
+      <c r="B70">
+        <v>-237.26</v>
+      </c>
+      <c r="C70">
+        <v>-55.8</v>
+      </c>
+      <c r="D70">
+        <v>17955</v>
+      </c>
+      <c r="F70">
+        <v>67</v>
+      </c>
+      <c r="G70">
+        <v>253.32</v>
+      </c>
+      <c r="H70">
+        <v>5.55</v>
+      </c>
+      <c r="I70">
+        <v>17904</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A71">
+        <v>68</v>
+      </c>
+      <c r="B71">
+        <v>-240.58</v>
+      </c>
+      <c r="C71">
+        <v>-57.41</v>
+      </c>
+      <c r="D71">
+        <v>18006</v>
+      </c>
+      <c r="F71">
+        <v>68</v>
+      </c>
+      <c r="G71">
+        <v>258.06</v>
+      </c>
+      <c r="H71">
+        <v>6.5</v>
+      </c>
+      <c r="I71">
+        <v>17954</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A72">
+        <v>69</v>
+      </c>
+      <c r="B72">
+        <v>-245.28</v>
+      </c>
+      <c r="C72">
+        <v>-59.75</v>
+      </c>
+      <c r="D72">
+        <v>18057</v>
+      </c>
+      <c r="F72">
+        <v>69</v>
+      </c>
+      <c r="G72">
+        <v>262.92</v>
+      </c>
+      <c r="H72">
+        <v>7.53</v>
+      </c>
+      <c r="I72">
+        <v>18004</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A73">
+        <v>70</v>
+      </c>
+      <c r="B73">
+        <v>-250.08</v>
+      </c>
+      <c r="C73">
+        <v>-62.19</v>
+      </c>
+      <c r="D73">
+        <v>18107</v>
+      </c>
+      <c r="F73">
+        <v>70</v>
+      </c>
+      <c r="G73">
+        <v>267.77999999999997</v>
+      </c>
+      <c r="H73">
+        <v>8.6</v>
+      </c>
+      <c r="I73">
+        <v>18054</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A74">
+        <v>71</v>
+      </c>
+      <c r="B74">
+        <v>-253.36</v>
+      </c>
+      <c r="C74">
+        <v>-63.88</v>
+      </c>
+      <c r="D74">
+        <v>18157</v>
+      </c>
+      <c r="F74">
+        <v>71</v>
+      </c>
+      <c r="G74">
+        <v>272.35000000000002</v>
+      </c>
+      <c r="H74">
+        <v>9.66</v>
+      </c>
+      <c r="I74">
+        <v>18104</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A75">
+        <v>72</v>
+      </c>
+      <c r="B75">
+        <v>-258.26</v>
+      </c>
+      <c r="C75">
+        <v>-66.459999999999994</v>
+      </c>
+      <c r="D75">
+        <v>18208</v>
+      </c>
+      <c r="F75">
+        <v>72</v>
+      </c>
+      <c r="G75">
+        <v>276.91000000000003</v>
+      </c>
+      <c r="H75">
+        <v>10.76</v>
+      </c>
+      <c r="I75">
+        <v>18154</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A76">
+        <v>73</v>
+      </c>
+      <c r="B76">
+        <v>-261.51</v>
+      </c>
+      <c r="C76">
+        <v>-68.2</v>
+      </c>
+      <c r="D76">
+        <v>18258</v>
+      </c>
+      <c r="F76">
+        <v>73</v>
+      </c>
+      <c r="G76">
+        <v>281.73</v>
+      </c>
+      <c r="H76">
+        <v>11.98</v>
+      </c>
+      <c r="I76">
+        <v>18204</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A77">
+        <v>74</v>
+      </c>
+      <c r="B77">
+        <v>-265.12</v>
+      </c>
+      <c r="C77">
+        <v>-70.180000000000007</v>
+      </c>
+      <c r="D77">
+        <v>18309</v>
+      </c>
+      <c r="F77">
+        <v>74</v>
+      </c>
+      <c r="G77">
+        <v>286.67</v>
+      </c>
+      <c r="H77">
+        <v>13.29</v>
+      </c>
+      <c r="I77">
+        <v>18254</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A78">
+        <v>75</v>
+      </c>
+      <c r="B78">
+        <v>-267.60000000000002</v>
+      </c>
+      <c r="C78">
+        <v>-71.56</v>
+      </c>
+      <c r="D78">
+        <v>18359</v>
+      </c>
+      <c r="F78">
+        <v>75</v>
+      </c>
+      <c r="G78">
+        <v>291.33</v>
+      </c>
+      <c r="H78">
+        <v>14.56</v>
+      </c>
+      <c r="I78">
+        <v>18304</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A79">
+        <v>76</v>
+      </c>
+      <c r="B79">
+        <v>-271.05</v>
+      </c>
+      <c r="C79">
+        <v>-73.52</v>
+      </c>
+      <c r="D79">
+        <v>18409</v>
+      </c>
+      <c r="F79">
+        <v>76</v>
+      </c>
+      <c r="G79">
+        <v>296.94</v>
+      </c>
+      <c r="H79">
+        <v>16.149999999999999</v>
+      </c>
+      <c r="I79">
+        <v>18363</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A80">
+        <v>77</v>
+      </c>
+      <c r="B80">
+        <v>-273.25</v>
+      </c>
+      <c r="C80">
+        <v>-74.81</v>
+      </c>
+      <c r="D80">
+        <v>18459</v>
+      </c>
+      <c r="F80">
+        <v>77</v>
+      </c>
+      <c r="G80">
+        <v>300.89</v>
+      </c>
+      <c r="H80">
+        <v>17.309999999999999</v>
+      </c>
+      <c r="I80">
+        <v>18413</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A81">
+        <v>78</v>
+      </c>
+      <c r="B81">
+        <v>-276.91000000000003</v>
+      </c>
+      <c r="C81">
+        <v>-76.989999999999995</v>
+      </c>
+      <c r="D81">
+        <v>18510</v>
+      </c>
+      <c r="F81">
+        <v>78</v>
+      </c>
+      <c r="G81">
+        <v>306.06</v>
+      </c>
+      <c r="H81">
+        <v>18.88</v>
+      </c>
+      <c r="I81">
+        <v>18463</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A82">
+        <v>79</v>
+      </c>
+      <c r="B82">
+        <v>-279.22000000000003</v>
+      </c>
+      <c r="C82">
+        <v>-78.38</v>
+      </c>
+      <c r="D82">
+        <v>18560</v>
+      </c>
+      <c r="F82">
+        <v>79</v>
+      </c>
+      <c r="G82">
+        <v>310.8</v>
+      </c>
+      <c r="H82">
+        <v>20.37</v>
+      </c>
+      <c r="I82">
+        <v>18513</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A83">
+        <v>80</v>
+      </c>
+      <c r="B83">
+        <v>-282.60000000000002</v>
+      </c>
+      <c r="C83">
+        <v>-80.47</v>
+      </c>
+      <c r="D83">
+        <v>18610</v>
+      </c>
+      <c r="F83">
+        <v>80</v>
+      </c>
+      <c r="G83">
+        <v>315.39999999999998</v>
+      </c>
+      <c r="H83">
+        <v>21.86</v>
+      </c>
+      <c r="I83">
+        <v>18563</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A84">
+        <v>81</v>
+      </c>
+      <c r="B84">
+        <v>-284.88</v>
+      </c>
+      <c r="C84">
+        <v>-81.91</v>
+      </c>
+      <c r="D84">
+        <v>18660</v>
+      </c>
+      <c r="F84">
+        <v>81</v>
+      </c>
+      <c r="G84">
+        <v>320.12</v>
+      </c>
+      <c r="H84">
+        <v>23.43</v>
+      </c>
+      <c r="I84">
+        <v>18613</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A85">
+        <v>82</v>
+      </c>
+      <c r="B85">
+        <v>-288.45999999999998</v>
+      </c>
+      <c r="C85">
+        <v>-84.21</v>
+      </c>
+      <c r="D85">
+        <v>18710</v>
+      </c>
+      <c r="F85">
+        <v>82</v>
+      </c>
+      <c r="G85">
+        <v>324.95999999999998</v>
+      </c>
+      <c r="H85">
+        <v>25.08</v>
+      </c>
+      <c r="I85">
+        <v>18663</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A86">
+        <v>83</v>
+      </c>
+      <c r="B86">
+        <v>-290.82</v>
+      </c>
+      <c r="C86">
+        <v>-85.77</v>
+      </c>
+      <c r="D86">
+        <v>18760</v>
+      </c>
+      <c r="F86">
+        <v>83</v>
+      </c>
+      <c r="G86">
+        <v>-325.43</v>
+      </c>
+      <c r="H86">
+        <v>26.81</v>
+      </c>
+      <c r="I86">
+        <v>18722</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A87">
+        <v>84</v>
+      </c>
+      <c r="B87">
+        <v>-294.13</v>
+      </c>
+      <c r="C87">
+        <v>-87.98</v>
+      </c>
+      <c r="D87">
+        <v>18810</v>
+      </c>
+      <c r="F87">
+        <v>84</v>
+      </c>
+      <c r="G87">
+        <v>-324.89999999999998</v>
+      </c>
+      <c r="H87">
+        <v>27</v>
+      </c>
+      <c r="I87">
+        <v>18772</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A88">
+        <v>85</v>
+      </c>
+      <c r="B88">
+        <v>-296.47000000000003</v>
+      </c>
+      <c r="C88">
+        <v>-89.58</v>
+      </c>
+      <c r="D88">
+        <v>18860</v>
+      </c>
+      <c r="F88">
+        <v>85</v>
+      </c>
+      <c r="G88">
+        <v>-325.02999999999997</v>
+      </c>
+      <c r="H88">
+        <v>26.95</v>
+      </c>
+      <c r="I88">
+        <v>18822</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A89">
+        <v>86</v>
+      </c>
+      <c r="B89">
+        <v>-298.8</v>
+      </c>
+      <c r="C89">
+        <v>-91.19</v>
+      </c>
+      <c r="D89">
+        <v>18910</v>
+      </c>
+      <c r="F89">
+        <v>86</v>
+      </c>
+      <c r="G89">
+        <v>-325.02999999999997</v>
+      </c>
+      <c r="H89">
+        <v>26.95</v>
+      </c>
+      <c r="I89">
+        <v>18872</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A90">
+        <v>87</v>
+      </c>
+      <c r="B90">
+        <v>-302.39</v>
+      </c>
+      <c r="C90">
+        <v>-93.74</v>
+      </c>
+      <c r="D90">
+        <v>18960</v>
+      </c>
+      <c r="F90">
+        <v>87</v>
+      </c>
+      <c r="G90">
+        <v>-325.02999999999997</v>
+      </c>
+      <c r="H90">
+        <v>26.95</v>
+      </c>
+      <c r="I90">
+        <v>18922</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="F91">
+        <v>88</v>
+      </c>
+      <c r="G91">
+        <v>-325.02999999999997</v>
+      </c>
+      <c r="H91">
+        <v>26.95</v>
+      </c>
+      <c r="I91">
+        <v>18972</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="F92">
+        <v>89</v>
+      </c>
+      <c r="G92">
+        <v>-325.02999999999997</v>
+      </c>
+      <c r="H92">
+        <v>26.95</v>
+      </c>
+      <c r="I92">
+        <v>19022</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="F93">
+        <v>90</v>
+      </c>
+      <c r="G93">
+        <v>-325.02999999999997</v>
+      </c>
+      <c r="H93">
+        <v>26.95</v>
+      </c>
+      <c r="I93">
+        <v>19073</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="F94">
+        <v>91</v>
+      </c>
+      <c r="G94">
+        <v>-325.02999999999997</v>
+      </c>
+      <c r="H94">
+        <v>26.95</v>
+      </c>
+      <c r="I94">
+        <v>19132</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="F95">
+        <v>92</v>
+      </c>
+      <c r="G95">
+        <v>-325.02999999999997</v>
+      </c>
+      <c r="H95">
+        <v>26.95</v>
+      </c>
+      <c r="I95">
+        <v>19182</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Bump_Sensor_Test/BumpDataArcCentred.xlsx
+++ b/Bump_Sensor_Test/BumpDataArcCentred.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uob-my.sharepoint.com/personal/hp21003_bristol_ac_uk/Documents/Year 4/Robotics/SEMTM0042_43_Group/Bump_Sensor_Test/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="36" documentId="8_{01EBAB60-033A-44EA-9F52-BC9677D5084A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9F33BCF7-5BE3-4C49-8808-85D9792C7979}"/>
+  <xr:revisionPtr revIDLastSave="59" documentId="8_{01EBAB60-033A-44EA-9F52-BC9677D5084A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A76339D1-4F8C-47D9-9868-1DD543EA6DE8}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="8" xr2:uid="{DC0997CF-A461-4C3D-B828-7A4D9066FEE4}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" firstSheet="3" activeTab="11" xr2:uid="{DC0997CF-A461-4C3D-B828-7A4D9066FEE4}"/>
   </bookViews>
   <sheets>
     <sheet name="100mmY0" sheetId="1" r:id="rId1"/>
@@ -22,6 +22,9 @@
     <sheet name="105mmY0" sheetId="7" r:id="rId7"/>
     <sheet name="115mmY0" sheetId="8" r:id="rId8"/>
     <sheet name="115 retest" sheetId="9" r:id="rId9"/>
+    <sheet name="100 retest" sheetId="10" r:id="rId10"/>
+    <sheet name="110 retest " sheetId="12" r:id="rId11"/>
+    <sheet name="120mm" sheetId="13" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="8">
   <si>
     <t>i</t>
   </si>
@@ -62,6 +65,12 @@
   </si>
   <si>
     <t>Follower</t>
+  </si>
+  <si>
+    <t>FOLLOWER KINDA CLOSD THE GAP A LOT AT THE ND FOR THIS ONE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAME THING HERE </t>
   </si>
 </sst>
 </file>
@@ -3017,6 +3026,7578 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CED782D-BB28-44B4-9FB7-1BFC394E9AE7}">
+  <dimension ref="A1:I109"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2" t="s">
+        <v>1</v>
+      </c>
+      <c r="H2" t="s">
+        <v>2</v>
+      </c>
+      <c r="I2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>0</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>17053</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>-0.41</v>
+      </c>
+      <c r="H3">
+        <v>2.5</v>
+      </c>
+      <c r="I3">
+        <v>14422</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>-0.14000000000000001</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>17103</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>-0.41</v>
+      </c>
+      <c r="H4">
+        <v>2.5</v>
+      </c>
+      <c r="I4">
+        <v>14481</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5">
+        <v>-0.99</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>17153</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>-0.41</v>
+      </c>
+      <c r="H5">
+        <v>2.5</v>
+      </c>
+      <c r="I5">
+        <v>14531</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6">
+        <v>-1.7</v>
+      </c>
+      <c r="C6">
+        <v>0.01</v>
+      </c>
+      <c r="D6">
+        <v>17203</v>
+      </c>
+      <c r="F6">
+        <v>3</v>
+      </c>
+      <c r="G6">
+        <v>-0.41</v>
+      </c>
+      <c r="H6">
+        <v>2.5</v>
+      </c>
+      <c r="I6">
+        <v>14581</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>4</v>
+      </c>
+      <c r="B7">
+        <v>-2.97</v>
+      </c>
+      <c r="C7">
+        <v>0.02</v>
+      </c>
+      <c r="D7">
+        <v>17254</v>
+      </c>
+      <c r="F7">
+        <v>4</v>
+      </c>
+      <c r="G7">
+        <v>-0.41</v>
+      </c>
+      <c r="H7">
+        <v>2.5</v>
+      </c>
+      <c r="I7">
+        <v>14631</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>5</v>
+      </c>
+      <c r="B8">
+        <v>-6.8</v>
+      </c>
+      <c r="C8">
+        <v>-0.06</v>
+      </c>
+      <c r="D8">
+        <v>17304</v>
+      </c>
+      <c r="F8">
+        <v>5</v>
+      </c>
+      <c r="G8">
+        <v>-0.41</v>
+      </c>
+      <c r="H8">
+        <v>2.5</v>
+      </c>
+      <c r="I8">
+        <v>14681</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>6</v>
+      </c>
+      <c r="B9">
+        <v>-9.36</v>
+      </c>
+      <c r="C9">
+        <v>-0.12</v>
+      </c>
+      <c r="D9">
+        <v>17354</v>
+      </c>
+      <c r="F9">
+        <v>6</v>
+      </c>
+      <c r="G9">
+        <v>-0.41</v>
+      </c>
+      <c r="H9">
+        <v>2.5</v>
+      </c>
+      <c r="I9">
+        <v>14731</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>7</v>
+      </c>
+      <c r="B10">
+        <v>-13.33</v>
+      </c>
+      <c r="C10">
+        <v>-0.23</v>
+      </c>
+      <c r="D10">
+        <v>17404</v>
+      </c>
+      <c r="F10">
+        <v>7</v>
+      </c>
+      <c r="G10">
+        <v>-0.41</v>
+      </c>
+      <c r="H10">
+        <v>2.5</v>
+      </c>
+      <c r="I10">
+        <v>14781</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>8</v>
+      </c>
+      <c r="B11">
+        <v>-16.02</v>
+      </c>
+      <c r="C11">
+        <v>-0.33</v>
+      </c>
+      <c r="D11">
+        <v>17454</v>
+      </c>
+      <c r="F11">
+        <v>8</v>
+      </c>
+      <c r="G11">
+        <v>-0.41</v>
+      </c>
+      <c r="H11">
+        <v>2.5</v>
+      </c>
+      <c r="I11">
+        <v>14831</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>9</v>
+      </c>
+      <c r="B12">
+        <v>-19.71</v>
+      </c>
+      <c r="C12">
+        <v>-0.48</v>
+      </c>
+      <c r="D12">
+        <v>17504</v>
+      </c>
+      <c r="F12">
+        <v>9</v>
+      </c>
+      <c r="G12">
+        <v>-0.41</v>
+      </c>
+      <c r="H12">
+        <v>2.5</v>
+      </c>
+      <c r="I12">
+        <v>14881</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>10</v>
+      </c>
+      <c r="B13">
+        <v>-21.97</v>
+      </c>
+      <c r="C13">
+        <v>-0.56999999999999995</v>
+      </c>
+      <c r="D13">
+        <v>17554</v>
+      </c>
+      <c r="F13">
+        <v>10</v>
+      </c>
+      <c r="G13">
+        <v>-0.41</v>
+      </c>
+      <c r="H13">
+        <v>2.5</v>
+      </c>
+      <c r="I13">
+        <v>14931</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>11</v>
+      </c>
+      <c r="B14">
+        <v>-25.94</v>
+      </c>
+      <c r="C14">
+        <v>-0.76</v>
+      </c>
+      <c r="D14">
+        <v>17605</v>
+      </c>
+      <c r="F14">
+        <v>11</v>
+      </c>
+      <c r="G14">
+        <v>-0.26</v>
+      </c>
+      <c r="H14">
+        <v>2.5</v>
+      </c>
+      <c r="I14">
+        <v>14982</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>12</v>
+      </c>
+      <c r="B15">
+        <v>-28.63</v>
+      </c>
+      <c r="C15">
+        <v>-0.9</v>
+      </c>
+      <c r="D15">
+        <v>17655</v>
+      </c>
+      <c r="F15">
+        <v>12</v>
+      </c>
+      <c r="G15">
+        <v>-0.26</v>
+      </c>
+      <c r="H15">
+        <v>2.5</v>
+      </c>
+      <c r="I15">
+        <v>15032</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>13</v>
+      </c>
+      <c r="B16">
+        <v>-32.6</v>
+      </c>
+      <c r="C16">
+        <v>-1.1399999999999999</v>
+      </c>
+      <c r="D16">
+        <v>17705</v>
+      </c>
+      <c r="F16">
+        <v>13</v>
+      </c>
+      <c r="G16">
+        <v>-0.26</v>
+      </c>
+      <c r="H16">
+        <v>2.5</v>
+      </c>
+      <c r="I16">
+        <v>15082</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>14</v>
+      </c>
+      <c r="B17">
+        <v>-35.29</v>
+      </c>
+      <c r="C17">
+        <v>-1.32</v>
+      </c>
+      <c r="D17">
+        <v>17755</v>
+      </c>
+      <c r="F17">
+        <v>14</v>
+      </c>
+      <c r="G17">
+        <v>-0.26</v>
+      </c>
+      <c r="H17">
+        <v>2.5</v>
+      </c>
+      <c r="I17">
+        <v>15132</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>15</v>
+      </c>
+      <c r="B18">
+        <v>-39.25</v>
+      </c>
+      <c r="C18">
+        <v>-1.62</v>
+      </c>
+      <c r="D18">
+        <v>17805</v>
+      </c>
+      <c r="F18">
+        <v>15</v>
+      </c>
+      <c r="G18">
+        <v>-0.26</v>
+      </c>
+      <c r="H18">
+        <v>2.5</v>
+      </c>
+      <c r="I18">
+        <v>15182</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>16</v>
+      </c>
+      <c r="B19">
+        <v>-41.79</v>
+      </c>
+      <c r="C19">
+        <v>-1.83</v>
+      </c>
+      <c r="D19">
+        <v>17855</v>
+      </c>
+      <c r="F19">
+        <v>16</v>
+      </c>
+      <c r="G19">
+        <v>-0.26</v>
+      </c>
+      <c r="H19">
+        <v>2.5</v>
+      </c>
+      <c r="I19">
+        <v>15234</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>17</v>
+      </c>
+      <c r="B20">
+        <v>-46.03</v>
+      </c>
+      <c r="C20">
+        <v>-2.2000000000000002</v>
+      </c>
+      <c r="D20">
+        <v>17905</v>
+      </c>
+      <c r="F20">
+        <v>17</v>
+      </c>
+      <c r="G20">
+        <v>-0.26</v>
+      </c>
+      <c r="H20">
+        <v>2.5</v>
+      </c>
+      <c r="I20">
+        <v>15293</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>18</v>
+      </c>
+      <c r="B21">
+        <v>-48.72</v>
+      </c>
+      <c r="C21">
+        <v>-2.4500000000000002</v>
+      </c>
+      <c r="D21">
+        <v>17956</v>
+      </c>
+      <c r="F21">
+        <v>18</v>
+      </c>
+      <c r="G21">
+        <v>-0.26</v>
+      </c>
+      <c r="H21">
+        <v>2.5</v>
+      </c>
+      <c r="I21">
+        <v>15343</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>19</v>
+      </c>
+      <c r="B22">
+        <v>-52.95</v>
+      </c>
+      <c r="C22">
+        <v>-2.88</v>
+      </c>
+      <c r="D22">
+        <v>18006</v>
+      </c>
+      <c r="F22">
+        <v>19</v>
+      </c>
+      <c r="G22">
+        <v>-0.26</v>
+      </c>
+      <c r="H22">
+        <v>2.5</v>
+      </c>
+      <c r="I22">
+        <v>15393</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>20</v>
+      </c>
+      <c r="B23">
+        <v>-55.91</v>
+      </c>
+      <c r="C23">
+        <v>-3.21</v>
+      </c>
+      <c r="D23">
+        <v>18057</v>
+      </c>
+      <c r="F23">
+        <v>20</v>
+      </c>
+      <c r="G23">
+        <v>-0.26</v>
+      </c>
+      <c r="H23">
+        <v>2.5</v>
+      </c>
+      <c r="I23">
+        <v>15444</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>21</v>
+      </c>
+      <c r="B24">
+        <v>-59.58</v>
+      </c>
+      <c r="C24">
+        <v>-3.62</v>
+      </c>
+      <c r="D24">
+        <v>18108</v>
+      </c>
+      <c r="F24">
+        <v>21</v>
+      </c>
+      <c r="G24">
+        <v>-0.26</v>
+      </c>
+      <c r="H24">
+        <v>2.5</v>
+      </c>
+      <c r="I24">
+        <v>15494</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>22</v>
+      </c>
+      <c r="B25">
+        <v>-62.26</v>
+      </c>
+      <c r="C25">
+        <v>-3.94</v>
+      </c>
+      <c r="D25">
+        <v>18158</v>
+      </c>
+      <c r="F25">
+        <v>22</v>
+      </c>
+      <c r="G25">
+        <v>-0.26</v>
+      </c>
+      <c r="H25">
+        <v>2.5</v>
+      </c>
+      <c r="I25">
+        <v>15544</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>23</v>
+      </c>
+      <c r="B26">
+        <v>-66.34</v>
+      </c>
+      <c r="C26">
+        <v>-4.47</v>
+      </c>
+      <c r="D26">
+        <v>18209</v>
+      </c>
+      <c r="F26">
+        <v>23</v>
+      </c>
+      <c r="G26">
+        <v>0.44</v>
+      </c>
+      <c r="H26">
+        <v>2.5299999999999998</v>
+      </c>
+      <c r="I26">
+        <v>15595</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>24</v>
+      </c>
+      <c r="B27">
+        <v>-69.010000000000005</v>
+      </c>
+      <c r="C27">
+        <v>-4.82</v>
+      </c>
+      <c r="D27">
+        <v>18259</v>
+      </c>
+      <c r="F27">
+        <v>24</v>
+      </c>
+      <c r="G27">
+        <v>2.14</v>
+      </c>
+      <c r="H27">
+        <v>2.57</v>
+      </c>
+      <c r="I27">
+        <v>15645</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>25</v>
+      </c>
+      <c r="B28">
+        <v>-73.5</v>
+      </c>
+      <c r="C28">
+        <v>-5.45</v>
+      </c>
+      <c r="D28">
+        <v>18309</v>
+      </c>
+      <c r="F28">
+        <v>25</v>
+      </c>
+      <c r="G28">
+        <v>4.9800000000000004</v>
+      </c>
+      <c r="H28">
+        <v>2.64</v>
+      </c>
+      <c r="I28">
+        <v>15695</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>26</v>
+      </c>
+      <c r="B29">
+        <v>-76.31</v>
+      </c>
+      <c r="C29">
+        <v>-5.85</v>
+      </c>
+      <c r="D29">
+        <v>18359</v>
+      </c>
+      <c r="F29">
+        <v>26</v>
+      </c>
+      <c r="G29">
+        <v>8.39</v>
+      </c>
+      <c r="H29">
+        <v>2.71</v>
+      </c>
+      <c r="I29">
+        <v>15746</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>27</v>
+      </c>
+      <c r="B30">
+        <v>-80.52</v>
+      </c>
+      <c r="C30">
+        <v>-6.5</v>
+      </c>
+      <c r="D30">
+        <v>18409</v>
+      </c>
+      <c r="F30">
+        <v>27</v>
+      </c>
+      <c r="G30">
+        <v>12.94</v>
+      </c>
+      <c r="H30">
+        <v>2.82</v>
+      </c>
+      <c r="I30">
+        <v>15805</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>28</v>
+      </c>
+      <c r="B31">
+        <v>-83.46</v>
+      </c>
+      <c r="C31">
+        <v>-6.96</v>
+      </c>
+      <c r="D31">
+        <v>18459</v>
+      </c>
+      <c r="F31">
+        <v>28</v>
+      </c>
+      <c r="G31">
+        <v>16.77</v>
+      </c>
+      <c r="H31">
+        <v>2.92</v>
+      </c>
+      <c r="I31">
+        <v>15855</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>29</v>
+      </c>
+      <c r="B32">
+        <v>-87.8</v>
+      </c>
+      <c r="C32">
+        <v>-7.67</v>
+      </c>
+      <c r="D32">
+        <v>18509</v>
+      </c>
+      <c r="F32">
+        <v>29</v>
+      </c>
+      <c r="G32">
+        <v>20.47</v>
+      </c>
+      <c r="H32">
+        <v>3.02</v>
+      </c>
+      <c r="I32">
+        <v>15905</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>30</v>
+      </c>
+      <c r="B33">
+        <v>-90.74</v>
+      </c>
+      <c r="C33">
+        <v>-8.17</v>
+      </c>
+      <c r="D33">
+        <v>18560</v>
+      </c>
+      <c r="F33">
+        <v>30</v>
+      </c>
+      <c r="G33">
+        <v>24.3</v>
+      </c>
+      <c r="H33">
+        <v>3.14</v>
+      </c>
+      <c r="I33">
+        <v>15955</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A34">
+        <v>31</v>
+      </c>
+      <c r="B34">
+        <v>-95.21</v>
+      </c>
+      <c r="C34">
+        <v>-8.9600000000000009</v>
+      </c>
+      <c r="D34">
+        <v>18610</v>
+      </c>
+      <c r="F34">
+        <v>31</v>
+      </c>
+      <c r="G34">
+        <v>29.13</v>
+      </c>
+      <c r="H34">
+        <v>3.29</v>
+      </c>
+      <c r="I34">
+        <v>16015</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A35">
+        <v>32</v>
+      </c>
+      <c r="B35">
+        <v>-98.14</v>
+      </c>
+      <c r="C35">
+        <v>-9.49</v>
+      </c>
+      <c r="D35">
+        <v>18661</v>
+      </c>
+      <c r="F35">
+        <v>32</v>
+      </c>
+      <c r="G35">
+        <v>33.25</v>
+      </c>
+      <c r="H35">
+        <v>3.42</v>
+      </c>
+      <c r="I35">
+        <v>16065</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A36">
+        <v>33</v>
+      </c>
+      <c r="B36">
+        <v>-102.46</v>
+      </c>
+      <c r="C36">
+        <v>-10.3</v>
+      </c>
+      <c r="D36">
+        <v>18711</v>
+      </c>
+      <c r="F36">
+        <v>33</v>
+      </c>
+      <c r="G36">
+        <v>37.08</v>
+      </c>
+      <c r="H36">
+        <v>3.55</v>
+      </c>
+      <c r="I36">
+        <v>16115</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A37">
+        <v>34</v>
+      </c>
+      <c r="B37">
+        <v>-105.53</v>
+      </c>
+      <c r="C37">
+        <v>-10.9</v>
+      </c>
+      <c r="D37">
+        <v>18761</v>
+      </c>
+      <c r="F37">
+        <v>34</v>
+      </c>
+      <c r="G37">
+        <v>42.19</v>
+      </c>
+      <c r="H37">
+        <v>3.74</v>
+      </c>
+      <c r="I37">
+        <v>16175</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A38">
+        <v>35</v>
+      </c>
+      <c r="B38">
+        <v>-109.83</v>
+      </c>
+      <c r="C38">
+        <v>-11.79</v>
+      </c>
+      <c r="D38">
+        <v>18811</v>
+      </c>
+      <c r="F38">
+        <v>35</v>
+      </c>
+      <c r="G38">
+        <v>47.31</v>
+      </c>
+      <c r="H38">
+        <v>3.93</v>
+      </c>
+      <c r="I38">
+        <v>16234</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A39">
+        <v>36</v>
+      </c>
+      <c r="B39">
+        <v>-112.89</v>
+      </c>
+      <c r="C39">
+        <v>-12.44</v>
+      </c>
+      <c r="D39">
+        <v>18861</v>
+      </c>
+      <c r="F39">
+        <v>36</v>
+      </c>
+      <c r="G39">
+        <v>51.42</v>
+      </c>
+      <c r="H39">
+        <v>4.09</v>
+      </c>
+      <c r="I39">
+        <v>16284</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A40">
+        <v>37</v>
+      </c>
+      <c r="B40">
+        <v>-117.32</v>
+      </c>
+      <c r="C40">
+        <v>-13.42</v>
+      </c>
+      <c r="D40">
+        <v>18911</v>
+      </c>
+      <c r="F40">
+        <v>37</v>
+      </c>
+      <c r="G40">
+        <v>55.68</v>
+      </c>
+      <c r="H40">
+        <v>4.26</v>
+      </c>
+      <c r="I40">
+        <v>16334</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A41">
+        <v>38</v>
+      </c>
+      <c r="B41">
+        <v>-120.5</v>
+      </c>
+      <c r="C41">
+        <v>-14.14</v>
+      </c>
+      <c r="D41">
+        <v>18961</v>
+      </c>
+      <c r="F41">
+        <v>38</v>
+      </c>
+      <c r="G41">
+        <v>60.08</v>
+      </c>
+      <c r="H41">
+        <v>4.45</v>
+      </c>
+      <c r="I41">
+        <v>16385</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A42">
+        <v>39</v>
+      </c>
+      <c r="B42">
+        <v>-125.2</v>
+      </c>
+      <c r="C42">
+        <v>-15.25</v>
+      </c>
+      <c r="D42">
+        <v>19011</v>
+      </c>
+      <c r="F42">
+        <v>39</v>
+      </c>
+      <c r="G42">
+        <v>65.34</v>
+      </c>
+      <c r="H42">
+        <v>4.6900000000000004</v>
+      </c>
+      <c r="I42">
+        <v>16444</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A43">
+        <v>40</v>
+      </c>
+      <c r="B43">
+        <v>-128.37</v>
+      </c>
+      <c r="C43">
+        <v>-16.02</v>
+      </c>
+      <c r="D43">
+        <v>19061</v>
+      </c>
+      <c r="F43">
+        <v>40</v>
+      </c>
+      <c r="G43">
+        <v>69.45</v>
+      </c>
+      <c r="H43">
+        <v>4.88</v>
+      </c>
+      <c r="I43">
+        <v>16494</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A44">
+        <v>41</v>
+      </c>
+      <c r="B44">
+        <v>-133.18</v>
+      </c>
+      <c r="C44">
+        <v>-17.22</v>
+      </c>
+      <c r="D44">
+        <v>19111</v>
+      </c>
+      <c r="F44">
+        <v>41</v>
+      </c>
+      <c r="G44">
+        <v>73.989999999999995</v>
+      </c>
+      <c r="H44">
+        <v>5.1100000000000003</v>
+      </c>
+      <c r="I44">
+        <v>16544</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A45">
+        <v>42</v>
+      </c>
+      <c r="B45">
+        <v>-136.19999999999999</v>
+      </c>
+      <c r="C45">
+        <v>-18.010000000000002</v>
+      </c>
+      <c r="D45">
+        <v>19161</v>
+      </c>
+      <c r="F45">
+        <v>42</v>
+      </c>
+      <c r="G45">
+        <v>78.25</v>
+      </c>
+      <c r="H45">
+        <v>5.32</v>
+      </c>
+      <c r="I45">
+        <v>16594</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A46">
+        <v>43</v>
+      </c>
+      <c r="B46">
+        <v>-140.86000000000001</v>
+      </c>
+      <c r="C46">
+        <v>-19.25</v>
+      </c>
+      <c r="D46">
+        <v>19211</v>
+      </c>
+      <c r="F46">
+        <v>43</v>
+      </c>
+      <c r="G46">
+        <v>82.79</v>
+      </c>
+      <c r="H46">
+        <v>5.54</v>
+      </c>
+      <c r="I46">
+        <v>16644</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A47">
+        <v>44</v>
+      </c>
+      <c r="B47">
+        <v>-144.01</v>
+      </c>
+      <c r="C47">
+        <v>-20.11</v>
+      </c>
+      <c r="D47">
+        <v>19261</v>
+      </c>
+      <c r="F47">
+        <v>44</v>
+      </c>
+      <c r="G47">
+        <v>87.33</v>
+      </c>
+      <c r="H47">
+        <v>5.77</v>
+      </c>
+      <c r="I47">
+        <v>16694</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A48">
+        <v>45</v>
+      </c>
+      <c r="B48">
+        <v>-148.79</v>
+      </c>
+      <c r="C48">
+        <v>-21.45</v>
+      </c>
+      <c r="D48">
+        <v>19312</v>
+      </c>
+      <c r="F48">
+        <v>45</v>
+      </c>
+      <c r="G48">
+        <v>91.87</v>
+      </c>
+      <c r="H48">
+        <v>6.01</v>
+      </c>
+      <c r="I48">
+        <v>16744</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A49">
+        <v>46</v>
+      </c>
+      <c r="B49">
+        <v>-152.06</v>
+      </c>
+      <c r="C49">
+        <v>-22.4</v>
+      </c>
+      <c r="D49">
+        <v>19362</v>
+      </c>
+      <c r="F49">
+        <v>46</v>
+      </c>
+      <c r="G49">
+        <v>96.41</v>
+      </c>
+      <c r="H49">
+        <v>6.27</v>
+      </c>
+      <c r="I49">
+        <v>16794</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A50">
+        <v>47</v>
+      </c>
+      <c r="B50">
+        <v>-156.69</v>
+      </c>
+      <c r="C50">
+        <v>-23.78</v>
+      </c>
+      <c r="D50">
+        <v>19412</v>
+      </c>
+      <c r="F50">
+        <v>47</v>
+      </c>
+      <c r="G50">
+        <v>100.95</v>
+      </c>
+      <c r="H50">
+        <v>6.55</v>
+      </c>
+      <c r="I50">
+        <v>16844</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A51">
+        <v>48</v>
+      </c>
+      <c r="B51">
+        <v>-159.81</v>
+      </c>
+      <c r="C51">
+        <v>-24.73</v>
+      </c>
+      <c r="D51">
+        <v>19462</v>
+      </c>
+      <c r="F51">
+        <v>48</v>
+      </c>
+      <c r="G51">
+        <v>105.63</v>
+      </c>
+      <c r="H51">
+        <v>6.85</v>
+      </c>
+      <c r="I51">
+        <v>16894</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A52">
+        <v>49</v>
+      </c>
+      <c r="B52">
+        <v>-164.55</v>
+      </c>
+      <c r="C52">
+        <v>-26.21</v>
+      </c>
+      <c r="D52">
+        <v>19512</v>
+      </c>
+      <c r="F52">
+        <v>49</v>
+      </c>
+      <c r="G52">
+        <v>110.17</v>
+      </c>
+      <c r="H52">
+        <v>7.17</v>
+      </c>
+      <c r="I52">
+        <v>16944</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A53">
+        <v>50</v>
+      </c>
+      <c r="B53">
+        <v>-167.65</v>
+      </c>
+      <c r="C53">
+        <v>-27.21</v>
+      </c>
+      <c r="D53">
+        <v>19562</v>
+      </c>
+      <c r="F53">
+        <v>50</v>
+      </c>
+      <c r="G53">
+        <v>115.98</v>
+      </c>
+      <c r="H53">
+        <v>7.6</v>
+      </c>
+      <c r="I53">
+        <v>17003</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A54">
+        <v>51</v>
+      </c>
+      <c r="B54">
+        <v>-172.5</v>
+      </c>
+      <c r="C54">
+        <v>-28.81</v>
+      </c>
+      <c r="D54">
+        <v>19612</v>
+      </c>
+      <c r="F54">
+        <v>51</v>
+      </c>
+      <c r="G54">
+        <v>120.51</v>
+      </c>
+      <c r="H54">
+        <v>7.96</v>
+      </c>
+      <c r="I54">
+        <v>17053</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A55">
+        <v>52</v>
+      </c>
+      <c r="B55">
+        <v>-175.73</v>
+      </c>
+      <c r="C55">
+        <v>-29.89</v>
+      </c>
+      <c r="D55">
+        <v>19662</v>
+      </c>
+      <c r="F55">
+        <v>52</v>
+      </c>
+      <c r="G55">
+        <v>125.18</v>
+      </c>
+      <c r="H55">
+        <v>8.3699999999999992</v>
+      </c>
+      <c r="I55">
+        <v>17103</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A56">
+        <v>53</v>
+      </c>
+      <c r="B56">
+        <v>-180.56</v>
+      </c>
+      <c r="C56">
+        <v>-31.55</v>
+      </c>
+      <c r="D56">
+        <v>19712</v>
+      </c>
+      <c r="F56">
+        <v>53</v>
+      </c>
+      <c r="G56">
+        <v>129.85</v>
+      </c>
+      <c r="H56">
+        <v>8.7899999999999991</v>
+      </c>
+      <c r="I56">
+        <v>17154</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A57">
+        <v>54</v>
+      </c>
+      <c r="B57">
+        <v>-183.77</v>
+      </c>
+      <c r="C57">
+        <v>-32.68</v>
+      </c>
+      <c r="D57">
+        <v>19762</v>
+      </c>
+      <c r="F57">
+        <v>54</v>
+      </c>
+      <c r="G57">
+        <v>135.51</v>
+      </c>
+      <c r="H57">
+        <v>9.36</v>
+      </c>
+      <c r="I57">
+        <v>17213</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A58">
+        <v>55</v>
+      </c>
+      <c r="B58">
+        <v>-188.58</v>
+      </c>
+      <c r="C58">
+        <v>-34.409999999999997</v>
+      </c>
+      <c r="D58">
+        <v>19812</v>
+      </c>
+      <c r="F58">
+        <v>55</v>
+      </c>
+      <c r="G58">
+        <v>140.31</v>
+      </c>
+      <c r="H58">
+        <v>9.8699999999999992</v>
+      </c>
+      <c r="I58">
+        <v>17263</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A59">
+        <v>56</v>
+      </c>
+      <c r="B59">
+        <v>-191.77</v>
+      </c>
+      <c r="C59">
+        <v>-35.590000000000003</v>
+      </c>
+      <c r="D59">
+        <v>19862</v>
+      </c>
+      <c r="F59">
+        <v>56</v>
+      </c>
+      <c r="G59">
+        <v>145.11000000000001</v>
+      </c>
+      <c r="H59">
+        <v>10.41</v>
+      </c>
+      <c r="I59">
+        <v>17313</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A60">
+        <v>57</v>
+      </c>
+      <c r="B60">
+        <v>-196.69</v>
+      </c>
+      <c r="C60">
+        <v>-37.44</v>
+      </c>
+      <c r="D60">
+        <v>19912</v>
+      </c>
+      <c r="F60">
+        <v>57</v>
+      </c>
+      <c r="G60">
+        <v>149.77000000000001</v>
+      </c>
+      <c r="H60">
+        <v>10.97</v>
+      </c>
+      <c r="I60">
+        <v>17363</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A61">
+        <v>58</v>
+      </c>
+      <c r="B61">
+        <v>-199.86</v>
+      </c>
+      <c r="C61">
+        <v>-38.659999999999997</v>
+      </c>
+      <c r="D61">
+        <v>19963</v>
+      </c>
+      <c r="F61">
+        <v>58</v>
+      </c>
+      <c r="G61">
+        <v>154.56</v>
+      </c>
+      <c r="H61">
+        <v>11.56</v>
+      </c>
+      <c r="I61">
+        <v>17413</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A62">
+        <v>59</v>
+      </c>
+      <c r="B62">
+        <v>-204.88</v>
+      </c>
+      <c r="C62">
+        <v>-40.64</v>
+      </c>
+      <c r="D62">
+        <v>20013</v>
+      </c>
+      <c r="F62">
+        <v>59</v>
+      </c>
+      <c r="G62">
+        <v>159.21</v>
+      </c>
+      <c r="H62">
+        <v>12.17</v>
+      </c>
+      <c r="I62">
+        <v>17463</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A63">
+        <v>60</v>
+      </c>
+      <c r="B63">
+        <v>-208.17</v>
+      </c>
+      <c r="C63">
+        <v>-41.97</v>
+      </c>
+      <c r="D63">
+        <v>20063</v>
+      </c>
+      <c r="F63">
+        <v>60</v>
+      </c>
+      <c r="G63">
+        <v>164</v>
+      </c>
+      <c r="H63">
+        <v>12.84</v>
+      </c>
+      <c r="I63">
+        <v>17513</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A64">
+        <v>61</v>
+      </c>
+      <c r="B64">
+        <v>-212.89</v>
+      </c>
+      <c r="C64">
+        <v>-43.92</v>
+      </c>
+      <c r="D64">
+        <v>20114</v>
+      </c>
+      <c r="F64">
+        <v>61</v>
+      </c>
+      <c r="G64">
+        <v>168.77</v>
+      </c>
+      <c r="H64">
+        <v>13.56</v>
+      </c>
+      <c r="I64">
+        <v>17563</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A65">
+        <v>62</v>
+      </c>
+      <c r="B65">
+        <v>-216.15</v>
+      </c>
+      <c r="C65">
+        <v>-45.3</v>
+      </c>
+      <c r="D65">
+        <v>20164</v>
+      </c>
+      <c r="F65">
+        <v>62</v>
+      </c>
+      <c r="G65">
+        <v>173.69</v>
+      </c>
+      <c r="H65">
+        <v>14.31</v>
+      </c>
+      <c r="I65">
+        <v>17613</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A66">
+        <v>63</v>
+      </c>
+      <c r="B66">
+        <v>-221.23</v>
+      </c>
+      <c r="C66">
+        <v>-47.5</v>
+      </c>
+      <c r="D66">
+        <v>20214</v>
+      </c>
+      <c r="F66">
+        <v>63</v>
+      </c>
+      <c r="G66">
+        <v>178.32</v>
+      </c>
+      <c r="H66">
+        <v>15.04</v>
+      </c>
+      <c r="I66">
+        <v>17664</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A67">
+        <v>64</v>
+      </c>
+      <c r="B67">
+        <v>-224.34</v>
+      </c>
+      <c r="C67">
+        <v>-48.89</v>
+      </c>
+      <c r="D67">
+        <v>20264</v>
+      </c>
+      <c r="F67">
+        <v>64</v>
+      </c>
+      <c r="G67">
+        <v>184.07</v>
+      </c>
+      <c r="H67">
+        <v>15.98</v>
+      </c>
+      <c r="I67">
+        <v>17723</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A68">
+        <v>65</v>
+      </c>
+      <c r="B68">
+        <v>-229.25</v>
+      </c>
+      <c r="C68">
+        <v>-51.12</v>
+      </c>
+      <c r="D68">
+        <v>20314</v>
+      </c>
+      <c r="F68">
+        <v>65</v>
+      </c>
+      <c r="G68">
+        <v>188.27</v>
+      </c>
+      <c r="H68">
+        <v>16.7</v>
+      </c>
+      <c r="I68">
+        <v>17773</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A69">
+        <v>66</v>
+      </c>
+      <c r="B69">
+        <v>-232.47</v>
+      </c>
+      <c r="C69">
+        <v>-52.6</v>
+      </c>
+      <c r="D69">
+        <v>20364</v>
+      </c>
+      <c r="F69">
+        <v>66</v>
+      </c>
+      <c r="G69">
+        <v>193.17</v>
+      </c>
+      <c r="H69">
+        <v>17.559999999999999</v>
+      </c>
+      <c r="I69">
+        <v>17823</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A70">
+        <v>67</v>
+      </c>
+      <c r="B70">
+        <v>-237.48</v>
+      </c>
+      <c r="C70">
+        <v>-54.94</v>
+      </c>
+      <c r="D70">
+        <v>20415</v>
+      </c>
+      <c r="F70">
+        <v>67</v>
+      </c>
+      <c r="G70">
+        <v>197.92</v>
+      </c>
+      <c r="H70">
+        <v>18.43</v>
+      </c>
+      <c r="I70">
+        <v>17873</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A71">
+        <v>68</v>
+      </c>
+      <c r="B71">
+        <v>-240.55</v>
+      </c>
+      <c r="C71">
+        <v>-56.41</v>
+      </c>
+      <c r="D71">
+        <v>20465</v>
+      </c>
+      <c r="F71">
+        <v>68</v>
+      </c>
+      <c r="G71">
+        <v>202.67</v>
+      </c>
+      <c r="H71">
+        <v>19.34</v>
+      </c>
+      <c r="I71">
+        <v>17923</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A72">
+        <v>69</v>
+      </c>
+      <c r="B72">
+        <v>-245.4</v>
+      </c>
+      <c r="C72">
+        <v>-58.77</v>
+      </c>
+      <c r="D72">
+        <v>20515</v>
+      </c>
+      <c r="F72">
+        <v>69</v>
+      </c>
+      <c r="G72">
+        <v>207.26</v>
+      </c>
+      <c r="H72">
+        <v>20.27</v>
+      </c>
+      <c r="I72">
+        <v>17973</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A73">
+        <v>70</v>
+      </c>
+      <c r="B73">
+        <v>-248.71</v>
+      </c>
+      <c r="C73">
+        <v>-60.4</v>
+      </c>
+      <c r="D73">
+        <v>20566</v>
+      </c>
+      <c r="F73">
+        <v>70</v>
+      </c>
+      <c r="G73">
+        <v>212.13</v>
+      </c>
+      <c r="H73">
+        <v>21.31</v>
+      </c>
+      <c r="I73">
+        <v>18023</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A74">
+        <v>71</v>
+      </c>
+      <c r="B74">
+        <v>-253.4</v>
+      </c>
+      <c r="C74">
+        <v>-62.77</v>
+      </c>
+      <c r="D74">
+        <v>20616</v>
+      </c>
+      <c r="F74">
+        <v>71</v>
+      </c>
+      <c r="G74">
+        <v>216.84</v>
+      </c>
+      <c r="H74">
+        <v>22.37</v>
+      </c>
+      <c r="I74">
+        <v>18073</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A75">
+        <v>72</v>
+      </c>
+      <c r="B75">
+        <v>-256.67</v>
+      </c>
+      <c r="C75">
+        <v>-64.45</v>
+      </c>
+      <c r="D75">
+        <v>20666</v>
+      </c>
+      <c r="F75">
+        <v>72</v>
+      </c>
+      <c r="G75">
+        <v>222.65</v>
+      </c>
+      <c r="H75">
+        <v>23.73</v>
+      </c>
+      <c r="I75">
+        <v>18134</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A76">
+        <v>73</v>
+      </c>
+      <c r="B76">
+        <v>-261.57</v>
+      </c>
+      <c r="C76">
+        <v>-67.040000000000006</v>
+      </c>
+      <c r="D76">
+        <v>20716</v>
+      </c>
+      <c r="F76">
+        <v>73</v>
+      </c>
+      <c r="G76">
+        <v>228.45</v>
+      </c>
+      <c r="H76">
+        <v>25.16</v>
+      </c>
+      <c r="I76">
+        <v>18192</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A77">
+        <v>74</v>
+      </c>
+      <c r="B77">
+        <v>-264.57</v>
+      </c>
+      <c r="C77">
+        <v>-68.650000000000006</v>
+      </c>
+      <c r="D77">
+        <v>20766</v>
+      </c>
+      <c r="F77">
+        <v>74</v>
+      </c>
+      <c r="G77">
+        <v>233.12</v>
+      </c>
+      <c r="H77">
+        <v>26.39</v>
+      </c>
+      <c r="I77">
+        <v>18242</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A78">
+        <v>75</v>
+      </c>
+      <c r="B78">
+        <v>-267.8</v>
+      </c>
+      <c r="C78">
+        <v>-70.430000000000007</v>
+      </c>
+      <c r="D78">
+        <v>20816</v>
+      </c>
+      <c r="F78">
+        <v>75</v>
+      </c>
+      <c r="G78">
+        <v>237.91</v>
+      </c>
+      <c r="H78">
+        <v>-627.65</v>
+      </c>
+      <c r="I78">
+        <v>18292</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A79">
+        <v>76</v>
+      </c>
+      <c r="B79">
+        <v>-270.52</v>
+      </c>
+      <c r="C79">
+        <v>-71.959999999999994</v>
+      </c>
+      <c r="D79">
+        <v>20866</v>
+      </c>
+      <c r="F79">
+        <v>76</v>
+      </c>
+      <c r="G79">
+        <v>242.7</v>
+      </c>
+      <c r="H79">
+        <v>-626.29999999999995</v>
+      </c>
+      <c r="I79">
+        <v>18342</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A80">
+        <v>77</v>
+      </c>
+      <c r="B80">
+        <v>-273.72000000000003</v>
+      </c>
+      <c r="C80">
+        <v>-73.790000000000006</v>
+      </c>
+      <c r="D80">
+        <v>20916</v>
+      </c>
+      <c r="F80">
+        <v>77</v>
+      </c>
+      <c r="G80">
+        <v>247.47</v>
+      </c>
+      <c r="H80">
+        <v>-624.91</v>
+      </c>
+      <c r="I80">
+        <v>18392</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A81">
+        <v>78</v>
+      </c>
+      <c r="B81">
+        <v>-276.06</v>
+      </c>
+      <c r="C81">
+        <v>-75.13</v>
+      </c>
+      <c r="D81">
+        <v>20966</v>
+      </c>
+      <c r="F81">
+        <v>78</v>
+      </c>
+      <c r="G81">
+        <v>252.1</v>
+      </c>
+      <c r="H81">
+        <v>-623.51</v>
+      </c>
+      <c r="I81">
+        <v>18442</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A82">
+        <v>79</v>
+      </c>
+      <c r="B82">
+        <v>-279.72000000000003</v>
+      </c>
+      <c r="C82">
+        <v>-77.3</v>
+      </c>
+      <c r="D82">
+        <v>21016</v>
+      </c>
+      <c r="F82">
+        <v>79</v>
+      </c>
+      <c r="G82">
+        <v>256.70999999999998</v>
+      </c>
+      <c r="H82">
+        <v>-622.05999999999995</v>
+      </c>
+      <c r="I82">
+        <v>18492</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A83">
+        <v>80</v>
+      </c>
+      <c r="B83">
+        <v>-282.14999999999998</v>
+      </c>
+      <c r="C83">
+        <v>-78.760000000000005</v>
+      </c>
+      <c r="D83">
+        <v>21066</v>
+      </c>
+      <c r="F83">
+        <v>80</v>
+      </c>
+      <c r="G83">
+        <v>261.58</v>
+      </c>
+      <c r="H83">
+        <v>-620.49</v>
+      </c>
+      <c r="I83">
+        <v>18542</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A84">
+        <v>81</v>
+      </c>
+      <c r="B84">
+        <v>-285.66000000000003</v>
+      </c>
+      <c r="C84">
+        <v>-80.91</v>
+      </c>
+      <c r="D84">
+        <v>21116</v>
+      </c>
+      <c r="F84">
+        <v>81</v>
+      </c>
+      <c r="G84">
+        <v>266.16000000000003</v>
+      </c>
+      <c r="H84">
+        <v>-618.96</v>
+      </c>
+      <c r="I84">
+        <v>18592</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A85">
+        <v>82</v>
+      </c>
+      <c r="B85">
+        <v>-288.07</v>
+      </c>
+      <c r="C85">
+        <v>-82.41</v>
+      </c>
+      <c r="D85">
+        <v>21166</v>
+      </c>
+      <c r="F85">
+        <v>82</v>
+      </c>
+      <c r="G85">
+        <v>270.73</v>
+      </c>
+      <c r="H85">
+        <v>-617.4</v>
+      </c>
+      <c r="I85">
+        <v>18642</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A86">
+        <v>83</v>
+      </c>
+      <c r="B86">
+        <v>-291.42</v>
+      </c>
+      <c r="C86">
+        <v>-84.54</v>
+      </c>
+      <c r="D86">
+        <v>21216</v>
+      </c>
+      <c r="F86">
+        <v>83</v>
+      </c>
+      <c r="G86">
+        <v>275.14999999999998</v>
+      </c>
+      <c r="H86">
+        <v>-615.84</v>
+      </c>
+      <c r="I86">
+        <v>18692</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A87">
+        <v>84</v>
+      </c>
+      <c r="B87">
+        <v>-293.81</v>
+      </c>
+      <c r="C87">
+        <v>-86.07</v>
+      </c>
+      <c r="D87">
+        <v>21266</v>
+      </c>
+      <c r="F87">
+        <v>84</v>
+      </c>
+      <c r="G87">
+        <v>279.95999999999998</v>
+      </c>
+      <c r="H87">
+        <v>-614.1</v>
+      </c>
+      <c r="I87">
+        <v>18742</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A88">
+        <v>85</v>
+      </c>
+      <c r="B88">
+        <v>-297.36</v>
+      </c>
+      <c r="C88">
+        <v>-88.42</v>
+      </c>
+      <c r="D88">
+        <v>21316</v>
+      </c>
+      <c r="F88">
+        <v>85</v>
+      </c>
+      <c r="G88">
+        <v>284.49</v>
+      </c>
+      <c r="H88">
+        <v>-612.41999999999996</v>
+      </c>
+      <c r="I88">
+        <v>18792</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A89">
+        <v>86</v>
+      </c>
+      <c r="B89">
+        <v>-299.70999999999998</v>
+      </c>
+      <c r="C89">
+        <v>-90</v>
+      </c>
+      <c r="D89">
+        <v>21366</v>
+      </c>
+      <c r="F89">
+        <v>86</v>
+      </c>
+      <c r="G89">
+        <v>289.01</v>
+      </c>
+      <c r="H89">
+        <v>-610.70000000000005</v>
+      </c>
+      <c r="I89">
+        <v>18842</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A90">
+        <v>87</v>
+      </c>
+      <c r="B90">
+        <v>-302.17</v>
+      </c>
+      <c r="C90">
+        <v>-91.68</v>
+      </c>
+      <c r="D90">
+        <v>21416</v>
+      </c>
+      <c r="F90">
+        <v>87</v>
+      </c>
+      <c r="G90">
+        <v>294.69</v>
+      </c>
+      <c r="H90">
+        <v>-608.46</v>
+      </c>
+      <c r="I90">
+        <v>18902</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="F91">
+        <v>88</v>
+      </c>
+      <c r="G91">
+        <v>299.56</v>
+      </c>
+      <c r="H91">
+        <v>-606.48</v>
+      </c>
+      <c r="I91">
+        <v>18961</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="F92">
+        <v>89</v>
+      </c>
+      <c r="G92">
+        <v>300.08999999999997</v>
+      </c>
+      <c r="H92">
+        <v>-606.26</v>
+      </c>
+      <c r="I92">
+        <v>19012</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="F93">
+        <v>90</v>
+      </c>
+      <c r="G93">
+        <v>302.18</v>
+      </c>
+      <c r="H93">
+        <v>-605.38</v>
+      </c>
+      <c r="I93">
+        <v>19062</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="F94">
+        <v>91</v>
+      </c>
+      <c r="G94">
+        <v>305.69</v>
+      </c>
+      <c r="H94">
+        <v>-603.84</v>
+      </c>
+      <c r="I94">
+        <v>19112</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="F95">
+        <v>92</v>
+      </c>
+      <c r="G95">
+        <v>309.97000000000003</v>
+      </c>
+      <c r="H95">
+        <v>-601.9</v>
+      </c>
+      <c r="I95">
+        <v>19162</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="F96">
+        <v>93</v>
+      </c>
+      <c r="G96">
+        <v>314.86</v>
+      </c>
+      <c r="H96">
+        <v>-599.63</v>
+      </c>
+      <c r="I96">
+        <v>19221</v>
+      </c>
+    </row>
+    <row r="97" spans="6:9" x14ac:dyDescent="0.35">
+      <c r="F97">
+        <v>94</v>
+      </c>
+      <c r="G97">
+        <v>318.70999999999998</v>
+      </c>
+      <c r="H97">
+        <v>-597.78</v>
+      </c>
+      <c r="I97">
+        <v>19271</v>
+      </c>
+    </row>
+    <row r="98" spans="6:9" x14ac:dyDescent="0.35">
+      <c r="F98">
+        <v>95</v>
+      </c>
+      <c r="G98">
+        <v>319.86</v>
+      </c>
+      <c r="H98">
+        <v>-597.23</v>
+      </c>
+      <c r="I98">
+        <v>19322</v>
+      </c>
+    </row>
+    <row r="99" spans="6:9" x14ac:dyDescent="0.35">
+      <c r="F99">
+        <v>96</v>
+      </c>
+      <c r="G99">
+        <v>321.52</v>
+      </c>
+      <c r="H99">
+        <v>-596.41</v>
+      </c>
+      <c r="I99">
+        <v>19372</v>
+      </c>
+    </row>
+    <row r="100" spans="6:9" x14ac:dyDescent="0.35">
+      <c r="F100">
+        <v>97</v>
+      </c>
+      <c r="G100">
+        <v>324.32</v>
+      </c>
+      <c r="H100">
+        <v>-595.02</v>
+      </c>
+      <c r="I100">
+        <v>19431</v>
+      </c>
+    </row>
+    <row r="101" spans="6:9" x14ac:dyDescent="0.35">
+      <c r="F101">
+        <v>98</v>
+      </c>
+      <c r="G101">
+        <v>324.57</v>
+      </c>
+      <c r="H101">
+        <v>-594.89</v>
+      </c>
+      <c r="I101">
+        <v>19481</v>
+      </c>
+    </row>
+    <row r="102" spans="6:9" x14ac:dyDescent="0.35">
+      <c r="F102">
+        <v>99</v>
+      </c>
+      <c r="G102">
+        <v>324.57</v>
+      </c>
+      <c r="H102">
+        <v>-594.89</v>
+      </c>
+      <c r="I102">
+        <v>19531</v>
+      </c>
+    </row>
+    <row r="103" spans="6:9" x14ac:dyDescent="0.35">
+      <c r="F103">
+        <v>100</v>
+      </c>
+      <c r="G103">
+        <v>324.57</v>
+      </c>
+      <c r="H103">
+        <v>-594.89</v>
+      </c>
+      <c r="I103">
+        <v>19581</v>
+      </c>
+    </row>
+    <row r="104" spans="6:9" x14ac:dyDescent="0.35">
+      <c r="F104">
+        <v>101</v>
+      </c>
+      <c r="G104">
+        <v>324.57</v>
+      </c>
+      <c r="H104">
+        <v>-594.89</v>
+      </c>
+      <c r="I104">
+        <v>19631</v>
+      </c>
+    </row>
+    <row r="105" spans="6:9" x14ac:dyDescent="0.35">
+      <c r="F105">
+        <v>102</v>
+      </c>
+      <c r="G105">
+        <v>324.57</v>
+      </c>
+      <c r="H105">
+        <v>-594.89</v>
+      </c>
+      <c r="I105">
+        <v>19681</v>
+      </c>
+    </row>
+    <row r="106" spans="6:9" x14ac:dyDescent="0.35">
+      <c r="F106">
+        <v>103</v>
+      </c>
+      <c r="G106">
+        <v>324.57</v>
+      </c>
+      <c r="H106">
+        <v>-594.89</v>
+      </c>
+      <c r="I106">
+        <v>19731</v>
+      </c>
+    </row>
+    <row r="107" spans="6:9" x14ac:dyDescent="0.35">
+      <c r="F107">
+        <v>104</v>
+      </c>
+      <c r="G107">
+        <v>324.57</v>
+      </c>
+      <c r="H107">
+        <v>-594.89</v>
+      </c>
+      <c r="I107">
+        <v>19781</v>
+      </c>
+    </row>
+    <row r="108" spans="6:9" x14ac:dyDescent="0.35">
+      <c r="F108">
+        <v>105</v>
+      </c>
+      <c r="G108">
+        <v>324.57</v>
+      </c>
+      <c r="H108">
+        <v>-594.89</v>
+      </c>
+      <c r="I108">
+        <v>19831</v>
+      </c>
+    </row>
+    <row r="109" spans="6:9" x14ac:dyDescent="0.35">
+      <c r="F109">
+        <v>106</v>
+      </c>
+      <c r="G109">
+        <v>324.57</v>
+      </c>
+      <c r="H109">
+        <v>-594.89</v>
+      </c>
+      <c r="I109">
+        <v>19881</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{652C810A-2770-401E-8C22-C83AC1CB5591}">
+  <dimension ref="A1:K98"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2" t="s">
+        <v>1</v>
+      </c>
+      <c r="H2" t="s">
+        <v>2</v>
+      </c>
+      <c r="I2" t="s">
+        <v>3</v>
+      </c>
+      <c r="K2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>0</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>14955</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0.97</v>
+      </c>
+      <c r="H3">
+        <v>1.49</v>
+      </c>
+      <c r="I3">
+        <v>14414</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>-0.14000000000000001</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>15005</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>1.25</v>
+      </c>
+      <c r="H4">
+        <v>1.49</v>
+      </c>
+      <c r="I4">
+        <v>14465</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5">
+        <v>-0.28000000000000003</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>15055</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>1.25</v>
+      </c>
+      <c r="H5">
+        <v>1.49</v>
+      </c>
+      <c r="I5">
+        <v>14524</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6">
+        <v>-0.28000000000000003</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>15105</v>
+      </c>
+      <c r="F6">
+        <v>3</v>
+      </c>
+      <c r="G6">
+        <v>1.25</v>
+      </c>
+      <c r="H6">
+        <v>1.49</v>
+      </c>
+      <c r="I6">
+        <v>14575</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>4</v>
+      </c>
+      <c r="B7">
+        <v>-1.7</v>
+      </c>
+      <c r="C7">
+        <v>-0.02</v>
+      </c>
+      <c r="D7">
+        <v>15155</v>
+      </c>
+      <c r="F7">
+        <v>4</v>
+      </c>
+      <c r="G7">
+        <v>1.25</v>
+      </c>
+      <c r="H7">
+        <v>1.49</v>
+      </c>
+      <c r="I7">
+        <v>14625</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>5</v>
+      </c>
+      <c r="B8">
+        <v>-5.81</v>
+      </c>
+      <c r="C8">
+        <v>-0.12</v>
+      </c>
+      <c r="D8">
+        <v>15205</v>
+      </c>
+      <c r="F8">
+        <v>5</v>
+      </c>
+      <c r="G8">
+        <v>1.25</v>
+      </c>
+      <c r="H8">
+        <v>1.49</v>
+      </c>
+      <c r="I8">
+        <v>14675</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>6</v>
+      </c>
+      <c r="B9">
+        <v>-8.5</v>
+      </c>
+      <c r="C9">
+        <v>-0.2</v>
+      </c>
+      <c r="D9">
+        <v>15255</v>
+      </c>
+      <c r="F9">
+        <v>6</v>
+      </c>
+      <c r="G9">
+        <v>1.25</v>
+      </c>
+      <c r="H9">
+        <v>1.49</v>
+      </c>
+      <c r="I9">
+        <v>14725</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>7</v>
+      </c>
+      <c r="B10">
+        <v>-12.33</v>
+      </c>
+      <c r="C10">
+        <v>-0.34</v>
+      </c>
+      <c r="D10">
+        <v>15305</v>
+      </c>
+      <c r="F10">
+        <v>7</v>
+      </c>
+      <c r="G10">
+        <v>1.25</v>
+      </c>
+      <c r="H10">
+        <v>1.49</v>
+      </c>
+      <c r="I10">
+        <v>14776</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>8</v>
+      </c>
+      <c r="B11">
+        <v>-15.03</v>
+      </c>
+      <c r="C11">
+        <v>-0.44</v>
+      </c>
+      <c r="D11">
+        <v>15355</v>
+      </c>
+      <c r="F11">
+        <v>8</v>
+      </c>
+      <c r="G11">
+        <v>1.25</v>
+      </c>
+      <c r="H11">
+        <v>1.49</v>
+      </c>
+      <c r="I11">
+        <v>14826</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>9</v>
+      </c>
+      <c r="B12">
+        <v>-18.71</v>
+      </c>
+      <c r="C12">
+        <v>-0.61</v>
+      </c>
+      <c r="D12">
+        <v>15405</v>
+      </c>
+      <c r="F12">
+        <v>9</v>
+      </c>
+      <c r="G12">
+        <v>1.25</v>
+      </c>
+      <c r="H12">
+        <v>1.49</v>
+      </c>
+      <c r="I12">
+        <v>14876</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>10</v>
+      </c>
+      <c r="B13">
+        <v>-21.12</v>
+      </c>
+      <c r="C13">
+        <v>-0.72</v>
+      </c>
+      <c r="D13">
+        <v>15455</v>
+      </c>
+      <c r="F13">
+        <v>10</v>
+      </c>
+      <c r="G13">
+        <v>1.25</v>
+      </c>
+      <c r="H13">
+        <v>1.49</v>
+      </c>
+      <c r="I13">
+        <v>14926</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>11</v>
+      </c>
+      <c r="B14">
+        <v>-24.94</v>
+      </c>
+      <c r="C14">
+        <v>-0.94</v>
+      </c>
+      <c r="D14">
+        <v>15505</v>
+      </c>
+      <c r="F14">
+        <v>11</v>
+      </c>
+      <c r="G14">
+        <v>1.25</v>
+      </c>
+      <c r="H14">
+        <v>1.49</v>
+      </c>
+      <c r="I14">
+        <v>14977</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>12</v>
+      </c>
+      <c r="B15">
+        <v>-27.49</v>
+      </c>
+      <c r="C15">
+        <v>-1.0900000000000001</v>
+      </c>
+      <c r="D15">
+        <v>15555</v>
+      </c>
+      <c r="F15">
+        <v>12</v>
+      </c>
+      <c r="G15">
+        <v>1.4</v>
+      </c>
+      <c r="H15">
+        <v>1.5</v>
+      </c>
+      <c r="I15">
+        <v>15036</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>13</v>
+      </c>
+      <c r="B16">
+        <v>-31.46</v>
+      </c>
+      <c r="C16">
+        <v>-1.34</v>
+      </c>
+      <c r="D16">
+        <v>15605</v>
+      </c>
+      <c r="F16">
+        <v>13</v>
+      </c>
+      <c r="G16">
+        <v>2.82</v>
+      </c>
+      <c r="H16">
+        <v>1.54</v>
+      </c>
+      <c r="I16">
+        <v>15086</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>14</v>
+      </c>
+      <c r="B17">
+        <v>-34.15</v>
+      </c>
+      <c r="C17">
+        <v>-1.52</v>
+      </c>
+      <c r="D17">
+        <v>15655</v>
+      </c>
+      <c r="F17">
+        <v>14</v>
+      </c>
+      <c r="G17">
+        <v>5.09</v>
+      </c>
+      <c r="H17">
+        <v>1.62</v>
+      </c>
+      <c r="I17">
+        <v>15136</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>15</v>
+      </c>
+      <c r="B18">
+        <v>-38.25</v>
+      </c>
+      <c r="C18">
+        <v>-1.84</v>
+      </c>
+      <c r="D18">
+        <v>15705</v>
+      </c>
+      <c r="F18">
+        <v>15</v>
+      </c>
+      <c r="G18">
+        <v>8.07</v>
+      </c>
+      <c r="H18">
+        <v>1.71</v>
+      </c>
+      <c r="I18">
+        <v>15186</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>16</v>
+      </c>
+      <c r="B19">
+        <v>-40.93</v>
+      </c>
+      <c r="C19">
+        <v>-2.0699999999999998</v>
+      </c>
+      <c r="D19">
+        <v>15755</v>
+      </c>
+      <c r="F19">
+        <v>16</v>
+      </c>
+      <c r="G19">
+        <v>11.62</v>
+      </c>
+      <c r="H19">
+        <v>1.82</v>
+      </c>
+      <c r="I19">
+        <v>15237</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>17</v>
+      </c>
+      <c r="B20">
+        <v>-44.89</v>
+      </c>
+      <c r="C20">
+        <v>-2.41</v>
+      </c>
+      <c r="D20">
+        <v>15805</v>
+      </c>
+      <c r="F20">
+        <v>17</v>
+      </c>
+      <c r="G20">
+        <v>15.46</v>
+      </c>
+      <c r="H20">
+        <v>1.94</v>
+      </c>
+      <c r="I20">
+        <v>15296</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>18</v>
+      </c>
+      <c r="B21">
+        <v>-47.43</v>
+      </c>
+      <c r="C21">
+        <v>-2.65</v>
+      </c>
+      <c r="D21">
+        <v>15855</v>
+      </c>
+      <c r="F21">
+        <v>18</v>
+      </c>
+      <c r="G21">
+        <v>19.010000000000002</v>
+      </c>
+      <c r="H21">
+        <v>2.04</v>
+      </c>
+      <c r="I21">
+        <v>15346</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>19</v>
+      </c>
+      <c r="B22">
+        <v>-51.39</v>
+      </c>
+      <c r="C22">
+        <v>-3.05</v>
+      </c>
+      <c r="D22">
+        <v>15905</v>
+      </c>
+      <c r="F22">
+        <v>19</v>
+      </c>
+      <c r="G22">
+        <v>22.7</v>
+      </c>
+      <c r="H22">
+        <v>2.14</v>
+      </c>
+      <c r="I22">
+        <v>15396</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>20</v>
+      </c>
+      <c r="B23">
+        <v>-54.21</v>
+      </c>
+      <c r="C23">
+        <v>-3.35</v>
+      </c>
+      <c r="D23">
+        <v>15955</v>
+      </c>
+      <c r="F23">
+        <v>20</v>
+      </c>
+      <c r="G23">
+        <v>26.39</v>
+      </c>
+      <c r="H23">
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="I23">
+        <v>15447</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>21</v>
+      </c>
+      <c r="B24">
+        <v>-58.29</v>
+      </c>
+      <c r="C24">
+        <v>-3.82</v>
+      </c>
+      <c r="D24">
+        <v>16006</v>
+      </c>
+      <c r="F24">
+        <v>21</v>
+      </c>
+      <c r="G24">
+        <v>31.08</v>
+      </c>
+      <c r="H24">
+        <v>2.36</v>
+      </c>
+      <c r="I24">
+        <v>15506</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>22</v>
+      </c>
+      <c r="B25">
+        <v>-61.11</v>
+      </c>
+      <c r="C25">
+        <v>-4.17</v>
+      </c>
+      <c r="D25">
+        <v>16056</v>
+      </c>
+      <c r="F25">
+        <v>22</v>
+      </c>
+      <c r="G25">
+        <v>35.06</v>
+      </c>
+      <c r="H25">
+        <v>2.4700000000000002</v>
+      </c>
+      <c r="I25">
+        <v>15556</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>23</v>
+      </c>
+      <c r="B26">
+        <v>-65.19</v>
+      </c>
+      <c r="C26">
+        <v>-4.68</v>
+      </c>
+      <c r="D26">
+        <v>16106</v>
+      </c>
+      <c r="F26">
+        <v>23</v>
+      </c>
+      <c r="G26">
+        <v>38.89</v>
+      </c>
+      <c r="H26">
+        <v>2.59</v>
+      </c>
+      <c r="I26">
+        <v>15606</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>24</v>
+      </c>
+      <c r="B27">
+        <v>-68</v>
+      </c>
+      <c r="C27">
+        <v>-5.0599999999999996</v>
+      </c>
+      <c r="D27">
+        <v>16156</v>
+      </c>
+      <c r="F27">
+        <v>24</v>
+      </c>
+      <c r="G27">
+        <v>42.87</v>
+      </c>
+      <c r="H27">
+        <v>2.73</v>
+      </c>
+      <c r="I27">
+        <v>15656</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>25</v>
+      </c>
+      <c r="B28">
+        <v>-72.36</v>
+      </c>
+      <c r="C28">
+        <v>-5.69</v>
+      </c>
+      <c r="D28">
+        <v>16207</v>
+      </c>
+      <c r="F28">
+        <v>25</v>
+      </c>
+      <c r="G28">
+        <v>47.13</v>
+      </c>
+      <c r="H28">
+        <v>2.87</v>
+      </c>
+      <c r="I28">
+        <v>15707</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>26</v>
+      </c>
+      <c r="B29">
+        <v>-75.44</v>
+      </c>
+      <c r="C29">
+        <v>-6.15</v>
+      </c>
+      <c r="D29">
+        <v>16257</v>
+      </c>
+      <c r="F29">
+        <v>26</v>
+      </c>
+      <c r="G29">
+        <v>52.1</v>
+      </c>
+      <c r="H29">
+        <v>3.05</v>
+      </c>
+      <c r="I29">
+        <v>15766</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>27</v>
+      </c>
+      <c r="B30">
+        <v>-79.650000000000006</v>
+      </c>
+      <c r="C30">
+        <v>-6.79</v>
+      </c>
+      <c r="D30">
+        <v>16307</v>
+      </c>
+      <c r="F30">
+        <v>27</v>
+      </c>
+      <c r="G30">
+        <v>56.5</v>
+      </c>
+      <c r="H30">
+        <v>3.22</v>
+      </c>
+      <c r="I30">
+        <v>15816</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>28</v>
+      </c>
+      <c r="B31">
+        <v>-82.45</v>
+      </c>
+      <c r="C31">
+        <v>-7.24</v>
+      </c>
+      <c r="D31">
+        <v>16357</v>
+      </c>
+      <c r="F31">
+        <v>28</v>
+      </c>
+      <c r="G31">
+        <v>60.34</v>
+      </c>
+      <c r="H31">
+        <v>3.37</v>
+      </c>
+      <c r="I31">
+        <v>15866</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>29</v>
+      </c>
+      <c r="B32">
+        <v>-86.93</v>
+      </c>
+      <c r="C32">
+        <v>-7.99</v>
+      </c>
+      <c r="D32">
+        <v>16407</v>
+      </c>
+      <c r="F32">
+        <v>29</v>
+      </c>
+      <c r="G32">
+        <v>64.739999999999995</v>
+      </c>
+      <c r="H32">
+        <v>3.55</v>
+      </c>
+      <c r="I32">
+        <v>15917</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>30</v>
+      </c>
+      <c r="B33">
+        <v>-90.01</v>
+      </c>
+      <c r="C33">
+        <v>-8.52</v>
+      </c>
+      <c r="D33">
+        <v>16457</v>
+      </c>
+      <c r="F33">
+        <v>30</v>
+      </c>
+      <c r="G33">
+        <v>69.989999999999995</v>
+      </c>
+      <c r="H33">
+        <v>3.78</v>
+      </c>
+      <c r="I33">
+        <v>15976</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A34">
+        <v>31</v>
+      </c>
+      <c r="B34">
+        <v>-94.33</v>
+      </c>
+      <c r="C34">
+        <v>-9.3000000000000007</v>
+      </c>
+      <c r="D34">
+        <v>16507</v>
+      </c>
+      <c r="F34">
+        <v>31</v>
+      </c>
+      <c r="G34">
+        <v>74.39</v>
+      </c>
+      <c r="H34">
+        <v>3.98</v>
+      </c>
+      <c r="I34">
+        <v>16026</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A35">
+        <v>32</v>
+      </c>
+      <c r="B35">
+        <v>-97.26</v>
+      </c>
+      <c r="C35">
+        <v>-9.86</v>
+      </c>
+      <c r="D35">
+        <v>16557</v>
+      </c>
+      <c r="F35">
+        <v>32</v>
+      </c>
+      <c r="G35">
+        <v>78.790000000000006</v>
+      </c>
+      <c r="H35">
+        <v>4.1900000000000004</v>
+      </c>
+      <c r="I35">
+        <v>16076</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A36">
+        <v>33</v>
+      </c>
+      <c r="B36">
+        <v>-101.58</v>
+      </c>
+      <c r="C36">
+        <v>-10.7</v>
+      </c>
+      <c r="D36">
+        <v>16607</v>
+      </c>
+      <c r="F36">
+        <v>33</v>
+      </c>
+      <c r="G36">
+        <v>83.19</v>
+      </c>
+      <c r="H36">
+        <v>4.42</v>
+      </c>
+      <c r="I36">
+        <v>16126</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A37">
+        <v>34</v>
+      </c>
+      <c r="B37">
+        <v>-104.5</v>
+      </c>
+      <c r="C37">
+        <v>-11.29</v>
+      </c>
+      <c r="D37">
+        <v>16657</v>
+      </c>
+      <c r="F37">
+        <v>34</v>
+      </c>
+      <c r="G37">
+        <v>87.73</v>
+      </c>
+      <c r="H37">
+        <v>4.66</v>
+      </c>
+      <c r="I37">
+        <v>16177</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A38">
+        <v>35</v>
+      </c>
+      <c r="B38">
+        <v>-109.22</v>
+      </c>
+      <c r="C38">
+        <v>-12.29</v>
+      </c>
+      <c r="D38">
+        <v>16707</v>
+      </c>
+      <c r="F38">
+        <v>35</v>
+      </c>
+      <c r="G38">
+        <v>93.12</v>
+      </c>
+      <c r="H38">
+        <v>4.95</v>
+      </c>
+      <c r="I38">
+        <v>16236</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A39">
+        <v>36</v>
+      </c>
+      <c r="B39">
+        <v>-112.13</v>
+      </c>
+      <c r="C39">
+        <v>-12.92</v>
+      </c>
+      <c r="D39">
+        <v>16757</v>
+      </c>
+      <c r="F39">
+        <v>36</v>
+      </c>
+      <c r="G39">
+        <v>97.52</v>
+      </c>
+      <c r="H39">
+        <v>5.2</v>
+      </c>
+      <c r="I39">
+        <v>16286</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A40">
+        <v>37</v>
+      </c>
+      <c r="B40">
+        <v>-116.69</v>
+      </c>
+      <c r="C40">
+        <v>-13.95</v>
+      </c>
+      <c r="D40">
+        <v>16807</v>
+      </c>
+      <c r="F40">
+        <v>37</v>
+      </c>
+      <c r="G40">
+        <v>102.2</v>
+      </c>
+      <c r="H40">
+        <v>5.46</v>
+      </c>
+      <c r="I40">
+        <v>16336</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A41">
+        <v>38</v>
+      </c>
+      <c r="B41">
+        <v>-119.87</v>
+      </c>
+      <c r="C41">
+        <v>-14.7</v>
+      </c>
+      <c r="D41">
+        <v>16857</v>
+      </c>
+      <c r="F41">
+        <v>38</v>
+      </c>
+      <c r="G41">
+        <v>106.88</v>
+      </c>
+      <c r="H41">
+        <v>5.69</v>
+      </c>
+      <c r="I41">
+        <v>16387</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A42">
+        <v>39</v>
+      </c>
+      <c r="B42">
+        <v>-124.29</v>
+      </c>
+      <c r="C42">
+        <v>-15.75</v>
+      </c>
+      <c r="D42">
+        <v>16907</v>
+      </c>
+      <c r="F42">
+        <v>39</v>
+      </c>
+      <c r="G42">
+        <v>112.13</v>
+      </c>
+      <c r="H42">
+        <v>5.96</v>
+      </c>
+      <c r="I42">
+        <v>16446</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A43">
+        <v>40</v>
+      </c>
+      <c r="B43">
+        <v>-127.32</v>
+      </c>
+      <c r="C43">
+        <v>-16.489999999999998</v>
+      </c>
+      <c r="D43">
+        <v>16957</v>
+      </c>
+      <c r="F43">
+        <v>40</v>
+      </c>
+      <c r="G43">
+        <v>116.68</v>
+      </c>
+      <c r="H43">
+        <v>6.2</v>
+      </c>
+      <c r="I43">
+        <v>16496</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A44">
+        <v>41</v>
+      </c>
+      <c r="B44">
+        <v>-132.13</v>
+      </c>
+      <c r="C44">
+        <v>-17.71</v>
+      </c>
+      <c r="D44">
+        <v>17007</v>
+      </c>
+      <c r="F44">
+        <v>41</v>
+      </c>
+      <c r="G44">
+        <v>121.07</v>
+      </c>
+      <c r="H44">
+        <v>6.43</v>
+      </c>
+      <c r="I44">
+        <v>16546</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A45">
+        <v>42</v>
+      </c>
+      <c r="B45">
+        <v>-135.15</v>
+      </c>
+      <c r="C45">
+        <v>-18.5</v>
+      </c>
+      <c r="D45">
+        <v>17057</v>
+      </c>
+      <c r="F45">
+        <v>42</v>
+      </c>
+      <c r="G45">
+        <v>125.62</v>
+      </c>
+      <c r="H45">
+        <v>6.67</v>
+      </c>
+      <c r="I45">
+        <v>16596</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A46">
+        <v>43</v>
+      </c>
+      <c r="B46">
+        <v>-139.82</v>
+      </c>
+      <c r="C46">
+        <v>-19.73</v>
+      </c>
+      <c r="D46">
+        <v>17107</v>
+      </c>
+      <c r="F46">
+        <v>43</v>
+      </c>
+      <c r="G46">
+        <v>130.30000000000001</v>
+      </c>
+      <c r="H46">
+        <v>6.94</v>
+      </c>
+      <c r="I46">
+        <v>16646</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A47">
+        <v>44</v>
+      </c>
+      <c r="B47">
+        <v>-142.96</v>
+      </c>
+      <c r="C47">
+        <v>-20.59</v>
+      </c>
+      <c r="D47">
+        <v>17157</v>
+      </c>
+      <c r="F47">
+        <v>44</v>
+      </c>
+      <c r="G47">
+        <v>134.97999999999999</v>
+      </c>
+      <c r="H47">
+        <v>7.23</v>
+      </c>
+      <c r="I47">
+        <v>16696</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A48">
+        <v>45</v>
+      </c>
+      <c r="B48">
+        <v>-147.61000000000001</v>
+      </c>
+      <c r="C48">
+        <v>-21.9</v>
+      </c>
+      <c r="D48">
+        <v>17207</v>
+      </c>
+      <c r="F48">
+        <v>45</v>
+      </c>
+      <c r="G48">
+        <v>139.80000000000001</v>
+      </c>
+      <c r="H48">
+        <v>7.55</v>
+      </c>
+      <c r="I48">
+        <v>16746</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A49">
+        <v>46</v>
+      </c>
+      <c r="B49">
+        <v>-150.74</v>
+      </c>
+      <c r="C49">
+        <v>-22.8</v>
+      </c>
+      <c r="D49">
+        <v>17257</v>
+      </c>
+      <c r="F49">
+        <v>46</v>
+      </c>
+      <c r="G49">
+        <v>144.33000000000001</v>
+      </c>
+      <c r="H49">
+        <v>7.89</v>
+      </c>
+      <c r="I49">
+        <v>16796</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A50">
+        <v>47</v>
+      </c>
+      <c r="B50">
+        <v>-155.63999999999999</v>
+      </c>
+      <c r="C50">
+        <v>-24.25</v>
+      </c>
+      <c r="D50">
+        <v>17307</v>
+      </c>
+      <c r="F50">
+        <v>47</v>
+      </c>
+      <c r="G50">
+        <v>149.29</v>
+      </c>
+      <c r="H50">
+        <v>8.2799999999999994</v>
+      </c>
+      <c r="I50">
+        <v>16846</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A51">
+        <v>48</v>
+      </c>
+      <c r="B51">
+        <v>-158.76</v>
+      </c>
+      <c r="C51">
+        <v>-25.21</v>
+      </c>
+      <c r="D51">
+        <v>17357</v>
+      </c>
+      <c r="F51">
+        <v>48</v>
+      </c>
+      <c r="G51">
+        <v>153.96</v>
+      </c>
+      <c r="H51">
+        <v>8.65</v>
+      </c>
+      <c r="I51">
+        <v>16897</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A52">
+        <v>49</v>
+      </c>
+      <c r="B52">
+        <v>-163.63</v>
+      </c>
+      <c r="C52">
+        <v>-26.74</v>
+      </c>
+      <c r="D52">
+        <v>17408</v>
+      </c>
+      <c r="F52">
+        <v>49</v>
+      </c>
+      <c r="G52">
+        <v>159.77000000000001</v>
+      </c>
+      <c r="H52">
+        <v>9.1300000000000008</v>
+      </c>
+      <c r="I52">
+        <v>16956</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A53">
+        <v>50</v>
+      </c>
+      <c r="B53">
+        <v>-166.73</v>
+      </c>
+      <c r="C53">
+        <v>-27.75</v>
+      </c>
+      <c r="D53">
+        <v>17458</v>
+      </c>
+      <c r="F53">
+        <v>50</v>
+      </c>
+      <c r="G53">
+        <v>164.44</v>
+      </c>
+      <c r="H53">
+        <v>9.5399999999999991</v>
+      </c>
+      <c r="I53">
+        <v>17006</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A54">
+        <v>51</v>
+      </c>
+      <c r="B54">
+        <v>-171.45</v>
+      </c>
+      <c r="C54">
+        <v>-29.3</v>
+      </c>
+      <c r="D54">
+        <v>17509</v>
+      </c>
+      <c r="F54">
+        <v>51</v>
+      </c>
+      <c r="G54">
+        <v>169.25</v>
+      </c>
+      <c r="H54">
+        <v>9.9700000000000006</v>
+      </c>
+      <c r="I54">
+        <v>17056</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A55">
+        <v>52</v>
+      </c>
+      <c r="B55">
+        <v>-174.67</v>
+      </c>
+      <c r="C55">
+        <v>-30.4</v>
+      </c>
+      <c r="D55">
+        <v>17559</v>
+      </c>
+      <c r="F55">
+        <v>52</v>
+      </c>
+      <c r="G55">
+        <v>173.92</v>
+      </c>
+      <c r="H55">
+        <v>10.39</v>
+      </c>
+      <c r="I55">
+        <v>17106</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A56">
+        <v>53</v>
+      </c>
+      <c r="B56">
+        <v>-179.63</v>
+      </c>
+      <c r="C56">
+        <v>-32.130000000000003</v>
+      </c>
+      <c r="D56">
+        <v>17609</v>
+      </c>
+      <c r="F56">
+        <v>53</v>
+      </c>
+      <c r="G56">
+        <v>178.59</v>
+      </c>
+      <c r="H56">
+        <v>10.83</v>
+      </c>
+      <c r="I56">
+        <v>17157</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A57">
+        <v>54</v>
+      </c>
+      <c r="B57">
+        <v>-182.97</v>
+      </c>
+      <c r="C57">
+        <v>-33.33</v>
+      </c>
+      <c r="D57">
+        <v>17659</v>
+      </c>
+      <c r="F57">
+        <v>54</v>
+      </c>
+      <c r="G57">
+        <v>184.25</v>
+      </c>
+      <c r="H57">
+        <v>11.39</v>
+      </c>
+      <c r="I57">
+        <v>17216</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A58">
+        <v>55</v>
+      </c>
+      <c r="B58">
+        <v>-187.76</v>
+      </c>
+      <c r="C58">
+        <v>-35.090000000000003</v>
+      </c>
+      <c r="D58">
+        <v>17709</v>
+      </c>
+      <c r="F58">
+        <v>55</v>
+      </c>
+      <c r="G58">
+        <v>189.19</v>
+      </c>
+      <c r="H58">
+        <v>11.91</v>
+      </c>
+      <c r="I58">
+        <v>17266</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A59">
+        <v>56</v>
+      </c>
+      <c r="B59">
+        <v>-190.95</v>
+      </c>
+      <c r="C59">
+        <v>-36.28</v>
+      </c>
+      <c r="D59">
+        <v>17759</v>
+      </c>
+      <c r="F59">
+        <v>56</v>
+      </c>
+      <c r="G59">
+        <v>193.86</v>
+      </c>
+      <c r="H59">
+        <v>12.4</v>
+      </c>
+      <c r="I59">
+        <v>17316</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A60">
+        <v>57</v>
+      </c>
+      <c r="B60">
+        <v>-195.85</v>
+      </c>
+      <c r="C60">
+        <v>-38.15</v>
+      </c>
+      <c r="D60">
+        <v>17809</v>
+      </c>
+      <c r="F60">
+        <v>57</v>
+      </c>
+      <c r="G60">
+        <v>198.66</v>
+      </c>
+      <c r="H60">
+        <v>12.9</v>
+      </c>
+      <c r="I60">
+        <v>17367</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A61">
+        <v>58</v>
+      </c>
+      <c r="B61">
+        <v>-199.03</v>
+      </c>
+      <c r="C61">
+        <v>-39.39</v>
+      </c>
+      <c r="D61">
+        <v>17859</v>
+      </c>
+      <c r="F61">
+        <v>58</v>
+      </c>
+      <c r="G61">
+        <v>203.89</v>
+      </c>
+      <c r="H61">
+        <v>13.45</v>
+      </c>
+      <c r="I61">
+        <v>17426</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A62">
+        <v>59</v>
+      </c>
+      <c r="B62">
+        <v>-203.77</v>
+      </c>
+      <c r="C62">
+        <v>-41.27</v>
+      </c>
+      <c r="D62">
+        <v>17909</v>
+      </c>
+      <c r="F62">
+        <v>59</v>
+      </c>
+      <c r="G62">
+        <v>208.69</v>
+      </c>
+      <c r="H62">
+        <v>13.97</v>
+      </c>
+      <c r="I62">
+        <v>17476</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A63">
+        <v>60</v>
+      </c>
+      <c r="B63">
+        <v>-207.19</v>
+      </c>
+      <c r="C63">
+        <v>-42.66</v>
+      </c>
+      <c r="D63">
+        <v>17959</v>
+      </c>
+      <c r="F63">
+        <v>60</v>
+      </c>
+      <c r="G63">
+        <v>213.64</v>
+      </c>
+      <c r="H63">
+        <v>14.51</v>
+      </c>
+      <c r="I63">
+        <v>17526</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A64">
+        <v>61</v>
+      </c>
+      <c r="B64">
+        <v>-211.91</v>
+      </c>
+      <c r="C64">
+        <v>-44.62</v>
+      </c>
+      <c r="D64">
+        <v>18009</v>
+      </c>
+      <c r="F64">
+        <v>61</v>
+      </c>
+      <c r="G64">
+        <v>218.44</v>
+      </c>
+      <c r="H64">
+        <v>15.05</v>
+      </c>
+      <c r="I64">
+        <v>17576</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A65">
+        <v>62</v>
+      </c>
+      <c r="B65">
+        <v>-215.05</v>
+      </c>
+      <c r="C65">
+        <v>-45.94</v>
+      </c>
+      <c r="D65">
+        <v>18059</v>
+      </c>
+      <c r="F65">
+        <v>62</v>
+      </c>
+      <c r="G65">
+        <v>223.24</v>
+      </c>
+      <c r="H65">
+        <v>15.57</v>
+      </c>
+      <c r="I65">
+        <v>17627</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A66">
+        <v>63</v>
+      </c>
+      <c r="B66">
+        <v>-220</v>
+      </c>
+      <c r="C66">
+        <v>-48.08</v>
+      </c>
+      <c r="D66">
+        <v>18110</v>
+      </c>
+      <c r="F66">
+        <v>63</v>
+      </c>
+      <c r="G66">
+        <v>229.03</v>
+      </c>
+      <c r="H66">
+        <v>16.239999999999998</v>
+      </c>
+      <c r="I66">
+        <v>17686</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A67">
+        <v>64</v>
+      </c>
+      <c r="B67">
+        <v>-223.24</v>
+      </c>
+      <c r="C67">
+        <v>-49.52</v>
+      </c>
+      <c r="D67">
+        <v>18160</v>
+      </c>
+      <c r="F67">
+        <v>64</v>
+      </c>
+      <c r="G67">
+        <v>233.97</v>
+      </c>
+      <c r="H67">
+        <v>16.829999999999998</v>
+      </c>
+      <c r="I67">
+        <v>17736</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A68">
+        <v>65</v>
+      </c>
+      <c r="B68">
+        <v>-228.02</v>
+      </c>
+      <c r="C68">
+        <v>-51.67</v>
+      </c>
+      <c r="D68">
+        <v>18210</v>
+      </c>
+      <c r="F68">
+        <v>65</v>
+      </c>
+      <c r="G68">
+        <v>238.9</v>
+      </c>
+      <c r="H68">
+        <v>17.45</v>
+      </c>
+      <c r="I68">
+        <v>17786</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A69">
+        <v>66</v>
+      </c>
+      <c r="B69">
+        <v>-231.37</v>
+      </c>
+      <c r="C69">
+        <v>-53.21</v>
+      </c>
+      <c r="D69">
+        <v>18260</v>
+      </c>
+      <c r="F69">
+        <v>66</v>
+      </c>
+      <c r="G69">
+        <v>243.84</v>
+      </c>
+      <c r="H69">
+        <v>18.079999999999998</v>
+      </c>
+      <c r="I69">
+        <v>17837</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A70">
+        <v>67</v>
+      </c>
+      <c r="B70">
+        <v>-236.25</v>
+      </c>
+      <c r="C70">
+        <v>-55.51</v>
+      </c>
+      <c r="D70">
+        <v>18310</v>
+      </c>
+      <c r="F70">
+        <v>67</v>
+      </c>
+      <c r="G70">
+        <v>249.61</v>
+      </c>
+      <c r="H70">
+        <v>18.850000000000001</v>
+      </c>
+      <c r="I70">
+        <v>17896</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A71">
+        <v>68</v>
+      </c>
+      <c r="B71">
+        <v>-239.45</v>
+      </c>
+      <c r="C71">
+        <v>-57.03</v>
+      </c>
+      <c r="D71">
+        <v>18360</v>
+      </c>
+      <c r="F71">
+        <v>68</v>
+      </c>
+      <c r="G71">
+        <v>254.53</v>
+      </c>
+      <c r="H71">
+        <v>19.55</v>
+      </c>
+      <c r="I71">
+        <v>17946</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A72">
+        <v>69</v>
+      </c>
+      <c r="B72">
+        <v>-242.9</v>
+      </c>
+      <c r="C72">
+        <v>-58.7</v>
+      </c>
+      <c r="D72">
+        <v>18410</v>
+      </c>
+      <c r="F72">
+        <v>69</v>
+      </c>
+      <c r="G72">
+        <v>259.45999999999998</v>
+      </c>
+      <c r="H72">
+        <v>20.27</v>
+      </c>
+      <c r="I72">
+        <v>17996</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A73">
+        <v>70</v>
+      </c>
+      <c r="B73">
+        <v>-247.73</v>
+      </c>
+      <c r="C73">
+        <v>-61.1</v>
+      </c>
+      <c r="D73">
+        <v>18460</v>
+      </c>
+      <c r="F73">
+        <v>70</v>
+      </c>
+      <c r="G73">
+        <v>264.37</v>
+      </c>
+      <c r="H73">
+        <v>21.02</v>
+      </c>
+      <c r="I73">
+        <v>18046</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A74">
+        <v>71</v>
+      </c>
+      <c r="B74">
+        <v>-251.01</v>
+      </c>
+      <c r="C74">
+        <v>-62.78</v>
+      </c>
+      <c r="D74">
+        <v>18510</v>
+      </c>
+      <c r="F74">
+        <v>71</v>
+      </c>
+      <c r="G74">
+        <v>269.27999999999997</v>
+      </c>
+      <c r="H74">
+        <v>21.83</v>
+      </c>
+      <c r="I74">
+        <v>18097</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A75">
+        <v>72</v>
+      </c>
+      <c r="B75">
+        <v>-255.8</v>
+      </c>
+      <c r="C75">
+        <v>-65.27</v>
+      </c>
+      <c r="D75">
+        <v>18560</v>
+      </c>
+      <c r="F75">
+        <v>72</v>
+      </c>
+      <c r="G75">
+        <v>275.02</v>
+      </c>
+      <c r="H75">
+        <v>22.82</v>
+      </c>
+      <c r="I75">
+        <v>18156</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A76">
+        <v>73</v>
+      </c>
+      <c r="B76">
+        <v>-259.06</v>
+      </c>
+      <c r="C76">
+        <v>-66.989999999999995</v>
+      </c>
+      <c r="D76">
+        <v>18610</v>
+      </c>
+      <c r="F76">
+        <v>73</v>
+      </c>
+      <c r="G76">
+        <v>279.91000000000003</v>
+      </c>
+      <c r="H76">
+        <v>23.74</v>
+      </c>
+      <c r="I76">
+        <v>18206</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A77">
+        <v>74</v>
+      </c>
+      <c r="B77">
+        <v>-263.8</v>
+      </c>
+      <c r="C77">
+        <v>-69.55</v>
+      </c>
+      <c r="D77">
+        <v>18660</v>
+      </c>
+      <c r="F77">
+        <v>74</v>
+      </c>
+      <c r="G77">
+        <v>284.77999999999997</v>
+      </c>
+      <c r="H77">
+        <v>24.73</v>
+      </c>
+      <c r="I77">
+        <v>18256</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A78">
+        <v>75</v>
+      </c>
+      <c r="B78">
+        <v>-265.91000000000003</v>
+      </c>
+      <c r="C78">
+        <v>-70.709999999999994</v>
+      </c>
+      <c r="D78">
+        <v>18710</v>
+      </c>
+      <c r="F78">
+        <v>75</v>
+      </c>
+      <c r="G78">
+        <v>289.63</v>
+      </c>
+      <c r="H78">
+        <v>25.81</v>
+      </c>
+      <c r="I78">
+        <v>18307</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A79">
+        <v>76</v>
+      </c>
+      <c r="B79">
+        <v>-269.62</v>
+      </c>
+      <c r="C79">
+        <v>-72.8</v>
+      </c>
+      <c r="D79">
+        <v>18760</v>
+      </c>
+      <c r="F79">
+        <v>76</v>
+      </c>
+      <c r="G79">
+        <v>295.44</v>
+      </c>
+      <c r="H79">
+        <v>27.21</v>
+      </c>
+      <c r="I79">
+        <v>18365</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A80">
+        <v>77</v>
+      </c>
+      <c r="B80">
+        <v>-271.95999999999998</v>
+      </c>
+      <c r="C80">
+        <v>-74.150000000000006</v>
+      </c>
+      <c r="D80">
+        <v>18810</v>
+      </c>
+      <c r="F80">
+        <v>77</v>
+      </c>
+      <c r="G80">
+        <v>300.25</v>
+      </c>
+      <c r="H80">
+        <v>-626.89</v>
+      </c>
+      <c r="I80">
+        <v>18415</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A81">
+        <v>78</v>
+      </c>
+      <c r="B81">
+        <v>-275.25</v>
+      </c>
+      <c r="C81">
+        <v>-76.099999999999994</v>
+      </c>
+      <c r="D81">
+        <v>18860</v>
+      </c>
+      <c r="F81">
+        <v>78</v>
+      </c>
+      <c r="G81">
+        <v>305.04000000000002</v>
+      </c>
+      <c r="H81">
+        <v>-625.54999999999995</v>
+      </c>
+      <c r="I81">
+        <v>18465</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A82">
+        <v>79</v>
+      </c>
+      <c r="B82">
+        <v>-277.68</v>
+      </c>
+      <c r="C82">
+        <v>-77.569999999999993</v>
+      </c>
+      <c r="D82">
+        <v>18910</v>
+      </c>
+      <c r="F82">
+        <v>79</v>
+      </c>
+      <c r="G82">
+        <v>310.60000000000002</v>
+      </c>
+      <c r="H82">
+        <v>-623.83000000000004</v>
+      </c>
+      <c r="I82">
+        <v>18524</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A83">
+        <v>80</v>
+      </c>
+      <c r="B83">
+        <v>-281.32</v>
+      </c>
+      <c r="C83">
+        <v>-79.78</v>
+      </c>
+      <c r="D83">
+        <v>18960</v>
+      </c>
+      <c r="F83">
+        <v>80</v>
+      </c>
+      <c r="G83">
+        <v>315.72000000000003</v>
+      </c>
+      <c r="H83">
+        <v>-622.11</v>
+      </c>
+      <c r="I83">
+        <v>18583</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A84">
+        <v>81</v>
+      </c>
+      <c r="B84">
+        <v>-283.72000000000003</v>
+      </c>
+      <c r="C84">
+        <v>-81.290000000000006</v>
+      </c>
+      <c r="D84">
+        <v>19010</v>
+      </c>
+      <c r="F84">
+        <v>81</v>
+      </c>
+      <c r="G84">
+        <v>320.39999999999998</v>
+      </c>
+      <c r="H84">
+        <v>-620.42999999999995</v>
+      </c>
+      <c r="I84">
+        <v>18633</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A85">
+        <v>82</v>
+      </c>
+      <c r="B85">
+        <v>-287.2</v>
+      </c>
+      <c r="C85">
+        <v>-83.48</v>
+      </c>
+      <c r="D85">
+        <v>19060</v>
+      </c>
+      <c r="F85">
+        <v>82</v>
+      </c>
+      <c r="G85">
+        <v>325.95999999999998</v>
+      </c>
+      <c r="H85">
+        <v>-618.27</v>
+      </c>
+      <c r="I85">
+        <v>18692</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A86">
+        <v>83</v>
+      </c>
+      <c r="B86">
+        <v>-289.47000000000003</v>
+      </c>
+      <c r="C86">
+        <v>-84.94</v>
+      </c>
+      <c r="D86">
+        <v>19110</v>
+      </c>
+      <c r="F86">
+        <v>83</v>
+      </c>
+      <c r="G86">
+        <v>-324.94</v>
+      </c>
+      <c r="H86">
+        <v>-616.4</v>
+      </c>
+      <c r="I86">
+        <v>18742</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A87">
+        <v>84</v>
+      </c>
+      <c r="B87">
+        <v>-293.02999999999997</v>
+      </c>
+      <c r="C87">
+        <v>-87.27</v>
+      </c>
+      <c r="D87">
+        <v>19160</v>
+      </c>
+      <c r="F87">
+        <v>84</v>
+      </c>
+      <c r="G87">
+        <v>-323.89999999999998</v>
+      </c>
+      <c r="H87">
+        <v>-615.95000000000005</v>
+      </c>
+      <c r="I87">
+        <v>18792</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A88">
+        <v>85</v>
+      </c>
+      <c r="B88">
+        <v>-295.39999999999998</v>
+      </c>
+      <c r="C88">
+        <v>-88.83</v>
+      </c>
+      <c r="D88">
+        <v>19210</v>
+      </c>
+      <c r="F88">
+        <v>85</v>
+      </c>
+      <c r="G88">
+        <v>-322.86</v>
+      </c>
+      <c r="H88">
+        <v>-615.48</v>
+      </c>
+      <c r="I88">
+        <v>18842</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A89">
+        <v>86</v>
+      </c>
+      <c r="B89">
+        <v>-298.7</v>
+      </c>
+      <c r="C89">
+        <v>-91.05</v>
+      </c>
+      <c r="D89">
+        <v>19260</v>
+      </c>
+      <c r="F89">
+        <v>86</v>
+      </c>
+      <c r="G89">
+        <v>-320.42</v>
+      </c>
+      <c r="H89">
+        <v>-614.33000000000004</v>
+      </c>
+      <c r="I89">
+        <v>18902</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A90">
+        <v>87</v>
+      </c>
+      <c r="B90">
+        <v>-301.02999999999997</v>
+      </c>
+      <c r="C90">
+        <v>-92.66</v>
+      </c>
+      <c r="D90">
+        <v>19310</v>
+      </c>
+      <c r="F90">
+        <v>87</v>
+      </c>
+      <c r="G90">
+        <v>-320.17</v>
+      </c>
+      <c r="H90">
+        <v>-614.20000000000005</v>
+      </c>
+      <c r="I90">
+        <v>18961</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A91">
+        <v>88</v>
+      </c>
+      <c r="B91">
+        <v>-304.64</v>
+      </c>
+      <c r="C91">
+        <v>-95.18</v>
+      </c>
+      <c r="D91">
+        <v>19360</v>
+      </c>
+      <c r="F91">
+        <v>88</v>
+      </c>
+      <c r="G91">
+        <v>-320.17</v>
+      </c>
+      <c r="H91">
+        <v>-614.20000000000005</v>
+      </c>
+      <c r="I91">
+        <v>19011</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="F92">
+        <v>89</v>
+      </c>
+      <c r="G92">
+        <v>-320.17</v>
+      </c>
+      <c r="H92">
+        <v>-614.20000000000005</v>
+      </c>
+      <c r="I92">
+        <v>19061</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="F93">
+        <v>90</v>
+      </c>
+      <c r="G93">
+        <v>-320.17</v>
+      </c>
+      <c r="H93">
+        <v>-614.20000000000005</v>
+      </c>
+      <c r="I93">
+        <v>19111</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="F94">
+        <v>91</v>
+      </c>
+      <c r="G94">
+        <v>-320.17</v>
+      </c>
+      <c r="H94">
+        <v>-614.20000000000005</v>
+      </c>
+      <c r="I94">
+        <v>19161</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="F95">
+        <v>92</v>
+      </c>
+      <c r="G95">
+        <v>-320.17</v>
+      </c>
+      <c r="H95">
+        <v>-614.20000000000005</v>
+      </c>
+      <c r="I95">
+        <v>19211</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="F96">
+        <v>93</v>
+      </c>
+      <c r="G96">
+        <v>-320.17</v>
+      </c>
+      <c r="H96">
+        <v>-614.20000000000005</v>
+      </c>
+      <c r="I96">
+        <v>19261</v>
+      </c>
+    </row>
+    <row r="97" spans="6:9" x14ac:dyDescent="0.35">
+      <c r="F97">
+        <v>94</v>
+      </c>
+      <c r="G97">
+        <v>-320.17</v>
+      </c>
+      <c r="H97">
+        <v>-614.20000000000005</v>
+      </c>
+      <c r="I97">
+        <v>19311</v>
+      </c>
+    </row>
+    <row r="98" spans="6:9" x14ac:dyDescent="0.35">
+      <c r="F98">
+        <v>95</v>
+      </c>
+      <c r="G98">
+        <v>-320.17</v>
+      </c>
+      <c r="H98">
+        <v>-614.20000000000005</v>
+      </c>
+      <c r="I98">
+        <v>19361</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6C31DBF-3FF4-49A1-B9AC-C006401FCE48}">
+  <dimension ref="A1:K102"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2" t="s">
+        <v>1</v>
+      </c>
+      <c r="H2" t="s">
+        <v>2</v>
+      </c>
+      <c r="I2" t="s">
+        <v>3</v>
+      </c>
+      <c r="K2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>0</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>15622</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>2.91</v>
+      </c>
+      <c r="H3">
+        <v>0.91</v>
+      </c>
+      <c r="I3">
+        <v>14423</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>-0.28000000000000003</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>15672</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>2.91</v>
+      </c>
+      <c r="H4">
+        <v>0.91</v>
+      </c>
+      <c r="I4">
+        <v>14482</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5">
+        <v>-0.28000000000000003</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>15722</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>2.91</v>
+      </c>
+      <c r="H5">
+        <v>0.91</v>
+      </c>
+      <c r="I5">
+        <v>14532</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6">
+        <v>-0.28000000000000003</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>15772</v>
+      </c>
+      <c r="F6">
+        <v>3</v>
+      </c>
+      <c r="G6">
+        <v>2.91</v>
+      </c>
+      <c r="H6">
+        <v>0.91</v>
+      </c>
+      <c r="I6">
+        <v>14582</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>4</v>
+      </c>
+      <c r="B7">
+        <v>-0.85</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>15822</v>
+      </c>
+      <c r="F7">
+        <v>4</v>
+      </c>
+      <c r="G7">
+        <v>2.91</v>
+      </c>
+      <c r="H7">
+        <v>0.91</v>
+      </c>
+      <c r="I7">
+        <v>14632</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>5</v>
+      </c>
+      <c r="B8">
+        <v>-4.68</v>
+      </c>
+      <c r="C8">
+        <v>-0.02</v>
+      </c>
+      <c r="D8">
+        <v>15873</v>
+      </c>
+      <c r="F8">
+        <v>5</v>
+      </c>
+      <c r="G8">
+        <v>3.05</v>
+      </c>
+      <c r="H8">
+        <v>0.92</v>
+      </c>
+      <c r="I8">
+        <v>14682</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>6</v>
+      </c>
+      <c r="B9">
+        <v>-7.51</v>
+      </c>
+      <c r="C9">
+        <v>-7.0000000000000007E-2</v>
+      </c>
+      <c r="D9">
+        <v>15924</v>
+      </c>
+      <c r="F9">
+        <v>6</v>
+      </c>
+      <c r="G9">
+        <v>3.05</v>
+      </c>
+      <c r="H9">
+        <v>0.92</v>
+      </c>
+      <c r="I9">
+        <v>14733</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>7</v>
+      </c>
+      <c r="B10">
+        <v>-11.34</v>
+      </c>
+      <c r="C10">
+        <v>-0.15</v>
+      </c>
+      <c r="D10">
+        <v>15974</v>
+      </c>
+      <c r="F10">
+        <v>7</v>
+      </c>
+      <c r="G10">
+        <v>3.05</v>
+      </c>
+      <c r="H10">
+        <v>0.92</v>
+      </c>
+      <c r="I10">
+        <v>14783</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>8</v>
+      </c>
+      <c r="B11">
+        <v>-13.9</v>
+      </c>
+      <c r="C11">
+        <v>-0.22</v>
+      </c>
+      <c r="D11">
+        <v>16024</v>
+      </c>
+      <c r="F11">
+        <v>8</v>
+      </c>
+      <c r="G11">
+        <v>3.05</v>
+      </c>
+      <c r="H11">
+        <v>0.92</v>
+      </c>
+      <c r="I11">
+        <v>14833</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>9</v>
+      </c>
+      <c r="B12">
+        <v>-17.579999999999998</v>
+      </c>
+      <c r="C12">
+        <v>-0.36</v>
+      </c>
+      <c r="D12">
+        <v>16074</v>
+      </c>
+      <c r="F12">
+        <v>9</v>
+      </c>
+      <c r="G12">
+        <v>3.05</v>
+      </c>
+      <c r="H12">
+        <v>0.92</v>
+      </c>
+      <c r="I12">
+        <v>14884</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>10</v>
+      </c>
+      <c r="B13">
+        <v>-20.13</v>
+      </c>
+      <c r="C13">
+        <v>-0.46</v>
+      </c>
+      <c r="D13">
+        <v>16124</v>
+      </c>
+      <c r="F13">
+        <v>10</v>
+      </c>
+      <c r="G13">
+        <v>3.05</v>
+      </c>
+      <c r="H13">
+        <v>0.92</v>
+      </c>
+      <c r="I13">
+        <v>14935</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>11</v>
+      </c>
+      <c r="B14">
+        <v>-23.96</v>
+      </c>
+      <c r="C14">
+        <v>-0.64</v>
+      </c>
+      <c r="D14">
+        <v>16174</v>
+      </c>
+      <c r="F14">
+        <v>11</v>
+      </c>
+      <c r="G14">
+        <v>3.05</v>
+      </c>
+      <c r="H14">
+        <v>0.92</v>
+      </c>
+      <c r="I14">
+        <v>14994</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>12</v>
+      </c>
+      <c r="B15">
+        <v>-26.65</v>
+      </c>
+      <c r="C15">
+        <v>-0.78</v>
+      </c>
+      <c r="D15">
+        <v>16224</v>
+      </c>
+      <c r="F15">
+        <v>12</v>
+      </c>
+      <c r="G15">
+        <v>3.05</v>
+      </c>
+      <c r="H15">
+        <v>0.92</v>
+      </c>
+      <c r="I15">
+        <v>15044</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>13</v>
+      </c>
+      <c r="B16">
+        <v>-30.33</v>
+      </c>
+      <c r="C16">
+        <v>-0.99</v>
+      </c>
+      <c r="D16">
+        <v>16274</v>
+      </c>
+      <c r="F16">
+        <v>13</v>
+      </c>
+      <c r="G16">
+        <v>3.05</v>
+      </c>
+      <c r="H16">
+        <v>0.92</v>
+      </c>
+      <c r="I16">
+        <v>15095</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>14</v>
+      </c>
+      <c r="B17">
+        <v>-33.020000000000003</v>
+      </c>
+      <c r="C17">
+        <v>-1.1599999999999999</v>
+      </c>
+      <c r="D17">
+        <v>16324</v>
+      </c>
+      <c r="F17">
+        <v>14</v>
+      </c>
+      <c r="G17">
+        <v>3.05</v>
+      </c>
+      <c r="H17">
+        <v>0.92</v>
+      </c>
+      <c r="I17">
+        <v>15145</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>15</v>
+      </c>
+      <c r="B18">
+        <v>-37.270000000000003</v>
+      </c>
+      <c r="C18">
+        <v>-1.44</v>
+      </c>
+      <c r="D18">
+        <v>16375</v>
+      </c>
+      <c r="F18">
+        <v>15</v>
+      </c>
+      <c r="G18">
+        <v>3.05</v>
+      </c>
+      <c r="H18">
+        <v>0.92</v>
+      </c>
+      <c r="I18">
+        <v>15195</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>16</v>
+      </c>
+      <c r="B19">
+        <v>-39.68</v>
+      </c>
+      <c r="C19">
+        <v>-1.61</v>
+      </c>
+      <c r="D19">
+        <v>16425</v>
+      </c>
+      <c r="F19">
+        <v>16</v>
+      </c>
+      <c r="G19">
+        <v>3.05</v>
+      </c>
+      <c r="H19">
+        <v>0.92</v>
+      </c>
+      <c r="I19">
+        <v>15245</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>17</v>
+      </c>
+      <c r="B20">
+        <v>-43.64</v>
+      </c>
+      <c r="C20">
+        <v>-1.92</v>
+      </c>
+      <c r="D20">
+        <v>16475</v>
+      </c>
+      <c r="F20">
+        <v>17</v>
+      </c>
+      <c r="G20">
+        <v>3.05</v>
+      </c>
+      <c r="H20">
+        <v>0.92</v>
+      </c>
+      <c r="I20">
+        <v>15296</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>18</v>
+      </c>
+      <c r="B21">
+        <v>-46.6</v>
+      </c>
+      <c r="C21">
+        <v>-2.1800000000000002</v>
+      </c>
+      <c r="D21">
+        <v>16525</v>
+      </c>
+      <c r="F21">
+        <v>18</v>
+      </c>
+      <c r="G21">
+        <v>3.19</v>
+      </c>
+      <c r="H21">
+        <v>0.92</v>
+      </c>
+      <c r="I21">
+        <v>15346</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>19</v>
+      </c>
+      <c r="B22">
+        <v>-50.56</v>
+      </c>
+      <c r="C22">
+        <v>-2.54</v>
+      </c>
+      <c r="D22">
+        <v>16575</v>
+      </c>
+      <c r="F22">
+        <v>19</v>
+      </c>
+      <c r="G22">
+        <v>4.33</v>
+      </c>
+      <c r="H22">
+        <v>0.97</v>
+      </c>
+      <c r="I22">
+        <v>15396</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>20</v>
+      </c>
+      <c r="B23">
+        <v>-53.24</v>
+      </c>
+      <c r="C23">
+        <v>-2.81</v>
+      </c>
+      <c r="D23">
+        <v>16625</v>
+      </c>
+      <c r="F23">
+        <v>20</v>
+      </c>
+      <c r="G23">
+        <v>6.88</v>
+      </c>
+      <c r="H23">
+        <v>1.08</v>
+      </c>
+      <c r="I23">
+        <v>15447</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>21</v>
+      </c>
+      <c r="B24">
+        <v>-57.48</v>
+      </c>
+      <c r="C24">
+        <v>-3.25</v>
+      </c>
+      <c r="D24">
+        <v>16675</v>
+      </c>
+      <c r="F24">
+        <v>21</v>
+      </c>
+      <c r="G24">
+        <v>10.57</v>
+      </c>
+      <c r="H24">
+        <v>1.25</v>
+      </c>
+      <c r="I24">
+        <v>15506</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>22</v>
+      </c>
+      <c r="B25">
+        <v>-60.3</v>
+      </c>
+      <c r="C25">
+        <v>-3.56</v>
+      </c>
+      <c r="D25">
+        <v>16727</v>
+      </c>
+      <c r="F25">
+        <v>22</v>
+      </c>
+      <c r="G25">
+        <v>13.98</v>
+      </c>
+      <c r="H25">
+        <v>1.41</v>
+      </c>
+      <c r="I25">
+        <v>15556</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>23</v>
+      </c>
+      <c r="B26">
+        <v>-64.38</v>
+      </c>
+      <c r="C26">
+        <v>-4.05</v>
+      </c>
+      <c r="D26">
+        <v>16777</v>
+      </c>
+      <c r="F26">
+        <v>23</v>
+      </c>
+      <c r="G26">
+        <v>17.670000000000002</v>
+      </c>
+      <c r="H26">
+        <v>1.59</v>
+      </c>
+      <c r="I26">
+        <v>15606</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>24</v>
+      </c>
+      <c r="B27">
+        <v>-67.19</v>
+      </c>
+      <c r="C27">
+        <v>-4.41</v>
+      </c>
+      <c r="D27">
+        <v>16827</v>
+      </c>
+      <c r="F27">
+        <v>24</v>
+      </c>
+      <c r="G27">
+        <v>21.36</v>
+      </c>
+      <c r="H27">
+        <v>1.75</v>
+      </c>
+      <c r="I27">
+        <v>15656</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>25</v>
+      </c>
+      <c r="B28">
+        <v>-71.7</v>
+      </c>
+      <c r="C28">
+        <v>-5.01</v>
+      </c>
+      <c r="D28">
+        <v>16877</v>
+      </c>
+      <c r="F28">
+        <v>25</v>
+      </c>
+      <c r="G28">
+        <v>24.91</v>
+      </c>
+      <c r="H28">
+        <v>1.9</v>
+      </c>
+      <c r="I28">
+        <v>15707</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>26</v>
+      </c>
+      <c r="B29">
+        <v>-74.650000000000006</v>
+      </c>
+      <c r="C29">
+        <v>-5.42</v>
+      </c>
+      <c r="D29">
+        <v>16927</v>
+      </c>
+      <c r="F29">
+        <v>26</v>
+      </c>
+      <c r="G29">
+        <v>29.31</v>
+      </c>
+      <c r="H29">
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="I29">
+        <v>15766</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>27</v>
+      </c>
+      <c r="B30">
+        <v>-78.86</v>
+      </c>
+      <c r="C30">
+        <v>-6.03</v>
+      </c>
+      <c r="D30">
+        <v>16977</v>
+      </c>
+      <c r="F30">
+        <v>27</v>
+      </c>
+      <c r="G30">
+        <v>33.14</v>
+      </c>
+      <c r="H30">
+        <v>2.21</v>
+      </c>
+      <c r="I30">
+        <v>15816</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>28</v>
+      </c>
+      <c r="B31">
+        <v>-81.8</v>
+      </c>
+      <c r="C31">
+        <v>-6.48</v>
+      </c>
+      <c r="D31">
+        <v>17027</v>
+      </c>
+      <c r="F31">
+        <v>28</v>
+      </c>
+      <c r="G31">
+        <v>36.979999999999997</v>
+      </c>
+      <c r="H31">
+        <v>2.37</v>
+      </c>
+      <c r="I31">
+        <v>15866</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>29</v>
+      </c>
+      <c r="B32">
+        <v>-86.14</v>
+      </c>
+      <c r="C32">
+        <v>-7.18</v>
+      </c>
+      <c r="D32">
+        <v>17077</v>
+      </c>
+      <c r="F32">
+        <v>29</v>
+      </c>
+      <c r="G32">
+        <v>40.950000000000003</v>
+      </c>
+      <c r="H32">
+        <v>2.54</v>
+      </c>
+      <c r="I32">
+        <v>15917</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>30</v>
+      </c>
+      <c r="B33">
+        <v>-88.94</v>
+      </c>
+      <c r="C33">
+        <v>-7.64</v>
+      </c>
+      <c r="D33">
+        <v>17127</v>
+      </c>
+      <c r="F33">
+        <v>30</v>
+      </c>
+      <c r="G33">
+        <v>45.49</v>
+      </c>
+      <c r="H33">
+        <v>2.74</v>
+      </c>
+      <c r="I33">
+        <v>15976</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A34">
+        <v>31</v>
+      </c>
+      <c r="B34">
+        <v>-93.42</v>
+      </c>
+      <c r="C34">
+        <v>-8.42</v>
+      </c>
+      <c r="D34">
+        <v>17178</v>
+      </c>
+      <c r="F34">
+        <v>31</v>
+      </c>
+      <c r="G34">
+        <v>49.9</v>
+      </c>
+      <c r="H34">
+        <v>2.93</v>
+      </c>
+      <c r="I34">
+        <v>16026</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A35">
+        <v>32</v>
+      </c>
+      <c r="B35">
+        <v>-96.49</v>
+      </c>
+      <c r="C35">
+        <v>-8.9700000000000006</v>
+      </c>
+      <c r="D35">
+        <v>17228</v>
+      </c>
+      <c r="F35">
+        <v>32</v>
+      </c>
+      <c r="G35">
+        <v>54.01</v>
+      </c>
+      <c r="H35">
+        <v>3.13</v>
+      </c>
+      <c r="I35">
+        <v>16076</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A36">
+        <v>33</v>
+      </c>
+      <c r="B36">
+        <v>-100.95</v>
+      </c>
+      <c r="C36">
+        <v>-9.8000000000000007</v>
+      </c>
+      <c r="D36">
+        <v>17278</v>
+      </c>
+      <c r="F36">
+        <v>33</v>
+      </c>
+      <c r="G36">
+        <v>58.13</v>
+      </c>
+      <c r="H36">
+        <v>3.34</v>
+      </c>
+      <c r="I36">
+        <v>16126</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A37">
+        <v>34</v>
+      </c>
+      <c r="B37">
+        <v>-104.02</v>
+      </c>
+      <c r="C37">
+        <v>-10.39</v>
+      </c>
+      <c r="D37">
+        <v>17328</v>
+      </c>
+      <c r="F37">
+        <v>34</v>
+      </c>
+      <c r="G37">
+        <v>62.53</v>
+      </c>
+      <c r="H37">
+        <v>3.58</v>
+      </c>
+      <c r="I37">
+        <v>16177</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A38">
+        <v>35</v>
+      </c>
+      <c r="B38">
+        <v>-108.61</v>
+      </c>
+      <c r="C38">
+        <v>-11.32</v>
+      </c>
+      <c r="D38">
+        <v>17378</v>
+      </c>
+      <c r="F38">
+        <v>35</v>
+      </c>
+      <c r="G38">
+        <v>67.489999999999995</v>
+      </c>
+      <c r="H38">
+        <v>3.87</v>
+      </c>
+      <c r="I38">
+        <v>16236</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A39">
+        <v>36</v>
+      </c>
+      <c r="B39">
+        <v>-111.66</v>
+      </c>
+      <c r="C39">
+        <v>-11.96</v>
+      </c>
+      <c r="D39">
+        <v>17428</v>
+      </c>
+      <c r="F39">
+        <v>36</v>
+      </c>
+      <c r="G39">
+        <v>71.89</v>
+      </c>
+      <c r="H39">
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="I39">
+        <v>16286</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A40">
+        <v>37</v>
+      </c>
+      <c r="B40">
+        <v>-116.23</v>
+      </c>
+      <c r="C40">
+        <v>-12.96</v>
+      </c>
+      <c r="D40">
+        <v>17478</v>
+      </c>
+      <c r="F40">
+        <v>37</v>
+      </c>
+      <c r="G40">
+        <v>76.42</v>
+      </c>
+      <c r="H40">
+        <v>4.46</v>
+      </c>
+      <c r="I40">
+        <v>16336</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A41">
+        <v>38</v>
+      </c>
+      <c r="B41">
+        <v>-119.41</v>
+      </c>
+      <c r="C41">
+        <v>-13.69</v>
+      </c>
+      <c r="D41">
+        <v>17528</v>
+      </c>
+      <c r="F41">
+        <v>38</v>
+      </c>
+      <c r="G41">
+        <v>80.959999999999994</v>
+      </c>
+      <c r="H41">
+        <v>4.7699999999999996</v>
+      </c>
+      <c r="I41">
+        <v>16387</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A42">
+        <v>39</v>
+      </c>
+      <c r="B42">
+        <v>-123.84</v>
+      </c>
+      <c r="C42">
+        <v>-14.71</v>
+      </c>
+      <c r="D42">
+        <v>17579</v>
+      </c>
+      <c r="F42">
+        <v>39</v>
+      </c>
+      <c r="G42">
+        <v>86.2</v>
+      </c>
+      <c r="H42">
+        <v>5.14</v>
+      </c>
+      <c r="I42">
+        <v>16446</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A43">
+        <v>40</v>
+      </c>
+      <c r="B43">
+        <v>-126.87</v>
+      </c>
+      <c r="C43">
+        <v>-15.44</v>
+      </c>
+      <c r="D43">
+        <v>17629</v>
+      </c>
+      <c r="F43">
+        <v>40</v>
+      </c>
+      <c r="G43">
+        <v>89.89</v>
+      </c>
+      <c r="H43">
+        <v>5.42</v>
+      </c>
+      <c r="I43">
+        <v>16496</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A44">
+        <v>41</v>
+      </c>
+      <c r="B44">
+        <v>-131.56</v>
+      </c>
+      <c r="C44">
+        <v>-16.59</v>
+      </c>
+      <c r="D44">
+        <v>17679</v>
+      </c>
+      <c r="F44">
+        <v>41</v>
+      </c>
+      <c r="G44">
+        <v>94.99</v>
+      </c>
+      <c r="H44">
+        <v>5.84</v>
+      </c>
+      <c r="I44">
+        <v>16546</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A45">
+        <v>42</v>
+      </c>
+      <c r="B45">
+        <v>-134.58000000000001</v>
+      </c>
+      <c r="C45">
+        <v>-17.36</v>
+      </c>
+      <c r="D45">
+        <v>17729</v>
+      </c>
+      <c r="F45">
+        <v>42</v>
+      </c>
+      <c r="G45">
+        <v>99.52</v>
+      </c>
+      <c r="H45">
+        <v>6.22</v>
+      </c>
+      <c r="I45">
+        <v>16596</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A46">
+        <v>43</v>
+      </c>
+      <c r="B46">
+        <v>-139.38999999999999</v>
+      </c>
+      <c r="C46">
+        <v>-18.61</v>
+      </c>
+      <c r="D46">
+        <v>17779</v>
+      </c>
+      <c r="F46">
+        <v>43</v>
+      </c>
+      <c r="G46">
+        <v>105.04</v>
+      </c>
+      <c r="H46">
+        <v>6.72</v>
+      </c>
+      <c r="I46">
+        <v>16656</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A47">
+        <v>44</v>
+      </c>
+      <c r="B47">
+        <v>-142.66999999999999</v>
+      </c>
+      <c r="C47">
+        <v>-19.5</v>
+      </c>
+      <c r="D47">
+        <v>17830</v>
+      </c>
+      <c r="F47">
+        <v>44</v>
+      </c>
+      <c r="G47">
+        <v>110.55</v>
+      </c>
+      <c r="H47">
+        <v>7.22</v>
+      </c>
+      <c r="I47">
+        <v>16715</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A48">
+        <v>45</v>
+      </c>
+      <c r="B48">
+        <v>-147.46</v>
+      </c>
+      <c r="C48">
+        <v>-20.83</v>
+      </c>
+      <c r="D48">
+        <v>17880</v>
+      </c>
+      <c r="F48">
+        <v>45</v>
+      </c>
+      <c r="G48">
+        <v>115.22</v>
+      </c>
+      <c r="H48">
+        <v>7.67</v>
+      </c>
+      <c r="I48">
+        <v>16765</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A49">
+        <v>46</v>
+      </c>
+      <c r="B49">
+        <v>-150.44999999999999</v>
+      </c>
+      <c r="C49">
+        <v>-21.7</v>
+      </c>
+      <c r="D49">
+        <v>17930</v>
+      </c>
+      <c r="F49">
+        <v>46</v>
+      </c>
+      <c r="G49">
+        <v>119.89</v>
+      </c>
+      <c r="H49">
+        <v>8.1199999999999992</v>
+      </c>
+      <c r="I49">
+        <v>16816</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A50">
+        <v>47</v>
+      </c>
+      <c r="B50">
+        <v>-155.35</v>
+      </c>
+      <c r="C50">
+        <v>-23.15</v>
+      </c>
+      <c r="D50">
+        <v>17980</v>
+      </c>
+      <c r="F50">
+        <v>47</v>
+      </c>
+      <c r="G50">
+        <v>125.26</v>
+      </c>
+      <c r="H50">
+        <v>8.64</v>
+      </c>
+      <c r="I50">
+        <v>16875</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A51">
+        <v>48</v>
+      </c>
+      <c r="B51">
+        <v>-158.34</v>
+      </c>
+      <c r="C51">
+        <v>-24.06</v>
+      </c>
+      <c r="D51">
+        <v>18030</v>
+      </c>
+      <c r="F51">
+        <v>48</v>
+      </c>
+      <c r="G51">
+        <v>129.79</v>
+      </c>
+      <c r="H51">
+        <v>9.06</v>
+      </c>
+      <c r="I51">
+        <v>16925</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A52">
+        <v>49</v>
+      </c>
+      <c r="B52">
+        <v>-163.08000000000001</v>
+      </c>
+      <c r="C52">
+        <v>-25.53</v>
+      </c>
+      <c r="D52">
+        <v>18080</v>
+      </c>
+      <c r="F52">
+        <v>49</v>
+      </c>
+      <c r="G52">
+        <v>134.6</v>
+      </c>
+      <c r="H52">
+        <v>9.52</v>
+      </c>
+      <c r="I52">
+        <v>16975</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A53">
+        <v>50</v>
+      </c>
+      <c r="B53">
+        <v>-166.19</v>
+      </c>
+      <c r="C53">
+        <v>-26.52</v>
+      </c>
+      <c r="D53">
+        <v>18130</v>
+      </c>
+      <c r="F53">
+        <v>50</v>
+      </c>
+      <c r="G53">
+        <v>139.41</v>
+      </c>
+      <c r="H53">
+        <v>10.029999999999999</v>
+      </c>
+      <c r="I53">
+        <v>17026</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A54">
+        <v>51</v>
+      </c>
+      <c r="B54">
+        <v>-171.17</v>
+      </c>
+      <c r="C54">
+        <v>-28.16</v>
+      </c>
+      <c r="D54">
+        <v>18180</v>
+      </c>
+      <c r="F54">
+        <v>51</v>
+      </c>
+      <c r="G54">
+        <v>144.77000000000001</v>
+      </c>
+      <c r="H54">
+        <v>10.62</v>
+      </c>
+      <c r="I54">
+        <v>17085</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A55">
+        <v>52</v>
+      </c>
+      <c r="B55">
+        <v>-174.4</v>
+      </c>
+      <c r="C55">
+        <v>-29.25</v>
+      </c>
+      <c r="D55">
+        <v>18231</v>
+      </c>
+      <c r="F55">
+        <v>52</v>
+      </c>
+      <c r="G55">
+        <v>149.15</v>
+      </c>
+      <c r="H55">
+        <v>11.12</v>
+      </c>
+      <c r="I55">
+        <v>17135</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A56">
+        <v>53</v>
+      </c>
+      <c r="B56">
+        <v>-179.09</v>
+      </c>
+      <c r="C56">
+        <v>-30.88</v>
+      </c>
+      <c r="D56">
+        <v>18281</v>
+      </c>
+      <c r="F56">
+        <v>53</v>
+      </c>
+      <c r="G56">
+        <v>153.94999999999999</v>
+      </c>
+      <c r="H56">
+        <v>11.7</v>
+      </c>
+      <c r="I56">
+        <v>17185</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A57">
+        <v>54</v>
+      </c>
+      <c r="B57">
+        <v>-182.3</v>
+      </c>
+      <c r="C57">
+        <v>-32.020000000000003</v>
+      </c>
+      <c r="D57">
+        <v>18331</v>
+      </c>
+      <c r="F57">
+        <v>54</v>
+      </c>
+      <c r="G57">
+        <v>158.74</v>
+      </c>
+      <c r="H57">
+        <v>12.31</v>
+      </c>
+      <c r="I57">
+        <v>17235</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A58">
+        <v>55</v>
+      </c>
+      <c r="B58">
+        <v>-187.23</v>
+      </c>
+      <c r="C58">
+        <v>-33.82</v>
+      </c>
+      <c r="D58">
+        <v>18381</v>
+      </c>
+      <c r="F58">
+        <v>55</v>
+      </c>
+      <c r="G58">
+        <v>163.38</v>
+      </c>
+      <c r="H58">
+        <v>12.95</v>
+      </c>
+      <c r="I58">
+        <v>17285</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A59">
+        <v>56</v>
+      </c>
+      <c r="B59">
+        <v>-190.42</v>
+      </c>
+      <c r="C59">
+        <v>-35.01</v>
+      </c>
+      <c r="D59">
+        <v>18432</v>
+      </c>
+      <c r="F59">
+        <v>56</v>
+      </c>
+      <c r="G59">
+        <v>168.02</v>
+      </c>
+      <c r="H59">
+        <v>13.62</v>
+      </c>
+      <c r="I59">
+        <v>17335</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A60">
+        <v>57</v>
+      </c>
+      <c r="B60">
+        <v>-195.32</v>
+      </c>
+      <c r="C60">
+        <v>-36.89</v>
+      </c>
+      <c r="D60">
+        <v>18482</v>
+      </c>
+      <c r="F60">
+        <v>57</v>
+      </c>
+      <c r="G60">
+        <v>172.94</v>
+      </c>
+      <c r="H60">
+        <v>14.35</v>
+      </c>
+      <c r="I60">
+        <v>17385</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A61">
+        <v>58</v>
+      </c>
+      <c r="B61">
+        <v>-198.63</v>
+      </c>
+      <c r="C61">
+        <v>-38.18</v>
+      </c>
+      <c r="D61">
+        <v>18532</v>
+      </c>
+      <c r="F61">
+        <v>58</v>
+      </c>
+      <c r="G61">
+        <v>177.72</v>
+      </c>
+      <c r="H61">
+        <v>15.1</v>
+      </c>
+      <c r="I61">
+        <v>17435</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A62">
+        <v>59</v>
+      </c>
+      <c r="B62">
+        <v>-203.5</v>
+      </c>
+      <c r="C62">
+        <v>-40.119999999999997</v>
+      </c>
+      <c r="D62">
+        <v>18582</v>
+      </c>
+      <c r="F62">
+        <v>59</v>
+      </c>
+      <c r="G62">
+        <v>182.35</v>
+      </c>
+      <c r="H62">
+        <v>15.84</v>
+      </c>
+      <c r="I62">
+        <v>17485</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A63">
+        <v>60</v>
+      </c>
+      <c r="B63">
+        <v>-206.79</v>
+      </c>
+      <c r="C63">
+        <v>-41.46</v>
+      </c>
+      <c r="D63">
+        <v>18632</v>
+      </c>
+      <c r="F63">
+        <v>60</v>
+      </c>
+      <c r="G63">
+        <v>187.25</v>
+      </c>
+      <c r="H63">
+        <v>16.670000000000002</v>
+      </c>
+      <c r="I63">
+        <v>17536</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A64">
+        <v>61</v>
+      </c>
+      <c r="B64">
+        <v>-211.63</v>
+      </c>
+      <c r="C64">
+        <v>-43.47</v>
+      </c>
+      <c r="D64">
+        <v>18682</v>
+      </c>
+      <c r="F64">
+        <v>61</v>
+      </c>
+      <c r="G64">
+        <v>192.85</v>
+      </c>
+      <c r="H64">
+        <v>17.63</v>
+      </c>
+      <c r="I64">
+        <v>17595</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A65">
+        <v>62</v>
+      </c>
+      <c r="B65">
+        <v>-214.77</v>
+      </c>
+      <c r="C65">
+        <v>-44.8</v>
+      </c>
+      <c r="D65">
+        <v>18732</v>
+      </c>
+      <c r="F65">
+        <v>62</v>
+      </c>
+      <c r="G65">
+        <v>197.47</v>
+      </c>
+      <c r="H65">
+        <v>18.46</v>
+      </c>
+      <c r="I65">
+        <v>17645</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A66">
+        <v>63</v>
+      </c>
+      <c r="B66">
+        <v>-219.58</v>
+      </c>
+      <c r="C66">
+        <v>-46.89</v>
+      </c>
+      <c r="D66">
+        <v>18782</v>
+      </c>
+      <c r="F66">
+        <v>63</v>
+      </c>
+      <c r="G66">
+        <v>202.22</v>
+      </c>
+      <c r="H66">
+        <v>19.32</v>
+      </c>
+      <c r="I66">
+        <v>17695</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A67">
+        <v>64</v>
+      </c>
+      <c r="B67">
+        <v>-222.83</v>
+      </c>
+      <c r="C67">
+        <v>-48.33</v>
+      </c>
+      <c r="D67">
+        <v>18832</v>
+      </c>
+      <c r="F67">
+        <v>64</v>
+      </c>
+      <c r="G67">
+        <v>207.11</v>
+      </c>
+      <c r="H67">
+        <v>20.239999999999998</v>
+      </c>
+      <c r="I67">
+        <v>17745</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A68">
+        <v>65</v>
+      </c>
+      <c r="B68">
+        <v>-227.74</v>
+      </c>
+      <c r="C68">
+        <v>-50.55</v>
+      </c>
+      <c r="D68">
+        <v>18882</v>
+      </c>
+      <c r="F68">
+        <v>65</v>
+      </c>
+      <c r="G68">
+        <v>212.13</v>
+      </c>
+      <c r="H68">
+        <v>21.24</v>
+      </c>
+      <c r="I68">
+        <v>17796</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A69">
+        <v>66</v>
+      </c>
+      <c r="B69">
+        <v>-230.95</v>
+      </c>
+      <c r="C69">
+        <v>-52.05</v>
+      </c>
+      <c r="D69">
+        <v>18932</v>
+      </c>
+      <c r="F69">
+        <v>66</v>
+      </c>
+      <c r="G69">
+        <v>217.83</v>
+      </c>
+      <c r="H69">
+        <v>22.41</v>
+      </c>
+      <c r="I69">
+        <v>17855</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A70">
+        <v>67</v>
+      </c>
+      <c r="B70">
+        <v>-235.83</v>
+      </c>
+      <c r="C70">
+        <v>-54.35</v>
+      </c>
+      <c r="D70">
+        <v>18982</v>
+      </c>
+      <c r="F70">
+        <v>67</v>
+      </c>
+      <c r="G70">
+        <v>223.4</v>
+      </c>
+      <c r="H70">
+        <v>23.57</v>
+      </c>
+      <c r="I70">
+        <v>17914</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A71">
+        <v>68</v>
+      </c>
+      <c r="B71">
+        <v>-239.14</v>
+      </c>
+      <c r="C71">
+        <v>-55.96</v>
+      </c>
+      <c r="D71">
+        <v>19032</v>
+      </c>
+      <c r="F71">
+        <v>68</v>
+      </c>
+      <c r="G71">
+        <v>228.26</v>
+      </c>
+      <c r="H71">
+        <v>24.61</v>
+      </c>
+      <c r="I71">
+        <v>17965</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A72">
+        <v>69</v>
+      </c>
+      <c r="B72">
+        <v>-243.98</v>
+      </c>
+      <c r="C72">
+        <v>-58.35</v>
+      </c>
+      <c r="D72">
+        <v>19082</v>
+      </c>
+      <c r="F72">
+        <v>69</v>
+      </c>
+      <c r="G72">
+        <v>233.95</v>
+      </c>
+      <c r="H72">
+        <v>25.87</v>
+      </c>
+      <c r="I72">
+        <v>18024</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A73">
+        <v>70</v>
+      </c>
+      <c r="B73">
+        <v>-247.28</v>
+      </c>
+      <c r="C73">
+        <v>-60</v>
+      </c>
+      <c r="D73">
+        <v>19132</v>
+      </c>
+      <c r="F73">
+        <v>70</v>
+      </c>
+      <c r="G73">
+        <v>238.66</v>
+      </c>
+      <c r="H73">
+        <v>26.96</v>
+      </c>
+      <c r="I73">
+        <v>18074</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A74">
+        <v>71</v>
+      </c>
+      <c r="B74">
+        <v>-252.2</v>
+      </c>
+      <c r="C74">
+        <v>-62.52</v>
+      </c>
+      <c r="D74">
+        <v>19182</v>
+      </c>
+      <c r="F74">
+        <v>71</v>
+      </c>
+      <c r="G74">
+        <v>243.36</v>
+      </c>
+      <c r="H74">
+        <v>-627.29</v>
+      </c>
+      <c r="I74">
+        <v>18124</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A75">
+        <v>72</v>
+      </c>
+      <c r="B75">
+        <v>-255.47</v>
+      </c>
+      <c r="C75">
+        <v>-64.23</v>
+      </c>
+      <c r="D75">
+        <v>19232</v>
+      </c>
+      <c r="F75">
+        <v>72</v>
+      </c>
+      <c r="G75">
+        <v>248.18</v>
+      </c>
+      <c r="H75">
+        <v>-626.09</v>
+      </c>
+      <c r="I75">
+        <v>18174</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A76">
+        <v>73</v>
+      </c>
+      <c r="B76">
+        <v>-260.47000000000003</v>
+      </c>
+      <c r="C76">
+        <v>-66.92</v>
+      </c>
+      <c r="D76">
+        <v>19282</v>
+      </c>
+      <c r="F76">
+        <v>73</v>
+      </c>
+      <c r="G76">
+        <v>252.86</v>
+      </c>
+      <c r="H76">
+        <v>-624.88</v>
+      </c>
+      <c r="I76">
+        <v>18224</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A77">
+        <v>74</v>
+      </c>
+      <c r="B77">
+        <v>-263.33</v>
+      </c>
+      <c r="C77">
+        <v>-68.48</v>
+      </c>
+      <c r="D77">
+        <v>19332</v>
+      </c>
+      <c r="F77">
+        <v>74</v>
+      </c>
+      <c r="G77">
+        <v>257.8</v>
+      </c>
+      <c r="H77">
+        <v>-623.55999999999995</v>
+      </c>
+      <c r="I77">
+        <v>18274</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A78">
+        <v>75</v>
+      </c>
+      <c r="B78">
+        <v>-266.68</v>
+      </c>
+      <c r="C78">
+        <v>-70.34</v>
+      </c>
+      <c r="D78">
+        <v>19382</v>
+      </c>
+      <c r="F78">
+        <v>75</v>
+      </c>
+      <c r="G78">
+        <v>262.45999999999998</v>
+      </c>
+      <c r="H78">
+        <v>-622.27</v>
+      </c>
+      <c r="I78">
+        <v>18324</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A79">
+        <v>76</v>
+      </c>
+      <c r="B79">
+        <v>-269.14999999999998</v>
+      </c>
+      <c r="C79">
+        <v>-71.739999999999995</v>
+      </c>
+      <c r="D79">
+        <v>19432</v>
+      </c>
+      <c r="F79">
+        <v>76</v>
+      </c>
+      <c r="G79">
+        <v>267.24</v>
+      </c>
+      <c r="H79">
+        <v>-620.89</v>
+      </c>
+      <c r="I79">
+        <v>18374</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A80">
+        <v>77</v>
+      </c>
+      <c r="B80">
+        <v>-272.45999999999998</v>
+      </c>
+      <c r="C80">
+        <v>-73.66</v>
+      </c>
+      <c r="D80">
+        <v>19482</v>
+      </c>
+      <c r="F80">
+        <v>77</v>
+      </c>
+      <c r="G80">
+        <v>271.45</v>
+      </c>
+      <c r="H80">
+        <v>-619.62</v>
+      </c>
+      <c r="I80">
+        <v>18424</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A81">
+        <v>78</v>
+      </c>
+      <c r="B81">
+        <v>-274.77999999999997</v>
+      </c>
+      <c r="C81">
+        <v>-75.03</v>
+      </c>
+      <c r="D81">
+        <v>19532</v>
+      </c>
+      <c r="F81">
+        <v>78</v>
+      </c>
+      <c r="G81">
+        <v>276.2</v>
+      </c>
+      <c r="H81">
+        <v>-618.15</v>
+      </c>
+      <c r="I81">
+        <v>18475</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A82">
+        <v>79</v>
+      </c>
+      <c r="B82">
+        <v>-278.55</v>
+      </c>
+      <c r="C82">
+        <v>-77.31</v>
+      </c>
+      <c r="D82">
+        <v>19582</v>
+      </c>
+      <c r="F82">
+        <v>79</v>
+      </c>
+      <c r="G82">
+        <v>281.76</v>
+      </c>
+      <c r="H82">
+        <v>-616.38</v>
+      </c>
+      <c r="I82">
+        <v>18533</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A83">
+        <v>80</v>
+      </c>
+      <c r="B83">
+        <v>-280.95999999999998</v>
+      </c>
+      <c r="C83">
+        <v>-78.8</v>
+      </c>
+      <c r="D83">
+        <v>19632</v>
+      </c>
+      <c r="F83">
+        <v>80</v>
+      </c>
+      <c r="G83">
+        <v>286.48</v>
+      </c>
+      <c r="H83">
+        <v>-614.83000000000004</v>
+      </c>
+      <c r="I83">
+        <v>18583</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A84">
+        <v>81</v>
+      </c>
+      <c r="B84">
+        <v>-284.2</v>
+      </c>
+      <c r="C84">
+        <v>-80.84</v>
+      </c>
+      <c r="D84">
+        <v>19683</v>
+      </c>
+      <c r="F84">
+        <v>81</v>
+      </c>
+      <c r="G84">
+        <v>291.19</v>
+      </c>
+      <c r="H84">
+        <v>-613.23</v>
+      </c>
+      <c r="I84">
+        <v>18633</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A85">
+        <v>82</v>
+      </c>
+      <c r="B85">
+        <v>-286.47000000000003</v>
+      </c>
+      <c r="C85">
+        <v>-82.29</v>
+      </c>
+      <c r="D85">
+        <v>19734</v>
+      </c>
+      <c r="F85">
+        <v>82</v>
+      </c>
+      <c r="G85">
+        <v>296.02999999999997</v>
+      </c>
+      <c r="H85">
+        <v>-611.58000000000004</v>
+      </c>
+      <c r="I85">
+        <v>18683</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A86">
+        <v>83</v>
+      </c>
+      <c r="B86">
+        <v>-290.02999999999997</v>
+      </c>
+      <c r="C86">
+        <v>-84.62</v>
+      </c>
+      <c r="D86">
+        <v>19784</v>
+      </c>
+      <c r="F86">
+        <v>83</v>
+      </c>
+      <c r="G86">
+        <v>300.72000000000003</v>
+      </c>
+      <c r="H86">
+        <v>-609.92999999999995</v>
+      </c>
+      <c r="I86">
+        <v>18734</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A87">
+        <v>84</v>
+      </c>
+      <c r="B87">
+        <v>-292.39999999999998</v>
+      </c>
+      <c r="C87">
+        <v>-86.19</v>
+      </c>
+      <c r="D87">
+        <v>19834</v>
+      </c>
+      <c r="F87">
+        <v>84</v>
+      </c>
+      <c r="G87">
+        <v>306.20999999999998</v>
+      </c>
+      <c r="H87">
+        <v>-607.96</v>
+      </c>
+      <c r="I87">
+        <v>18793</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A88">
+        <v>85</v>
+      </c>
+      <c r="B88">
+        <v>-295.93</v>
+      </c>
+      <c r="C88">
+        <v>-88.56</v>
+      </c>
+      <c r="D88">
+        <v>19884</v>
+      </c>
+      <c r="F88">
+        <v>85</v>
+      </c>
+      <c r="G88">
+        <v>310.47000000000003</v>
+      </c>
+      <c r="H88">
+        <v>-606.39</v>
+      </c>
+      <c r="I88">
+        <v>18843</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A89">
+        <v>86</v>
+      </c>
+      <c r="B89">
+        <v>-298.27</v>
+      </c>
+      <c r="C89">
+        <v>-90.17</v>
+      </c>
+      <c r="D89">
+        <v>19934</v>
+      </c>
+      <c r="F89">
+        <v>86</v>
+      </c>
+      <c r="G89">
+        <v>314.2</v>
+      </c>
+      <c r="H89">
+        <v>-605.01</v>
+      </c>
+      <c r="I89">
+        <v>18903</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A90">
+        <v>87</v>
+      </c>
+      <c r="B90">
+        <v>-301.66000000000003</v>
+      </c>
+      <c r="C90">
+        <v>-92.51</v>
+      </c>
+      <c r="D90">
+        <v>19984</v>
+      </c>
+      <c r="F90">
+        <v>87</v>
+      </c>
+      <c r="G90">
+        <v>314.33999999999997</v>
+      </c>
+      <c r="H90">
+        <v>-604.96</v>
+      </c>
+      <c r="I90">
+        <v>18953</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A91">
+        <v>88</v>
+      </c>
+      <c r="B91">
+        <v>-303.86</v>
+      </c>
+      <c r="C91">
+        <v>-94.06</v>
+      </c>
+      <c r="D91">
+        <v>20034</v>
+      </c>
+      <c r="F91">
+        <v>88</v>
+      </c>
+      <c r="G91">
+        <v>317</v>
+      </c>
+      <c r="H91">
+        <v>-603.95000000000005</v>
+      </c>
+      <c r="I91">
+        <v>19003</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="F92">
+        <v>89</v>
+      </c>
+      <c r="G92">
+        <v>320.31</v>
+      </c>
+      <c r="H92">
+        <v>-602.66</v>
+      </c>
+      <c r="I92">
+        <v>19053</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="F93">
+        <v>90</v>
+      </c>
+      <c r="G93">
+        <v>324.26</v>
+      </c>
+      <c r="H93">
+        <v>-601.07000000000005</v>
+      </c>
+      <c r="I93">
+        <v>19103</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="F94">
+        <v>91</v>
+      </c>
+      <c r="G94">
+        <v>326.37</v>
+      </c>
+      <c r="H94">
+        <v>-600.21</v>
+      </c>
+      <c r="I94">
+        <v>19162</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="F95">
+        <v>92</v>
+      </c>
+      <c r="G95">
+        <v>326.37</v>
+      </c>
+      <c r="H95">
+        <v>-600.21</v>
+      </c>
+      <c r="I95">
+        <v>19213</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="F96">
+        <v>93</v>
+      </c>
+      <c r="G96">
+        <v>-327.54000000000002</v>
+      </c>
+      <c r="H96">
+        <v>-599.63</v>
+      </c>
+      <c r="I96">
+        <v>19272</v>
+      </c>
+    </row>
+    <row r="97" spans="6:9" x14ac:dyDescent="0.35">
+      <c r="F97">
+        <v>94</v>
+      </c>
+      <c r="G97">
+        <v>-327.54000000000002</v>
+      </c>
+      <c r="H97">
+        <v>-599.63</v>
+      </c>
+      <c r="I97">
+        <v>19322</v>
+      </c>
+    </row>
+    <row r="98" spans="6:9" x14ac:dyDescent="0.35">
+      <c r="F98">
+        <v>95</v>
+      </c>
+      <c r="G98">
+        <v>-327.54000000000002</v>
+      </c>
+      <c r="H98">
+        <v>-599.63</v>
+      </c>
+      <c r="I98">
+        <v>19373</v>
+      </c>
+    </row>
+    <row r="99" spans="6:9" x14ac:dyDescent="0.35">
+      <c r="F99">
+        <v>96</v>
+      </c>
+      <c r="G99">
+        <v>-327.54000000000002</v>
+      </c>
+      <c r="H99">
+        <v>-599.63</v>
+      </c>
+      <c r="I99">
+        <v>19432</v>
+      </c>
+    </row>
+    <row r="100" spans="6:9" x14ac:dyDescent="0.35">
+      <c r="F100">
+        <v>97</v>
+      </c>
+      <c r="G100">
+        <v>-327.54000000000002</v>
+      </c>
+      <c r="H100">
+        <v>-599.63</v>
+      </c>
+      <c r="I100">
+        <v>19482</v>
+      </c>
+    </row>
+    <row r="101" spans="6:9" x14ac:dyDescent="0.35">
+      <c r="F101">
+        <v>98</v>
+      </c>
+      <c r="G101">
+        <v>-327.54000000000002</v>
+      </c>
+      <c r="H101">
+        <v>-599.63</v>
+      </c>
+      <c r="I101">
+        <v>19532</v>
+      </c>
+    </row>
+    <row r="102" spans="6:9" x14ac:dyDescent="0.35">
+      <c r="F102">
+        <v>99</v>
+      </c>
+      <c r="G102">
+        <v>-327.54000000000002</v>
+      </c>
+      <c r="H102">
+        <v>-599.63</v>
+      </c>
+      <c r="I102">
+        <v>19582</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AF85FAD-65A7-4226-BB8B-0A49844BC654}">
   <dimension ref="A1:J101"/>
